--- a/pidsg25Evaluation.xlsx
+++ b/pidsg25Evaluation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/debdeeppaul/Documents/Procurement/PIDSG25/pricesaa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD96E74-0C45-9844-A652-D8FDBCE7C14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B528CF3A-B94D-994B-B87A-97D3F6471DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="28800" windowHeight="15680" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15680" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="from_alvin" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,9 @@
     <sheet name="Eval04" sheetId="5" r:id="rId5"/>
     <sheet name="Eval07" sheetId="7" r:id="rId6"/>
     <sheet name="Eval08" sheetId="9" r:id="rId7"/>
-    <sheet name="Eval07Clean" sheetId="8" r:id="rId8"/>
-    <sheet name="Eval08Clean" sheetId="10" r:id="rId9"/>
+    <sheet name="Eval08Stor" sheetId="11" r:id="rId8"/>
+    <sheet name="Eval07Clean" sheetId="8" r:id="rId9"/>
+    <sheet name="Eval08Clean" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="99">
   <si>
     <t>FY24</t>
   </si>
@@ -449,7 +450,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -485,6 +486,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -16840,6 +16844,645 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{350C6D2B-71FC-0A4A-8981-25C5B83CB6E9}">
+  <dimension ref="A1:T13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="48" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="N1" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A2" s="12">
+        <v>45748</v>
+      </c>
+      <c r="B2">
+        <v>1.5288157894736842</v>
+      </c>
+      <c r="C2">
+        <v>1.4112105263157895</v>
+      </c>
+      <c r="D2">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="E2">
+        <v>9513.1687242798362</v>
+      </c>
+      <c r="F2">
+        <f t="shared" ref="F2:F13" si="0">SUM(D2:E2)</f>
+        <v>14400</v>
+      </c>
+      <c r="G2" s="8">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H2" s="8">
+        <v>9513.1687242798362</v>
+      </c>
+      <c r="I2">
+        <f>SUM(G2:H2)</f>
+        <v>14400</v>
+      </c>
+      <c r="J2">
+        <v>10314.285714285714</v>
+      </c>
+      <c r="K2">
+        <v>254.28571428571433</v>
+      </c>
+      <c r="L2">
+        <v>254.28571428571433</v>
+      </c>
+      <c r="M2">
+        <f>C2*E2</f>
+        <v>13425.083842321856</v>
+      </c>
+      <c r="N2">
+        <f>C2*H2</f>
+        <v>13425.083842321856</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A3" s="12">
+        <v>45778</v>
+      </c>
+      <c r="B3">
+        <v>1.5806907894736841</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="E3">
+        <v>2570.3115814226921</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="0"/>
+        <v>7457.1428571428569</v>
+      </c>
+      <c r="G3" s="8">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H3" s="8">
+        <v>2570.3115814226921</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I13" si="1">SUM(G3:H3)</f>
+        <v>7457.1428571428569</v>
+      </c>
+      <c r="J3">
+        <v>12000</v>
+      </c>
+      <c r="K3">
+        <v>27.142857142857157</v>
+      </c>
+      <c r="L3">
+        <v>27.142857142857157</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:M13" si="2">C3*E3</f>
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ref="N3:N13" si="3">C3*H3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A4" s="12">
+        <v>45809</v>
+      </c>
+      <c r="B4">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="C4">
+        <v>1.4613947368421052</v>
+      </c>
+      <c r="D4">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="E4">
+        <v>9627.4544385655499</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>14514.285714285714</v>
+      </c>
+      <c r="G4" s="8">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H4" s="8">
+        <v>9627.4544385655499</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="1"/>
+        <v>14514.285714285714</v>
+      </c>
+      <c r="J4">
+        <v>9828.5714285714294</v>
+      </c>
+      <c r="K4">
+        <v>261.42857142857139</v>
+      </c>
+      <c r="L4">
+        <v>261.42857142857139</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="2"/>
+        <v>14069.511245706859</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="3"/>
+        <v>14069.511245706859</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A5" s="12">
+        <v>45839</v>
+      </c>
+      <c r="B5">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="C5">
+        <v>0.97426315789473683</v>
+      </c>
+      <c r="D5">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="E5">
+        <v>7341.7401528512646</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>12228.571428571429</v>
+      </c>
+      <c r="G5" s="8">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H5">
+        <v>7341.7401528512646</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="1"/>
+        <v>12228.571428571429</v>
+      </c>
+      <c r="J5">
+        <v>12457.142857142857</v>
+      </c>
+      <c r="K5">
+        <v>249.99999999999991</v>
+      </c>
+      <c r="L5">
+        <v>249.99999999999991</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="2"/>
+        <v>7152.7869457594607</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="3"/>
+        <v>7152.7869457594607</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A6" s="12">
+        <v>45870</v>
+      </c>
+      <c r="B6">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="C6">
+        <v>0.97426315789473683</v>
+      </c>
+      <c r="D6">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="E6">
+        <v>7341.7401528512646</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>12228.571428571429</v>
+      </c>
+      <c r="G6" s="8">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H6">
+        <v>15000</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>19886.831275720164</v>
+      </c>
+      <c r="J6">
+        <v>12657.142857142857</v>
+      </c>
+      <c r="K6">
+        <v>228.57142857142856</v>
+      </c>
+      <c r="L6">
+        <v>611.48442092886535</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="2"/>
+        <v>7152.7869457594607</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="3"/>
+        <v>14613.947368421052</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A7" s="12">
+        <v>45901</v>
+      </c>
+      <c r="B7">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="C7">
+        <v>0.32475657894736842</v>
+      </c>
+      <c r="D7">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="E7">
+        <v>4456.0258671369784</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>9342.8571428571431</v>
+      </c>
+      <c r="G7" s="8">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H7">
+        <v>15000</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="1"/>
+        <v>19886.831275720164</v>
+      </c>
+      <c r="J7">
+        <v>12000</v>
+      </c>
+      <c r="K7">
+        <v>95.714285714285694</v>
+      </c>
+      <c r="L7">
+        <v>1005.8259847148737</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="2"/>
+        <v>1447.123716312386</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="3"/>
+        <v>4871.3486842105267</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A8" s="12">
+        <v>45931</v>
+      </c>
+      <c r="B8">
+        <v>1.7219534883720931</v>
+      </c>
+      <c r="C8">
+        <v>1.7219534883720931</v>
+      </c>
+      <c r="D8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="E8">
+        <v>10546.924603174602</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>13314.285714285714</v>
+      </c>
+      <c r="G8" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H8">
+        <v>15000</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="1"/>
+        <v>17767.361111111109</v>
+      </c>
+      <c r="J8">
+        <v>11714.285714285714</v>
+      </c>
+      <c r="K8">
+        <v>175.71428571428569</v>
+      </c>
+      <c r="L8">
+        <v>1308.4797545561435</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="2"/>
+        <v>18161.313612033959</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="3"/>
+        <v>25829.302325581397</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A9" s="12">
+        <v>45962</v>
+      </c>
+      <c r="B9">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="C9">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="D9">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="E9">
+        <v>7346.9246031746025</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>10114.285714285714</v>
+      </c>
+      <c r="G9" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H9">
+        <v>3088.8718871251899</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="1"/>
+        <v>5856.2329982363008</v>
+      </c>
+      <c r="J9">
+        <v>9342.8571428571431</v>
+      </c>
+      <c r="K9">
+        <v>214.28571428571422</v>
+      </c>
+      <c r="L9">
+        <v>1134.1485473251014</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="2"/>
+        <v>12639.892311851394</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="3"/>
+        <v>5314.1974536525295</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A10" s="12">
+        <v>45992</v>
+      </c>
+      <c r="B10">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="C10">
+        <v>2.2939030624099632</v>
+      </c>
+      <c r="D10">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="E10">
+        <v>6461.210317460318</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>9228.5714285714294</v>
+      </c>
+      <c r="G10" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="1"/>
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="J10">
+        <v>9085.7142857142862</v>
+      </c>
+      <c r="K10">
+        <v>221.42857142857139</v>
+      </c>
+      <c r="L10">
+        <v>818.2308885949426</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="2"/>
+        <v>14821.390134097073</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A11" s="12">
+        <v>46023</v>
+      </c>
+      <c r="B11">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="C11">
+        <v>0.28673497839118917</v>
+      </c>
+      <c r="D11">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="E11">
+        <v>3404.0674603174602</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>6171.4285714285716</v>
+      </c>
+      <c r="G11" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="1"/>
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="J11">
+        <v>9028.5714285714294</v>
+      </c>
+      <c r="K11">
+        <v>78.571428571428541</v>
+      </c>
+      <c r="L11">
+        <v>505.17037272192675</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="2"/>
+        <v>976.06520967627716</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A12" s="12">
+        <v>46054</v>
+      </c>
+      <c r="B12">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="C12">
+        <v>1.4336865095961708</v>
+      </c>
+      <c r="D12">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="E12">
+        <v>4975.4960317460318</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>7742.8571428571431</v>
+      </c>
+      <c r="G12" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="1"/>
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="J12">
+        <v>7685.7142857142853</v>
+      </c>
+      <c r="K12">
+        <v>81.428571428571431</v>
+      </c>
+      <c r="L12">
+        <v>259.25271399176808</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="2"/>
+        <v>7133.3015392635671</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A13" s="12">
+        <v>46082</v>
+      </c>
+      <c r="B13">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="C13">
+        <v>1.1469515312049816</v>
+      </c>
+      <c r="D13">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="E13">
+        <v>4918.353174603174</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>7685.7142857142853</v>
+      </c>
+      <c r="G13" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="1"/>
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="J13">
+        <v>7571.4285714285716</v>
+      </c>
+      <c r="K13">
+        <v>87.14285714285711</v>
+      </c>
+      <c r="L13">
+        <v>19.049340975895031</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="2"/>
+        <v>5641.1127046179927</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O17"/>
@@ -28323,6 +28966,4952 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F75FA8C-1640-AC43-9301-03E3B0E9069F}">
+  <dimension ref="A2:U220"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B2" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="2:18" s="15" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="B3" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B4" s="14">
+        <v>45748</v>
+      </c>
+      <c r="C4">
+        <v>504</v>
+      </c>
+      <c r="D4" s="8">
+        <v>35</v>
+      </c>
+      <c r="E4">
+        <f>C4*1000/D4</f>
+        <v>14400</v>
+      </c>
+      <c r="F4">
+        <v>1.5288157894736842</v>
+      </c>
+      <c r="G4">
+        <v>1.4112105263157895</v>
+      </c>
+      <c r="H4" s="16">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I4">
+        <f>E4-H4</f>
+        <v>9513.1687242798362</v>
+      </c>
+      <c r="J4">
+        <f>F4*H4</f>
+        <v>7471.0648148148148</v>
+      </c>
+      <c r="K4">
+        <f>G4*I4</f>
+        <v>13425.083842321856</v>
+      </c>
+      <c r="L4">
+        <f>SUM(J4:K4)</f>
+        <v>20896.148657136669</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B5" s="14">
+        <v>45778</v>
+      </c>
+      <c r="C5">
+        <v>261</v>
+      </c>
+      <c r="D5" s="8">
+        <v>35</v>
+      </c>
+      <c r="E5">
+        <f t="shared" ref="E5:E15" si="0">C5*1000/D5</f>
+        <v>7457.1428571428569</v>
+      </c>
+      <c r="F5">
+        <v>1.5806907894736841</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="16">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I5">
+        <f t="shared" ref="I5:I15" si="1">E5-H5</f>
+        <v>2570.3115814226921</v>
+      </c>
+      <c r="J5">
+        <f t="shared" ref="J5:K15" si="2">F5*H5</f>
+        <v>7724.5691872427979</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <f t="shared" ref="L5:L16" si="3">SUM(J5:K5)</f>
+        <v>7724.5691872427979</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B6" s="14">
+        <v>45809</v>
+      </c>
+      <c r="C6">
+        <v>508</v>
+      </c>
+      <c r="D6" s="8">
+        <v>35</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>14514.285714285714</v>
+      </c>
+      <c r="F6">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="G6">
+        <v>1.4613947368421052</v>
+      </c>
+      <c r="H6" s="16">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>9627.4544385655499</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="2"/>
+        <v>7935.0887345679021</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="2"/>
+        <v>14069.511245706859</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="3"/>
+        <v>22004.599980274761</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B7" s="14">
+        <v>45839</v>
+      </c>
+      <c r="C7">
+        <v>428</v>
+      </c>
+      <c r="D7" s="8">
+        <v>35</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>12228.571428571429</v>
+      </c>
+      <c r="F7">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="G7">
+        <v>0.97426315789473683</v>
+      </c>
+      <c r="H7" s="16">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="1"/>
+        <v>7341.7401528512646</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="2"/>
+        <v>7935.0887345679021</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="2"/>
+        <v>7152.7869457594607</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="3"/>
+        <v>15087.875680327363</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B8" s="14">
+        <v>45870</v>
+      </c>
+      <c r="C8">
+        <v>428</v>
+      </c>
+      <c r="D8" s="8">
+        <v>35</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>12228.571428571429</v>
+      </c>
+      <c r="F8">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="G8">
+        <v>0.97426315789473683</v>
+      </c>
+      <c r="H8" s="16">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="1"/>
+        <v>7341.7401528512646</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="2"/>
+        <v>7935.0887345679021</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="2"/>
+        <v>7152.7869457594607</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="3"/>
+        <v>15087.875680327363</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B9" s="14">
+        <v>45901</v>
+      </c>
+      <c r="C9">
+        <v>327</v>
+      </c>
+      <c r="D9" s="8">
+        <v>35</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>9342.8571428571431</v>
+      </c>
+      <c r="F9">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="G9">
+        <v>0.32475657894736842</v>
+      </c>
+      <c r="H9" s="16">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="1"/>
+        <v>4456.0258671369784</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="2"/>
+        <v>7935.0887345679021</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="2"/>
+        <v>1447.123716312386</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="3"/>
+        <v>9382.2124508802881</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B10" s="14">
+        <v>45931</v>
+      </c>
+      <c r="C10">
+        <v>466</v>
+      </c>
+      <c r="D10" s="8">
+        <v>35</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>13314.285714285714</v>
+      </c>
+      <c r="F10">
+        <v>1.7219534883720931</v>
+      </c>
+      <c r="G10">
+        <v>1.7219534883720931</v>
+      </c>
+      <c r="H10" s="16">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="1"/>
+        <v>10546.924603174602</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="2"/>
+        <v>4765.2671188630493</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="2"/>
+        <v>18161.313612033959</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="3"/>
+        <v>22926.580730897007</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B11" s="14">
+        <v>45962</v>
+      </c>
+      <c r="C11">
+        <v>354</v>
+      </c>
+      <c r="D11" s="8">
+        <v>35</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>10114.285714285714</v>
+      </c>
+      <c r="F11">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="G11">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="H11" s="16">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="1"/>
+        <v>7346.9246031746025</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="2"/>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="2"/>
+        <v>12639.892311851394</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="3"/>
+        <v>17400.951982633287</v>
+      </c>
+      <c r="P11" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>82</v>
+      </c>
+      <c r="R11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B12" s="14">
+        <v>45992</v>
+      </c>
+      <c r="C12">
+        <v>323</v>
+      </c>
+      <c r="D12" s="8">
+        <v>35</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>9228.5714285714294</v>
+      </c>
+      <c r="F12">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="G12">
+        <v>2.2939030624099632</v>
+      </c>
+      <c r="H12" s="16">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="1"/>
+        <v>6461.210317460318</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="2"/>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="2"/>
+        <v>14821.390134097073</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="3"/>
+        <v>19582.449804878968</v>
+      </c>
+      <c r="O12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P12">
+        <f>J16</f>
+        <v>75506.554413101723</v>
+      </c>
+      <c r="Q12">
+        <f>J34</f>
+        <v>75506.554413101723</v>
+      </c>
+      <c r="R12">
+        <f>100*(P12- Q12)/P12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B13" s="14">
+        <v>46023</v>
+      </c>
+      <c r="C13">
+        <v>216</v>
+      </c>
+      <c r="D13" s="8">
+        <v>35</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>6171.4285714285716</v>
+      </c>
+      <c r="F13">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="G13">
+        <v>0.28673497839118917</v>
+      </c>
+      <c r="H13" s="16">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="1"/>
+        <v>3404.0674603174602</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="2"/>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="2"/>
+        <v>976.06520967627716</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="3"/>
+        <v>5737.1248804581701</v>
+      </c>
+      <c r="O13" t="s">
+        <v>22</v>
+      </c>
+      <c r="P13">
+        <f>K16</f>
+        <v>102620.3682074003</v>
+      </c>
+      <c r="Q13">
+        <f>K34</f>
+        <v>80046.981272059056</v>
+      </c>
+      <c r="R13">
+        <f t="shared" ref="R13:R16" si="4">100*(P13- Q13)/P13</f>
+        <v>21.996984935504649</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B14" s="14">
+        <v>46054</v>
+      </c>
+      <c r="C14">
+        <v>271</v>
+      </c>
+      <c r="D14" s="8">
+        <v>35</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>7742.8571428571431</v>
+      </c>
+      <c r="F14">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="G14">
+        <v>1.4336865095961708</v>
+      </c>
+      <c r="H14" s="16">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="1"/>
+        <v>4975.4960317460318</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="2"/>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="2"/>
+        <v>7133.3015392635671</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="3"/>
+        <v>11894.361210045459</v>
+      </c>
+      <c r="O14" t="s">
+        <v>42</v>
+      </c>
+      <c r="P14">
+        <f>L51</f>
+        <v>1975.7142857142853</v>
+      </c>
+      <c r="Q14">
+        <f>M51</f>
+        <v>-6271.3727227715071</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="4"/>
+        <v>417.42305899783486</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B15" s="14">
+        <v>46082</v>
+      </c>
+      <c r="C15">
+        <v>269</v>
+      </c>
+      <c r="D15" s="8">
+        <v>35</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>7685.7142857142853</v>
+      </c>
+      <c r="F15">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="G15">
+        <v>1.1469515312049816</v>
+      </c>
+      <c r="H15" s="16">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="1"/>
+        <v>4918.353174603174</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="2"/>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="2"/>
+        <v>5641.1127046179927</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="3"/>
+        <v>10402.172375399885</v>
+      </c>
+      <c r="O15" t="s">
+        <v>83</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="I16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16">
+        <f>SUM(J4:J15)</f>
+        <v>75506.554413101723</v>
+      </c>
+      <c r="K16">
+        <f>SUM(K4:K15)</f>
+        <v>102620.3682074003</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="3"/>
+        <v>178126.92262050201</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P16">
+        <f>SUM(P12:P15)</f>
+        <v>180102.6369062163</v>
+      </c>
+      <c r="Q16">
+        <f>SUM(Q12:Q15)</f>
+        <v>149282.16296238927</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="4"/>
+        <v>17.112727760824502</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B20" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="P20">
+        <f>SUM(P12:P13)</f>
+        <v>178126.92262050201</v>
+      </c>
+      <c r="Q20">
+        <f>SUM(Q12:Q13)</f>
+        <v>155553.53568516078</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" ht="32" x14ac:dyDescent="0.2">
+      <c r="B21" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="M21" s="15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B22" s="14">
+        <v>45748</v>
+      </c>
+      <c r="C22">
+        <v>504</v>
+      </c>
+      <c r="D22" s="8">
+        <v>35</v>
+      </c>
+      <c r="E22">
+        <f>C22*1000/D22</f>
+        <v>14400</v>
+      </c>
+      <c r="F22">
+        <v>1.5288157894736842</v>
+      </c>
+      <c r="G22">
+        <v>1.4112105263157895</v>
+      </c>
+      <c r="H22" s="16">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I22" s="21">
+        <v>1.5315918917635199E-7</v>
+      </c>
+      <c r="J22">
+        <f>F22*H22</f>
+        <v>7471.0648148148148</v>
+      </c>
+      <c r="K22">
+        <f>G22*I22</f>
+        <v>2.1613985996765927E-7</v>
+      </c>
+      <c r="L22">
+        <f>SUM(J22:K22)</f>
+        <v>7471.0648150309544</v>
+      </c>
+      <c r="M22" s="16">
+        <f>SUM(H22:I22)</f>
+        <v>4886.8312758733236</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B23" s="14">
+        <v>45778</v>
+      </c>
+      <c r="C23">
+        <v>261</v>
+      </c>
+      <c r="D23" s="8">
+        <v>35</v>
+      </c>
+      <c r="E23">
+        <f t="shared" ref="E23:E33" si="5">C23*1000/D23</f>
+        <v>7457.1428571428569</v>
+      </c>
+      <c r="F23">
+        <v>1.5806907894736841</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" s="16">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I23">
+        <v>540.62315869746203</v>
+      </c>
+      <c r="J23">
+        <f t="shared" ref="J23:J33" si="6">F23*H23</f>
+        <v>7724.5691872427979</v>
+      </c>
+      <c r="K23">
+        <f>G23*I23</f>
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <f t="shared" ref="L23:L34" si="7">SUM(J23:K23)</f>
+        <v>7724.5691872427979</v>
+      </c>
+      <c r="M23" s="16">
+        <f>SUM(H23:I23)</f>
+        <v>5427.4544344176265</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B24" s="14">
+        <v>45809</v>
+      </c>
+      <c r="C24">
+        <v>508</v>
+      </c>
+      <c r="D24" s="8">
+        <v>35</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="5"/>
+        <v>14514.285714285714</v>
+      </c>
+      <c r="F24">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="G24">
+        <v>1.4613947368421052</v>
+      </c>
+      <c r="H24" s="16">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I24">
+        <v>4941.7401532788099</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="6"/>
+        <v>7935.0887345679021</v>
+      </c>
+      <c r="K24">
+        <f>G24*I24</f>
+        <v>7221.8330508429508</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="7"/>
+        <v>15156.921785410854</v>
+      </c>
+      <c r="M24" s="16">
+        <f>SUM(H24:I24)</f>
+        <v>9828.5714289989737</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B25" s="14">
+        <v>45839</v>
+      </c>
+      <c r="C25">
+        <v>428</v>
+      </c>
+      <c r="D25" s="8">
+        <v>35</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="5"/>
+        <v>12228.571428571429</v>
+      </c>
+      <c r="F25">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="G25">
+        <v>0.97426315789473683</v>
+      </c>
+      <c r="H25" s="16">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I25">
+        <v>7570.3115841096997</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="6"/>
+        <v>7935.0887345679021</v>
+      </c>
+      <c r="K25">
+        <f>G25*I25</f>
+        <v>7375.4756701818233</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="7"/>
+        <v>15310.564404749726</v>
+      </c>
+      <c r="M25" s="16">
+        <f>SUM(H25:I25)</f>
+        <v>12457.142859829864</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B26" s="14">
+        <v>45870</v>
+      </c>
+      <c r="C26">
+        <v>428</v>
+      </c>
+      <c r="D26" s="8">
+        <v>35</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="5"/>
+        <v>12228.571428571429</v>
+      </c>
+      <c r="F26">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="G26">
+        <v>0.97426315789473683</v>
+      </c>
+      <c r="H26" s="16">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I26">
+        <v>7770.31158376848</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="6"/>
+        <v>7935.0887345679021</v>
+      </c>
+      <c r="K26">
+        <f>G26*I26</f>
+        <v>7570.3283014283334</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="7"/>
+        <v>15505.417035996235</v>
+      </c>
+      <c r="M26" s="16">
+        <f>SUM(H26:I26)</f>
+        <v>12657.142859488646</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B27" s="14">
+        <v>45901</v>
+      </c>
+      <c r="C27">
+        <v>327</v>
+      </c>
+      <c r="D27" s="8">
+        <v>35</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="5"/>
+        <v>9342.8571428571431</v>
+      </c>
+      <c r="F27">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="G27">
+        <v>0.32475657894736842</v>
+      </c>
+      <c r="H27" s="16">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I27">
+        <v>7113.1687245564199</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="6"/>
+        <v>7935.0887345679021</v>
+      </c>
+      <c r="K27">
+        <f>G27*I27</f>
+        <v>2310.0483404623587</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="7"/>
+        <v>10245.137075030261</v>
+      </c>
+      <c r="M27" s="16">
+        <f>SUM(H27:I27)</f>
+        <v>12000.000000276585</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B28" s="14">
+        <v>45931</v>
+      </c>
+      <c r="C28">
+        <v>466</v>
+      </c>
+      <c r="D28" s="8">
+        <v>35</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="5"/>
+        <v>13314.285714285714</v>
+      </c>
+      <c r="F28">
+        <v>1.7219534883720931</v>
+      </c>
+      <c r="G28">
+        <v>1.7219534883720931</v>
+      </c>
+      <c r="H28" s="16">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I28">
+        <v>8946.9245984865192</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="6"/>
+        <v>4765.2671188630493</v>
+      </c>
+      <c r="K28">
+        <f>G28*I28</f>
+        <v>15406.18802256595</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="7"/>
+        <v>20171.455141429</v>
+      </c>
+      <c r="M28" s="16">
+        <f>SUM(H28:I28)</f>
+        <v>11714.285709597631</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B29" s="14">
+        <v>45962</v>
+      </c>
+      <c r="C29">
+        <v>354</v>
+      </c>
+      <c r="D29" s="8">
+        <v>35</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="5"/>
+        <v>10114.285714285714</v>
+      </c>
+      <c r="F29">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="G29">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="H29" s="16">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I29">
+        <v>6575.4960321840599</v>
+      </c>
+      <c r="J29">
+        <f>F29*H29</f>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K29">
+        <f>G29*I29</f>
+        <v>11312.701059692285</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="7"/>
+        <v>16073.760730474178</v>
+      </c>
+      <c r="M29" s="16">
+        <f>SUM(H29:I29)</f>
+        <v>9342.8571432951721</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B30" s="14">
+        <v>45992</v>
+      </c>
+      <c r="C30">
+        <v>323</v>
+      </c>
+      <c r="D30" s="8">
+        <v>35</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="5"/>
+        <v>9228.5714285714294</v>
+      </c>
+      <c r="F30">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="G30">
+        <v>2.2939030624099632</v>
+      </c>
+      <c r="H30" s="16">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I30">
+        <v>6318.3531745293103</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="6"/>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K30">
+        <f>G30*I30</f>
+        <v>14493.689696440499</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="7"/>
+        <v>19254.749367222394</v>
+      </c>
+      <c r="M30" s="16">
+        <f>SUM(H30:I30)</f>
+        <v>9085.7142856404207</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B31" s="14">
+        <v>46023</v>
+      </c>
+      <c r="C31">
+        <v>216</v>
+      </c>
+      <c r="D31" s="8">
+        <v>35</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="5"/>
+        <v>6171.4285714285716</v>
+      </c>
+      <c r="F31">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="G31">
+        <v>0.28673497839118917</v>
+      </c>
+      <c r="H31" s="16">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I31">
+        <v>6261.21031907623</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="6"/>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K31">
+        <f>G31*I31</f>
+        <v>1795.3080055430135</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="7"/>
+        <v>6556.3676763249068</v>
+      </c>
+      <c r="M31" s="16">
+        <f>SUM(H31:I31)</f>
+        <v>9028.5714301873413</v>
+      </c>
+      <c r="N31" s="21"/>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B32" s="14">
+        <v>46054</v>
+      </c>
+      <c r="C32">
+        <v>271</v>
+      </c>
+      <c r="D32" s="8">
+        <v>35</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="5"/>
+        <v>7742.8571428571431</v>
+      </c>
+      <c r="F32">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="G32">
+        <v>1.4336865095961708</v>
+      </c>
+      <c r="H32" s="16">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I32">
+        <v>4918.3531743943704</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="6"/>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K32">
+        <f>G32*I32</f>
+        <v>7051.3765955587114</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="7"/>
+        <v>11812.436266340605</v>
+      </c>
+      <c r="M32" s="16">
+        <f>SUM(H32:I32)</f>
+        <v>7685.7142855054817</v>
+      </c>
+      <c r="N32" s="21"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B33" s="14">
+        <v>46082</v>
+      </c>
+      <c r="C33">
+        <v>269</v>
+      </c>
+      <c r="D33" s="8">
+        <v>35</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="5"/>
+        <v>7685.7142857142853</v>
+      </c>
+      <c r="F33">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="G33">
+        <v>1.1469515312049816</v>
+      </c>
+      <c r="H33" s="16">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I33">
+        <v>4804.06745988488</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="6"/>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K33">
+        <f>G33*I33</f>
+        <v>5510.0325291269901</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="7"/>
+        <v>10271.092199908882</v>
+      </c>
+      <c r="M33" s="16">
+        <f>SUM(H33:I33)</f>
+        <v>7571.4285709959913</v>
+      </c>
+      <c r="N33" s="21"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="I34" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34">
+        <f>SUM(J22:J33)</f>
+        <v>75506.554413101723</v>
+      </c>
+      <c r="K34">
+        <f>SUM(K22:K33)</f>
+        <v>80046.981272059056</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="7"/>
+        <v>155553.53568516078</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="E37" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18" ht="32" x14ac:dyDescent="0.2">
+      <c r="B38" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G38" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="J38" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="K38" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="L38" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="M38" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="O38" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="P38" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>82</v>
+      </c>
+      <c r="R38" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B39" s="17">
+        <v>361</v>
+      </c>
+      <c r="C39" s="8">
+        <v>35</v>
+      </c>
+      <c r="E39">
+        <v>1000</v>
+      </c>
+      <c r="F39" s="14">
+        <v>45748</v>
+      </c>
+      <c r="G39">
+        <f>B39*1000/C39</f>
+        <v>10314.285714285714</v>
+      </c>
+      <c r="H39" s="16">
+        <f>SUM(H4:I4)</f>
+        <v>14400</v>
+      </c>
+      <c r="I39" s="16">
+        <f>H39-G39+E39</f>
+        <v>5085.7142857142862</v>
+      </c>
+      <c r="J39" s="22">
+        <f>M22</f>
+        <v>4886.8312758733236</v>
+      </c>
+      <c r="K39">
+        <f>E39+J39-G39</f>
+        <v>-4427.4544384123901</v>
+      </c>
+      <c r="L39">
+        <f>I39*0.05</f>
+        <v>254.28571428571433</v>
+      </c>
+      <c r="M39">
+        <f>K39*0.05</f>
+        <v>-221.37272192061951</v>
+      </c>
+      <c r="O39" t="s">
+        <v>21</v>
+      </c>
+      <c r="P39">
+        <v>75506.554413101723</v>
+      </c>
+      <c r="Q39">
+        <f>J70</f>
+        <v>75506.554413101723</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B40" s="17">
+        <v>420</v>
+      </c>
+      <c r="C40" s="8">
+        <v>35</v>
+      </c>
+      <c r="F40" s="14">
+        <v>45778</v>
+      </c>
+      <c r="G40">
+        <f t="shared" ref="G40:G49" si="8">B40*1000/C40</f>
+        <v>12000</v>
+      </c>
+      <c r="H40" s="16">
+        <f t="shared" ref="H40:H50" si="9">SUM(H5:I5)</f>
+        <v>7457.1428571428569</v>
+      </c>
+      <c r="I40" s="16">
+        <f>I39+H40-G40</f>
+        <v>542.85714285714312</v>
+      </c>
+      <c r="J40" s="22">
+        <f t="shared" ref="J40:J50" si="10">M23</f>
+        <v>5427.4544344176265</v>
+      </c>
+      <c r="K40">
+        <f>K39+J40-G40</f>
+        <v>-11000.000003994763</v>
+      </c>
+      <c r="L40">
+        <f t="shared" ref="L40:L50" si="11">I40*0.05</f>
+        <v>27.142857142857157</v>
+      </c>
+      <c r="M40">
+        <f t="shared" ref="M40:M50" si="12">K40*0.05</f>
+        <v>-550.00000019973811</v>
+      </c>
+      <c r="O40" t="s">
+        <v>22</v>
+      </c>
+      <c r="P40">
+        <v>102620.3682074003</v>
+      </c>
+      <c r="Q40">
+        <f>K70</f>
+        <v>86295.051536851184</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B41" s="17">
+        <v>344</v>
+      </c>
+      <c r="C41" s="8">
+        <v>35</v>
+      </c>
+      <c r="F41" s="14">
+        <v>45809</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="8"/>
+        <v>9828.5714285714294</v>
+      </c>
+      <c r="H41" s="16">
+        <f t="shared" si="9"/>
+        <v>14514.285714285714</v>
+      </c>
+      <c r="I41" s="16">
+        <f t="shared" ref="I41:I50" si="13">I40+H41-G41</f>
+        <v>5228.5714285714275</v>
+      </c>
+      <c r="J41" s="22">
+        <f t="shared" si="10"/>
+        <v>9828.5714289989737</v>
+      </c>
+      <c r="K41">
+        <f>K40+J41-G41</f>
+        <v>-11000.000003567218</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="11"/>
+        <v>261.42857142857139</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="12"/>
+        <v>-550.00000017836089</v>
+      </c>
+      <c r="O41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P41">
+        <v>1975.7142857142853</v>
+      </c>
+      <c r="Q41">
+        <f>P70</f>
+        <v>-1.4030861666469719E-5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B42" s="17">
+        <v>436</v>
+      </c>
+      <c r="C42" s="8">
+        <v>35</v>
+      </c>
+      <c r="F42" s="14">
+        <v>45839</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="8"/>
+        <v>12457.142857142857</v>
+      </c>
+      <c r="H42" s="16">
+        <f t="shared" si="9"/>
+        <v>12228.571428571429</v>
+      </c>
+      <c r="I42" s="16">
+        <f t="shared" si="13"/>
+        <v>4999.9999999999982</v>
+      </c>
+      <c r="J42" s="22">
+        <f t="shared" si="10"/>
+        <v>12457.142859829864</v>
+      </c>
+      <c r="K42">
+        <f t="shared" ref="K42:K50" si="14">K41+J42-G42</f>
+        <v>-11000.000000880211</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="11"/>
+        <v>249.99999999999991</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="12"/>
+        <v>-550.00000004401056</v>
+      </c>
+      <c r="O42" t="s">
+        <v>83</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B43" s="17">
+        <v>443</v>
+      </c>
+      <c r="C43" s="8">
+        <v>35</v>
+      </c>
+      <c r="F43" s="14">
+        <v>45870</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="8"/>
+        <v>12657.142857142857</v>
+      </c>
+      <c r="H43" s="16">
+        <f t="shared" si="9"/>
+        <v>12228.571428571429</v>
+      </c>
+      <c r="I43" s="16">
+        <f t="shared" si="13"/>
+        <v>4571.4285714285706</v>
+      </c>
+      <c r="J43" s="22">
+        <f t="shared" si="10"/>
+        <v>12657.142859488646</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="14"/>
+        <v>-10999.999998534422</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="11"/>
+        <v>228.57142857142856</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="12"/>
+        <v>-549.9999999267211</v>
+      </c>
+      <c r="O43" t="s">
+        <v>29</v>
+      </c>
+      <c r="P43">
+        <v>180102.6369062163</v>
+      </c>
+      <c r="Q43">
+        <f>SUM(Q39:Q42)</f>
+        <v>161801.60593592204</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B44" s="17">
+        <v>420</v>
+      </c>
+      <c r="C44" s="8">
+        <v>35</v>
+      </c>
+      <c r="F44" s="14">
+        <v>45901</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="8"/>
+        <v>12000</v>
+      </c>
+      <c r="H44" s="16">
+        <f t="shared" si="9"/>
+        <v>9342.8571428571431</v>
+      </c>
+      <c r="I44" s="16">
+        <f t="shared" si="13"/>
+        <v>1914.2857142857138</v>
+      </c>
+      <c r="J44" s="22">
+        <f t="shared" si="10"/>
+        <v>12000.000000276585</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="14"/>
+        <v>-10999.999998257837</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="11"/>
+        <v>95.714285714285694</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="12"/>
+        <v>-549.99999991289189</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B45" s="17">
+        <v>410</v>
+      </c>
+      <c r="C45" s="8">
+        <v>35</v>
+      </c>
+      <c r="F45" s="14">
+        <v>45931</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="8"/>
+        <v>11714.285714285714</v>
+      </c>
+      <c r="H45" s="16">
+        <f t="shared" si="9"/>
+        <v>13314.285714285714</v>
+      </c>
+      <c r="I45" s="16">
+        <f t="shared" si="13"/>
+        <v>3514.2857142857138</v>
+      </c>
+      <c r="J45" s="22">
+        <f t="shared" si="10"/>
+        <v>11714.285709597631</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="14"/>
+        <v>-11000.000002945921</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="11"/>
+        <v>175.71428571428569</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="12"/>
+        <v>-550.00000014729608</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B46" s="17">
+        <v>327</v>
+      </c>
+      <c r="C46" s="8">
+        <v>35</v>
+      </c>
+      <c r="F46" s="14">
+        <v>45962</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="8"/>
+        <v>9342.8571428571431</v>
+      </c>
+      <c r="H46" s="16">
+        <f t="shared" si="9"/>
+        <v>10114.285714285714</v>
+      </c>
+      <c r="I46" s="16">
+        <f t="shared" si="13"/>
+        <v>4285.7142857142844</v>
+      </c>
+      <c r="J46" s="22">
+        <f t="shared" si="10"/>
+        <v>9342.8571432951721</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="14"/>
+        <v>-11000.000002507892</v>
+      </c>
+      <c r="L46">
+        <f t="shared" si="11"/>
+        <v>214.28571428571422</v>
+      </c>
+      <c r="M46">
+        <f t="shared" si="12"/>
+        <v>-550.00000012539465</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B47" s="17">
+        <v>318</v>
+      </c>
+      <c r="C47" s="8">
+        <v>35</v>
+      </c>
+      <c r="F47" s="14">
+        <v>45992</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="8"/>
+        <v>9085.7142857142862</v>
+      </c>
+      <c r="H47" s="16">
+        <f t="shared" si="9"/>
+        <v>9228.5714285714294</v>
+      </c>
+      <c r="I47" s="16">
+        <f t="shared" si="13"/>
+        <v>4428.5714285714275</v>
+      </c>
+      <c r="J47" s="22">
+        <f t="shared" si="10"/>
+        <v>9085.7142856404207</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="14"/>
+        <v>-11000.000002581757</v>
+      </c>
+      <c r="L47">
+        <f t="shared" si="11"/>
+        <v>221.42857142857139</v>
+      </c>
+      <c r="M47">
+        <f t="shared" si="12"/>
+        <v>-550.00000012908788</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B48" s="17">
+        <v>316</v>
+      </c>
+      <c r="C48" s="8">
+        <v>35</v>
+      </c>
+      <c r="F48" s="14">
+        <v>46023</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="8"/>
+        <v>9028.5714285714294</v>
+      </c>
+      <c r="H48" s="16">
+        <f t="shared" si="9"/>
+        <v>6171.4285714285716</v>
+      </c>
+      <c r="I48" s="16">
+        <f t="shared" si="13"/>
+        <v>1571.4285714285706</v>
+      </c>
+      <c r="J48" s="22">
+        <f t="shared" si="10"/>
+        <v>9028.5714301873413</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="14"/>
+        <v>-11000.000000965845</v>
+      </c>
+      <c r="L48">
+        <f t="shared" si="11"/>
+        <v>78.571428571428541</v>
+      </c>
+      <c r="M48">
+        <f t="shared" si="12"/>
+        <v>-550.00000004829224</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B49" s="17">
+        <v>269</v>
+      </c>
+      <c r="C49" s="8">
+        <v>35</v>
+      </c>
+      <c r="F49" s="14">
+        <v>46054</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="8"/>
+        <v>7685.7142857142853</v>
+      </c>
+      <c r="H49" s="16">
+        <f t="shared" si="9"/>
+        <v>7742.8571428571431</v>
+      </c>
+      <c r="I49" s="16">
+        <f t="shared" si="13"/>
+        <v>1628.5714285714284</v>
+      </c>
+      <c r="J49" s="22">
+        <f t="shared" si="10"/>
+        <v>7685.7142855054817</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="14"/>
+        <v>-11000.000001174649</v>
+      </c>
+      <c r="L49">
+        <f t="shared" si="11"/>
+        <v>81.428571428571431</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="12"/>
+        <v>-550.00000005873244</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B50" s="17">
+        <v>265</v>
+      </c>
+      <c r="C50" s="8">
+        <v>35</v>
+      </c>
+      <c r="F50" s="14">
+        <v>46082</v>
+      </c>
+      <c r="G50">
+        <f>B50*1000/C50</f>
+        <v>7571.4285714285716</v>
+      </c>
+      <c r="H50" s="16">
+        <f t="shared" si="9"/>
+        <v>7685.7142857142853</v>
+      </c>
+      <c r="I50" s="16">
+        <f t="shared" si="13"/>
+        <v>1742.8571428571422</v>
+      </c>
+      <c r="J50" s="22">
+        <f t="shared" si="10"/>
+        <v>7571.4285709959913</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="14"/>
+        <v>-11000.00000160723</v>
+      </c>
+      <c r="L50">
+        <f t="shared" si="11"/>
+        <v>87.14285714285711</v>
+      </c>
+      <c r="M50">
+        <f t="shared" si="12"/>
+        <v>-550.00000008036147</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="K51" t="s">
+        <v>16</v>
+      </c>
+      <c r="L51">
+        <f>SUM(L39:L50)</f>
+        <v>1975.7142857142853</v>
+      </c>
+      <c r="M51">
+        <f>SUM(M39:M50)</f>
+        <v>-6271.3727227715071</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B56" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="B57" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E57" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F57" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G57" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H57" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="I57" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J57" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K57" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="L57" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="M57" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="N57" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="O57" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="P57" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>1000</v>
+      </c>
+      <c r="B58" s="14">
+        <v>45748</v>
+      </c>
+      <c r="C58">
+        <v>504</v>
+      </c>
+      <c r="D58" s="8">
+        <v>35</v>
+      </c>
+      <c r="E58">
+        <f>C58*1000/D58</f>
+        <v>14400</v>
+      </c>
+      <c r="F58">
+        <v>1.5288157894736842</v>
+      </c>
+      <c r="G58">
+        <v>1.4112105263157895</v>
+      </c>
+      <c r="H58" s="16">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I58" s="23">
+        <v>4427.4544299999998</v>
+      </c>
+      <c r="J58">
+        <f>F58*H58</f>
+        <v>7471.0648148148148</v>
+      </c>
+      <c r="K58">
+        <f>G58*I58</f>
+        <v>6248.0702963994736</v>
+      </c>
+      <c r="L58">
+        <f>SUM(J58:K58)</f>
+        <v>13719.135111214287</v>
+      </c>
+      <c r="M58" s="16">
+        <f>SUM(H58:I58)</f>
+        <v>9314.2857057201654</v>
+      </c>
+      <c r="O58" s="16">
+        <f>A58+M58-G39</f>
+        <v>-8.5655483417212963E-6</v>
+      </c>
+      <c r="P58">
+        <f>O58*0.05</f>
+        <v>-4.2827741708606482E-7</v>
+      </c>
+      <c r="R58" s="21">
+        <v>2.4889492989708898E-7</v>
+      </c>
+      <c r="S58" s="21">
+        <v>2.4889492989708898E-7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B59" s="14">
+        <v>45778</v>
+      </c>
+      <c r="C59">
+        <v>261</v>
+      </c>
+      <c r="D59" s="8">
+        <v>35</v>
+      </c>
+      <c r="E59">
+        <f t="shared" ref="E59:E69" si="15">C59*1000/D59</f>
+        <v>7457.1428571428569</v>
+      </c>
+      <c r="F59">
+        <v>1.5806907894736841</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59" s="16">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I59" s="23">
+        <v>7113.1687199999997</v>
+      </c>
+      <c r="J59">
+        <f t="shared" ref="J59:K69" si="16">F59*H59</f>
+        <v>7724.5691872427979</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <f t="shared" ref="L59:L70" si="17">SUM(J59:K59)</f>
+        <v>7724.5691872427979</v>
+      </c>
+      <c r="M59" s="16">
+        <f t="shared" ref="M59:M61" si="18">SUM(H59:I59)</f>
+        <v>11999.999995720165</v>
+      </c>
+      <c r="O59" s="16">
+        <f>O58+M59-G40</f>
+        <v>-1.2845383025705814E-5</v>
+      </c>
+      <c r="P59">
+        <f t="shared" ref="P59:P69" si="19">O59*0.05</f>
+        <v>-6.4226915128529074E-7</v>
+      </c>
+      <c r="R59">
+        <v>1040.6231586454401</v>
+      </c>
+      <c r="S59">
+        <v>1040.6231586454401</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B60" s="14">
+        <v>45809</v>
+      </c>
+      <c r="C60">
+        <v>508</v>
+      </c>
+      <c r="D60" s="8">
+        <v>35</v>
+      </c>
+      <c r="E60">
+        <f t="shared" si="15"/>
+        <v>14514.285714285714</v>
+      </c>
+      <c r="F60">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="G60">
+        <v>1.4613947368421052</v>
+      </c>
+      <c r="H60" s="16">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I60" s="23">
+        <v>4941.7401499999996</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="16"/>
+        <v>7935.0887345679021</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="16"/>
+        <v>7221.8330460513153</v>
+      </c>
+      <c r="L60">
+        <f t="shared" si="17"/>
+        <v>15156.921780619217</v>
+      </c>
+      <c r="M60" s="16">
+        <f t="shared" si="18"/>
+        <v>9828.5714257201653</v>
+      </c>
+      <c r="O60" s="16">
+        <f t="shared" ref="O60:O69" si="20">O59+M60-G41</f>
+        <v>-1.5696647096774541E-5</v>
+      </c>
+      <c r="P60">
+        <f t="shared" si="19"/>
+        <v>-7.8483235483872708E-7</v>
+      </c>
+      <c r="R60">
+        <v>4941.7401525896903</v>
+      </c>
+      <c r="S60">
+        <v>4941.7401525896903</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B61" s="14">
+        <v>45839</v>
+      </c>
+      <c r="C61">
+        <v>428</v>
+      </c>
+      <c r="D61" s="8">
+        <v>35</v>
+      </c>
+      <c r="E61">
+        <f t="shared" si="15"/>
+        <v>12228.571428571429</v>
+      </c>
+      <c r="F61">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="G61">
+        <v>0.97426315789473683</v>
+      </c>
+      <c r="H61" s="16">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I61" s="23">
+        <v>7570.3115799999996</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="16"/>
+        <v>7935.0887345679021</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="16"/>
+        <v>7375.4756661778947</v>
+      </c>
+      <c r="L61">
+        <f t="shared" si="17"/>
+        <v>15310.564400745796</v>
+      </c>
+      <c r="M61" s="16">
+        <f t="shared" si="18"/>
+        <v>12457.142855720165</v>
+      </c>
+      <c r="O61" s="16">
+        <f t="shared" si="20"/>
+        <v>-1.7119338735938072E-5</v>
+      </c>
+      <c r="P61">
+        <f t="shared" si="19"/>
+        <v>-8.5596693679690369E-7</v>
+      </c>
+      <c r="R61">
+        <v>7570.3115839435704</v>
+      </c>
+      <c r="S61">
+        <v>7570.3115839435704</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B62" s="14">
+        <v>45870</v>
+      </c>
+      <c r="C62">
+        <v>428</v>
+      </c>
+      <c r="D62" s="8">
+        <v>35</v>
+      </c>
+      <c r="E62">
+        <f t="shared" si="15"/>
+        <v>12228.571428571429</v>
+      </c>
+      <c r="F62">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="G62">
+        <v>0.97426315789473683</v>
+      </c>
+      <c r="H62" s="16">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I62" s="23">
+        <v>7770.3115799999996</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="16"/>
+        <v>7935.0887345679021</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="16"/>
+        <v>7570.3282977568415</v>
+      </c>
+      <c r="L62">
+        <f t="shared" si="17"/>
+        <v>15505.417032324744</v>
+      </c>
+      <c r="M62" s="16">
+        <f t="shared" ref="M62:M69" si="21">SUM(H62:I62)</f>
+        <v>12657.142855720165</v>
+      </c>
+      <c r="O62" s="16">
+        <f t="shared" si="20"/>
+        <v>-1.8542030375101604E-5</v>
+      </c>
+      <c r="P62">
+        <f t="shared" si="19"/>
+        <v>-9.271015187550802E-7</v>
+      </c>
+      <c r="R62">
+        <v>7770.3115839225802</v>
+      </c>
+      <c r="S62">
+        <v>7770.3115839225802</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B63" s="14">
+        <v>45901</v>
+      </c>
+      <c r="C63">
+        <v>327</v>
+      </c>
+      <c r="D63" s="8">
+        <v>35</v>
+      </c>
+      <c r="E63">
+        <f t="shared" si="15"/>
+        <v>9342.8571428571431</v>
+      </c>
+      <c r="F63">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="G63">
+        <v>0.32475657894736842</v>
+      </c>
+      <c r="H63" s="16">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I63" s="23">
+        <v>7113.1687199999997</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="16"/>
+        <v>7935.0887345679021</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="16"/>
+        <v>2310.0483389826313</v>
+      </c>
+      <c r="L63">
+        <f t="shared" si="17"/>
+        <v>10245.137073550533</v>
+      </c>
+      <c r="M63" s="16">
+        <f t="shared" si="21"/>
+        <v>11999.999995720165</v>
+      </c>
+      <c r="O63" s="16">
+        <f t="shared" si="20"/>
+        <v>-2.2821865059086122E-5</v>
+      </c>
+      <c r="P63">
+        <f t="shared" si="19"/>
+        <v>-1.1410932529543061E-6</v>
+      </c>
+      <c r="R63">
+        <v>7113.1687240479496</v>
+      </c>
+      <c r="S63">
+        <v>7113.1687240479496</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B64" s="14">
+        <v>45931</v>
+      </c>
+      <c r="C64">
+        <v>466</v>
+      </c>
+      <c r="D64" s="8">
+        <v>35</v>
+      </c>
+      <c r="E64">
+        <f t="shared" si="15"/>
+        <v>13314.285714285714</v>
+      </c>
+      <c r="F64">
+        <v>1.7219534883720931</v>
+      </c>
+      <c r="G64">
+        <v>1.7219534883720931</v>
+      </c>
+      <c r="H64" s="16">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I64" s="23">
+        <v>8946.9246000000003</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="16"/>
+        <v>4765.2671188630493</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="16"/>
+        <v>15406.188025172094</v>
+      </c>
+      <c r="L64">
+        <f t="shared" si="17"/>
+        <v>20171.455144035142</v>
+      </c>
+      <c r="M64" s="16">
+        <f t="shared" si="21"/>
+        <v>11714.285711111112</v>
+      </c>
+      <c r="O64" s="16">
+        <f t="shared" si="20"/>
+        <v>-2.5996467229560949E-5</v>
+      </c>
+      <c r="P64">
+        <f t="shared" si="19"/>
+        <v>-1.2998233614780476E-6</v>
+      </c>
+      <c r="R64">
+        <v>8946.9245989600804</v>
+      </c>
+      <c r="S64">
+        <v>8946.9245989600804</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B65" s="14">
+        <v>45962</v>
+      </c>
+      <c r="C65">
+        <v>354</v>
+      </c>
+      <c r="D65" s="8">
+        <v>35</v>
+      </c>
+      <c r="E65">
+        <f t="shared" si="15"/>
+        <v>10114.285714285714</v>
+      </c>
+      <c r="F65">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="G65">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="H65" s="16">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I65" s="23">
+        <v>6575.4960300000002</v>
+      </c>
+      <c r="J65">
+        <f>F65*H65</f>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="16"/>
+        <v>11312.701055934756</v>
+      </c>
+      <c r="L65">
+        <f t="shared" si="17"/>
+        <v>16073.76072671665</v>
+      </c>
+      <c r="M65" s="16">
+        <f t="shared" si="21"/>
+        <v>9342.8571411111116</v>
+      </c>
+      <c r="O65" s="16">
+        <f t="shared" si="20"/>
+        <v>-2.7742498787119985E-5</v>
+      </c>
+      <c r="P65">
+        <f t="shared" si="19"/>
+        <v>-1.3871249393559992E-6</v>
+      </c>
+      <c r="R65">
+        <v>6575.4960320465498</v>
+      </c>
+      <c r="S65">
+        <v>6575.4960320465498</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B66" s="14">
+        <v>45992</v>
+      </c>
+      <c r="C66">
+        <v>323</v>
+      </c>
+      <c r="D66" s="8">
+        <v>35</v>
+      </c>
+      <c r="E66">
+        <f t="shared" si="15"/>
+        <v>9228.5714285714294</v>
+      </c>
+      <c r="F66">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="G66">
+        <v>2.2939030624099632</v>
+      </c>
+      <c r="H66" s="16">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I66" s="23">
+        <v>6318.3531700000003</v>
+      </c>
+      <c r="J66">
+        <f t="shared" ref="J66:J69" si="22">F66*H66</f>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="16"/>
+        <v>14493.6896860507</v>
+      </c>
+      <c r="L66">
+        <f t="shared" si="17"/>
+        <v>19254.749356832595</v>
+      </c>
+      <c r="M66" s="16">
+        <f t="shared" si="21"/>
+        <v>9085.7142811111116</v>
+      </c>
+      <c r="O66" s="16">
+        <f t="shared" si="20"/>
+        <v>-3.2345673389500007E-5</v>
+      </c>
+      <c r="P66">
+        <f t="shared" si="19"/>
+        <v>-1.6172836694750005E-6</v>
+      </c>
+      <c r="R66">
+        <v>6318.3531747647503</v>
+      </c>
+      <c r="S66">
+        <v>6318.3531747647503</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B67" s="14">
+        <v>46023</v>
+      </c>
+      <c r="C67">
+        <v>216</v>
+      </c>
+      <c r="D67" s="8">
+        <v>35</v>
+      </c>
+      <c r="E67">
+        <f t="shared" si="15"/>
+        <v>6171.4285714285716</v>
+      </c>
+      <c r="F67">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="G67">
+        <v>0.28673497839118917</v>
+      </c>
+      <c r="H67" s="16">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I67" s="23">
+        <v>6261.2103200000001</v>
+      </c>
+      <c r="J67">
+        <f t="shared" si="22"/>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K67">
+        <f t="shared" si="16"/>
+        <v>1795.3080058078906</v>
+      </c>
+      <c r="L67">
+        <f t="shared" si="17"/>
+        <v>6556.3676765897835</v>
+      </c>
+      <c r="M67" s="16">
+        <f t="shared" si="21"/>
+        <v>9028.5714311111115</v>
+      </c>
+      <c r="O67" s="16">
+        <f t="shared" si="20"/>
+        <v>-2.9805991289322264E-5</v>
+      </c>
+      <c r="P67">
+        <f t="shared" si="19"/>
+        <v>-1.4902995644661134E-6</v>
+      </c>
+      <c r="R67">
+        <v>6261.2103181756202</v>
+      </c>
+      <c r="S67">
+        <v>6261.2103181756202</v>
+      </c>
+    </row>
+    <row r="68" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B68" s="14">
+        <v>46054</v>
+      </c>
+      <c r="C68">
+        <v>271</v>
+      </c>
+      <c r="D68" s="8">
+        <v>35</v>
+      </c>
+      <c r="E68">
+        <f t="shared" si="15"/>
+        <v>7742.8571428571431</v>
+      </c>
+      <c r="F68">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="G68">
+        <v>1.4336865095961708</v>
+      </c>
+      <c r="H68" s="16">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I68" s="23">
+        <v>4918.3531700000003</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="22"/>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="16"/>
+        <v>7051.3765892585625</v>
+      </c>
+      <c r="L68">
+        <f t="shared" si="17"/>
+        <v>11812.436260040457</v>
+      </c>
+      <c r="M68" s="16">
+        <f t="shared" si="21"/>
+        <v>7685.7142811111116</v>
+      </c>
+      <c r="O68" s="16">
+        <f t="shared" si="20"/>
+        <v>-3.4409164982207585E-5</v>
+      </c>
+      <c r="P68">
+        <f t="shared" si="19"/>
+        <v>-1.7204582491103793E-6</v>
+      </c>
+      <c r="R68">
+        <v>4918.3531750745196</v>
+      </c>
+      <c r="S68">
+        <v>4918.3531750745196</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B69" s="14">
+        <v>46082</v>
+      </c>
+      <c r="C69">
+        <v>269</v>
+      </c>
+      <c r="D69" s="8">
+        <v>35</v>
+      </c>
+      <c r="E69">
+        <f t="shared" si="15"/>
+        <v>7685.7142857142853</v>
+      </c>
+      <c r="F69">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="G69">
+        <v>1.1469515312049816</v>
+      </c>
+      <c r="H69" s="16">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I69" s="23">
+        <v>4804.0674600000002</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="22"/>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="16"/>
+        <v>5510.0325292590269</v>
+      </c>
+      <c r="L69">
+        <f t="shared" si="17"/>
+        <v>10271.092200040919</v>
+      </c>
+      <c r="M69" s="16">
+        <f t="shared" si="21"/>
+        <v>7571.4285711111115</v>
+      </c>
+      <c r="O69" s="16">
+        <f t="shared" si="20"/>
+        <v>-3.4726625017356128E-5</v>
+      </c>
+      <c r="P69">
+        <f t="shared" si="19"/>
+        <v>-1.7363312508678065E-6</v>
+      </c>
+      <c r="R69">
+        <v>4804.0674600945304</v>
+      </c>
+      <c r="S69">
+        <v>4804.0674600945304</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="I70" t="s">
+        <v>16</v>
+      </c>
+      <c r="J70">
+        <f>SUM(J58:J69)</f>
+        <v>75506.554413101723</v>
+      </c>
+      <c r="K70">
+        <f>SUM(K58:K69)</f>
+        <v>86295.051536851184</v>
+      </c>
+      <c r="L70">
+        <f t="shared" si="17"/>
+        <v>161801.60594995291</v>
+      </c>
+      <c r="P70" s="18">
+        <f>SUM(P58:P69)</f>
+        <v>-1.4030861666469719E-5</v>
+      </c>
+    </row>
+    <row r="129" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="J129" t="s">
+        <v>33</v>
+      </c>
+      <c r="K129" t="s">
+        <v>34</v>
+      </c>
+      <c r="L129" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="130" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="I130" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="J130">
+        <v>1316511.5530000001</v>
+      </c>
+      <c r="K130">
+        <v>765195</v>
+      </c>
+    </row>
+    <row r="131" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="I131" s="20"/>
+      <c r="J131">
+        <v>2116045</v>
+      </c>
+      <c r="K131">
+        <v>2116045</v>
+      </c>
+      <c r="L131">
+        <v>160216</v>
+      </c>
+    </row>
+    <row r="132" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="J132">
+        <f>SUM(J130:J131)</f>
+        <v>3432556.5530000003</v>
+      </c>
+      <c r="K132">
+        <f>SUM(K130:K131)</f>
+        <v>2881240</v>
+      </c>
+      <c r="L132">
+        <f>SUM(L131,K132)</f>
+        <v>3041456</v>
+      </c>
+    </row>
+    <row r="133" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="J133">
+        <v>3432556.5529999998</v>
+      </c>
+      <c r="K133">
+        <v>2881240</v>
+      </c>
+      <c r="L133">
+        <v>3041456</v>
+      </c>
+    </row>
+    <row r="135" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B135" t="s">
+        <v>26</v>
+      </c>
+      <c r="G135" t="s">
+        <v>35</v>
+      </c>
+      <c r="M135" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="136" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C136" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D136" s="8"/>
+      <c r="E136" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H136" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I136" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J136" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K136" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M136" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="N136" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="137" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B137" s="7">
+        <v>45772</v>
+      </c>
+      <c r="C137">
+        <v>1.5288157894736842</v>
+      </c>
+      <c r="E137">
+        <v>1.4112105263157895</v>
+      </c>
+      <c r="F137">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G137" s="8">
+        <v>4886.8312757201602</v>
+      </c>
+      <c r="H137" s="8">
+        <v>2483.1669423159556</v>
+      </c>
+      <c r="I137">
+        <f t="shared" ref="I137:I148" si="23">C137*F137*G137</f>
+        <v>232379.9999999998</v>
+      </c>
+      <c r="J137">
+        <f>E137*F137*H137</f>
+        <v>108996.8553735357</v>
+      </c>
+      <c r="K137">
+        <f>I137+J137</f>
+        <v>341376.85537353548</v>
+      </c>
+      <c r="L137" s="7">
+        <v>45772</v>
+      </c>
+      <c r="M137">
+        <f>J137</f>
+        <v>108996.8553735357</v>
+      </c>
+      <c r="N137">
+        <f>M153</f>
+        <v>108996.8553735357</v>
+      </c>
+    </row>
+    <row r="138" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B138" s="7">
+        <v>45802</v>
+      </c>
+      <c r="C138">
+        <v>1.5806907894736841</v>
+      </c>
+      <c r="E138">
+        <v>0</v>
+      </c>
+      <c r="F138">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G138" s="8">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H138" s="8">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <f t="shared" si="23"/>
+        <v>240264.99999999997</v>
+      </c>
+      <c r="J138">
+        <f t="shared" ref="J138:J148" si="24">E138*F138*H138</f>
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <f t="shared" ref="K138:K148" si="25">I138+J138</f>
+        <v>240264.99999999997</v>
+      </c>
+      <c r="L138" s="7">
+        <v>45802</v>
+      </c>
+      <c r="M138">
+        <f>M137+J138</f>
+        <v>108996.8553735357</v>
+      </c>
+      <c r="N138">
+        <f t="shared" ref="N138:N148" si="26">M154</f>
+        <v>108996.8553735357</v>
+      </c>
+    </row>
+    <row r="139" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B139" s="7">
+        <v>45833</v>
+      </c>
+      <c r="C139">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="E139">
+        <v>1.4613947368421052</v>
+      </c>
+      <c r="F139">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G139" s="8">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H139" s="8">
+        <v>2545.222790928924</v>
+      </c>
+      <c r="I139">
+        <f t="shared" si="23"/>
+        <v>246813</v>
+      </c>
+      <c r="J139">
+        <f t="shared" si="24"/>
+        <v>115693.66673321562</v>
+      </c>
+      <c r="K139">
+        <f t="shared" si="25"/>
+        <v>362506.66673321562</v>
+      </c>
+      <c r="L139" s="7">
+        <v>45833</v>
+      </c>
+      <c r="M139">
+        <f t="shared" ref="M139:M148" si="27">M138+J139</f>
+        <v>224690.52210675133</v>
+      </c>
+      <c r="N139">
+        <f t="shared" si="26"/>
+        <v>224690.52210675133</v>
+      </c>
+    </row>
+    <row r="140" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B140" s="7">
+        <v>45863</v>
+      </c>
+      <c r="C140">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="E140">
+        <v>0.97426315789473683</v>
+      </c>
+      <c r="F140">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G140" s="8">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H140" s="8">
+        <v>1371.7405698790662</v>
+      </c>
+      <c r="I140">
+        <f t="shared" si="23"/>
+        <v>246813</v>
+      </c>
+      <c r="J140">
+        <f t="shared" si="24"/>
+        <v>41568.514657243817</v>
+      </c>
+      <c r="K140">
+        <f t="shared" si="25"/>
+        <v>288381.5146572438</v>
+      </c>
+      <c r="L140" s="7">
+        <v>45863</v>
+      </c>
+      <c r="M140">
+        <f t="shared" si="27"/>
+        <v>266259.03676399513</v>
+      </c>
+      <c r="N140">
+        <f t="shared" si="26"/>
+        <v>415833.15958043491</v>
+      </c>
+    </row>
+    <row r="141" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B141" s="7">
+        <v>45894</v>
+      </c>
+      <c r="C141">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="E141">
+        <v>0.97426315789473683</v>
+      </c>
+      <c r="F141">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G141" s="8">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H141" s="8">
+        <v>1371.7405698790662</v>
+      </c>
+      <c r="I141">
+        <f t="shared" si="23"/>
+        <v>246813</v>
+      </c>
+      <c r="J141">
+        <f t="shared" si="24"/>
+        <v>41568.514657243817</v>
+      </c>
+      <c r="K141">
+        <f t="shared" si="25"/>
+        <v>288381.5146572438</v>
+      </c>
+      <c r="L141" s="7">
+        <v>45894</v>
+      </c>
+      <c r="M141">
+        <f t="shared" si="27"/>
+        <v>307827.55142123892</v>
+      </c>
+      <c r="N141">
+        <f t="shared" si="26"/>
+        <v>627957.52842254017</v>
+      </c>
+    </row>
+    <row r="142" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B142" s="7">
+        <v>45925</v>
+      </c>
+      <c r="C142">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="E142">
+        <v>0.32475657894736842</v>
+      </c>
+      <c r="F142">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G142" s="8">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H142" s="8">
+        <v>0</v>
+      </c>
+      <c r="I142">
+        <f t="shared" si="23"/>
+        <v>246813</v>
+      </c>
+      <c r="J142">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <f t="shared" si="25"/>
+        <v>246813</v>
+      </c>
+      <c r="L142" s="7">
+        <v>45925</v>
+      </c>
+      <c r="M142">
+        <f t="shared" si="27"/>
+        <v>307827.55142123892</v>
+      </c>
+      <c r="N142">
+        <f t="shared" si="26"/>
+        <v>627957.52842254017</v>
+      </c>
+    </row>
+    <row r="143" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B143" s="7">
+        <v>45955</v>
+      </c>
+      <c r="C143">
+        <v>1.7219534883720931</v>
+      </c>
+      <c r="E143">
+        <v>1.7219534883720931</v>
+      </c>
+      <c r="F143">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G143" s="8">
+        <v>2764.9176954732511</v>
+      </c>
+      <c r="H143" s="8">
+        <v>4045.6197993210399</v>
+      </c>
+      <c r="I143">
+        <f t="shared" si="23"/>
+        <v>148088</v>
+      </c>
+      <c r="J143">
+        <f t="shared" si="24"/>
+        <v>216681.9452972213</v>
+      </c>
+      <c r="K143">
+        <f t="shared" si="25"/>
+        <v>364769.9452972213</v>
+      </c>
+      <c r="L143" s="7">
+        <v>45955</v>
+      </c>
+      <c r="M143">
+        <f t="shared" si="27"/>
+        <v>524509.49671846023</v>
+      </c>
+      <c r="N143">
+        <f t="shared" si="26"/>
+        <v>627957.52842254017</v>
+      </c>
+    </row>
+    <row r="144" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B144" s="7">
+        <v>45986</v>
+      </c>
+      <c r="C144">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="E144">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="F144">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G144" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H144" s="8">
+        <v>2402.5977708842929</v>
+      </c>
+      <c r="I144">
+        <f t="shared" si="23"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="J144">
+        <f t="shared" si="24"/>
+        <v>128568.65599005947</v>
+      </c>
+      <c r="K144">
+        <f t="shared" si="25"/>
+        <v>276656.65599005949</v>
+      </c>
+      <c r="L144" s="7">
+        <v>45986</v>
+      </c>
+      <c r="M144">
+        <f t="shared" si="27"/>
+        <v>653078.15270851972</v>
+      </c>
+      <c r="N144">
+        <f t="shared" si="26"/>
+        <v>659262.465350062</v>
+      </c>
+    </row>
+    <row r="145" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B145" s="7">
+        <v>46016</v>
+      </c>
+      <c r="C145">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="E145">
+        <v>2.2939030624099632</v>
+      </c>
+      <c r="F145">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G145" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H145" s="8">
+        <v>1957.8353942526392</v>
+      </c>
+      <c r="I145">
+        <f t="shared" si="23"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="J145">
+        <f t="shared" si="24"/>
+        <v>139690.69560277648</v>
+      </c>
+      <c r="K145">
+        <f t="shared" si="25"/>
+        <v>287778.69560277648</v>
+      </c>
+      <c r="L145" s="7">
+        <v>46016</v>
+      </c>
+      <c r="M145">
+        <f t="shared" si="27"/>
+        <v>792768.8483112962</v>
+      </c>
+      <c r="N145">
+        <f t="shared" si="26"/>
+        <v>659262.465350062</v>
+      </c>
+    </row>
+    <row r="146" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B146" s="7">
+        <v>46047</v>
+      </c>
+      <c r="C146">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="E146">
+        <v>0.28673497839118917</v>
+      </c>
+      <c r="F146">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G146" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H146" s="8">
+        <v>384.25882680588074</v>
+      </c>
+      <c r="I146">
+        <f t="shared" si="23"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="J146">
+        <f t="shared" si="24"/>
+        <v>3427.052604850729</v>
+      </c>
+      <c r="K146">
+        <f t="shared" si="25"/>
+        <v>151515.05260485076</v>
+      </c>
+      <c r="L146" s="7">
+        <v>46047</v>
+      </c>
+      <c r="M146">
+        <f t="shared" si="27"/>
+        <v>796195.90091614693</v>
+      </c>
+      <c r="N146">
+        <f t="shared" si="26"/>
+        <v>659262.465350062</v>
+      </c>
+    </row>
+    <row r="147" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B147" s="7">
+        <v>46078</v>
+      </c>
+      <c r="C147">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="E147">
+        <v>1.4336865095961708</v>
+      </c>
+      <c r="F147">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G147" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H147" s="8">
+        <v>1188.9143226231608</v>
+      </c>
+      <c r="I147">
+        <f t="shared" si="23"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="J147">
+        <f t="shared" si="24"/>
+        <v>53017.714351968039</v>
+      </c>
+      <c r="K147">
+        <f t="shared" si="25"/>
+        <v>201105.71435196808</v>
+      </c>
+      <c r="L147" s="7">
+        <v>46078</v>
+      </c>
+      <c r="M147">
+        <f t="shared" si="27"/>
+        <v>849213.61526811495</v>
+      </c>
+      <c r="N147">
+        <f t="shared" si="26"/>
+        <v>659262.465350062</v>
+      </c>
+    </row>
+    <row r="148" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B148" s="7">
+        <v>46106</v>
+      </c>
+      <c r="C148">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="E148">
+        <v>1.1469515312049816</v>
+      </c>
+      <c r="F148">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G148" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H148" s="8">
+        <v>1166.5803075057843</v>
+      </c>
+      <c r="I148">
+        <f t="shared" si="23"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="J148">
+        <f t="shared" si="24"/>
+        <v>41617.496320264065</v>
+      </c>
+      <c r="K148">
+        <f t="shared" si="25"/>
+        <v>189705.49632026409</v>
+      </c>
+      <c r="L148" s="7">
+        <v>46106</v>
+      </c>
+      <c r="M148">
+        <f t="shared" si="27"/>
+        <v>890831.11158837902</v>
+      </c>
+      <c r="N148">
+        <f t="shared" si="26"/>
+        <v>659262.465350062</v>
+      </c>
+    </row>
+    <row r="149" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="G149">
+        <f>SUM(G137:G148)</f>
+        <v>45922.710905349777</v>
+      </c>
+      <c r="H149" s="8">
+        <f>SUM(H137:H148)</f>
+        <v>18917.677294395813</v>
+      </c>
+      <c r="I149" s="9">
+        <f>SUM(I137:I148)</f>
+        <v>2348425</v>
+      </c>
+      <c r="J149" s="9">
+        <f>SUM(J137:J148)</f>
+        <v>890831.11158837902</v>
+      </c>
+      <c r="K149" s="9">
+        <f>SUM(K137:K148)</f>
+        <v>3239256.1115883789</v>
+      </c>
+    </row>
+    <row r="150" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="J150">
+        <f>J149/H149</f>
+        <v>47.08987777544337</v>
+      </c>
+    </row>
+    <row r="151" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B151" t="s">
+        <v>26</v>
+      </c>
+      <c r="G151" t="s">
+        <v>36</v>
+      </c>
+      <c r="M151" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="152" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C152" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D152" s="8"/>
+      <c r="E152" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H152" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I152" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J152" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K152" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M152" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="153" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B153" s="7">
+        <v>45772</v>
+      </c>
+      <c r="C153">
+        <v>1.5288157894736842</v>
+      </c>
+      <c r="E153">
+        <v>1.4112105263157895</v>
+      </c>
+      <c r="F153">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G153" s="8">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H153" s="8">
+        <v>2483.1669423159556</v>
+      </c>
+      <c r="I153">
+        <f t="shared" ref="I153:I164" si="28">C153*F153*G153</f>
+        <v>232380</v>
+      </c>
+      <c r="J153">
+        <f>E153*F153*H153</f>
+        <v>108996.8553735357</v>
+      </c>
+      <c r="K153">
+        <f>I153+J153</f>
+        <v>341376.85537353571</v>
+      </c>
+      <c r="M153">
+        <f>J153</f>
+        <v>108996.8553735357</v>
+      </c>
+    </row>
+    <row r="154" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B154" s="7">
+        <v>45802</v>
+      </c>
+      <c r="C154">
+        <v>1.5806907894736841</v>
+      </c>
+      <c r="E154">
+        <v>0</v>
+      </c>
+      <c r="F154">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G154" s="8">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H154" s="8">
+        <v>0</v>
+      </c>
+      <c r="I154">
+        <f t="shared" si="28"/>
+        <v>240264.99999999997</v>
+      </c>
+      <c r="J154">
+        <f t="shared" ref="J154:J164" si="29">E154*F154*H154</f>
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <f t="shared" ref="K154:K164" si="30">I154+J154</f>
+        <v>240264.99999999997</v>
+      </c>
+      <c r="M154">
+        <f>M153+J154</f>
+        <v>108996.8553735357</v>
+      </c>
+      <c r="P154" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>78</v>
+      </c>
+      <c r="R154" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="155" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B155" s="7">
+        <v>45833</v>
+      </c>
+      <c r="C155">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="E155">
+        <v>1.4613947368421052</v>
+      </c>
+      <c r="F155">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G155" s="8">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H155" s="8">
+        <v>2545.222790928924</v>
+      </c>
+      <c r="I155">
+        <f t="shared" si="28"/>
+        <v>246813</v>
+      </c>
+      <c r="J155">
+        <f t="shared" si="29"/>
+        <v>115693.66673321562</v>
+      </c>
+      <c r="K155">
+        <f t="shared" si="30"/>
+        <v>362506.66673321562</v>
+      </c>
+      <c r="M155">
+        <f t="shared" ref="M155:M164" si="31">M154+J155</f>
+        <v>224690.52210675133</v>
+      </c>
+      <c r="P155">
+        <v>500</v>
+      </c>
+      <c r="Q155">
+        <f>35*31.104</f>
+        <v>1088.6399999999999</v>
+      </c>
+      <c r="R155">
+        <f>500000*31.104/Q155</f>
+        <v>14285.714285714288</v>
+      </c>
+    </row>
+    <row r="156" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B156" s="7">
+        <v>45863</v>
+      </c>
+      <c r="C156">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="E156">
+        <v>0.97426315789473683</v>
+      </c>
+      <c r="F156">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G156" s="8">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H156">
+        <v>6307.6131687242596</v>
+      </c>
+      <c r="I156">
+        <f t="shared" si="28"/>
+        <v>246813</v>
+      </c>
+      <c r="J156">
+        <f t="shared" si="29"/>
+        <v>191142.6374736836</v>
+      </c>
+      <c r="K156">
+        <f t="shared" si="30"/>
+        <v>437955.63747368357</v>
+      </c>
+      <c r="M156">
+        <f t="shared" si="31"/>
+        <v>415833.15958043491</v>
+      </c>
+    </row>
+    <row r="157" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B157" s="7">
+        <v>45894</v>
+      </c>
+      <c r="C157">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="E157">
+        <v>0.97426315789473683</v>
+      </c>
+      <c r="F157">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G157" s="8">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H157">
+        <v>7000</v>
+      </c>
+      <c r="I157">
+        <f t="shared" si="28"/>
+        <v>246813</v>
+      </c>
+      <c r="J157">
+        <f t="shared" si="29"/>
+        <v>212124.36884210526</v>
+      </c>
+      <c r="K157">
+        <f t="shared" si="30"/>
+        <v>458937.36884210526</v>
+      </c>
+      <c r="M157">
+        <f t="shared" si="31"/>
+        <v>627957.52842254017</v>
+      </c>
+    </row>
+    <row r="158" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B158" s="7">
+        <v>45925</v>
+      </c>
+      <c r="C158">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="E158">
+        <v>0.32475657894736842</v>
+      </c>
+      <c r="F158">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G158" s="8">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158">
+        <f t="shared" si="28"/>
+        <v>246813</v>
+      </c>
+      <c r="J158">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <f t="shared" si="30"/>
+        <v>246813</v>
+      </c>
+      <c r="M158">
+        <f t="shared" si="31"/>
+        <v>627957.52842254017</v>
+      </c>
+    </row>
+    <row r="159" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B159" s="7">
+        <v>45955</v>
+      </c>
+      <c r="C159">
+        <v>1.7219534883720931</v>
+      </c>
+      <c r="E159">
+        <v>1.7219534883720931</v>
+      </c>
+      <c r="F159">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G159" s="8">
+        <v>2764.9176954732511</v>
+      </c>
+      <c r="H159">
+        <v>0</v>
+      </c>
+      <c r="I159">
+        <f t="shared" si="28"/>
+        <v>148088</v>
+      </c>
+      <c r="J159">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <f t="shared" si="30"/>
+        <v>148088</v>
+      </c>
+      <c r="M159">
+        <f t="shared" si="31"/>
+        <v>627957.52842254017</v>
+      </c>
+    </row>
+    <row r="160" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B160" s="7">
+        <v>45986</v>
+      </c>
+      <c r="C160">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="E160">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="F160">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G160" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H160">
+        <v>585.00395061726795</v>
+      </c>
+      <c r="I160">
+        <f t="shared" si="28"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="J160">
+        <f t="shared" si="29"/>
+        <v>31304.936927521801</v>
+      </c>
+      <c r="K160">
+        <f t="shared" si="30"/>
+        <v>179392.93692752183</v>
+      </c>
+      <c r="M160">
+        <f t="shared" si="31"/>
+        <v>659262.465350062</v>
+      </c>
+    </row>
+    <row r="161" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B161" s="7">
+        <v>46016</v>
+      </c>
+      <c r="C161">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="E161">
+        <v>2.2939030624099632</v>
+      </c>
+      <c r="F161">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G161" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H161">
+        <v>0</v>
+      </c>
+      <c r="I161">
+        <f t="shared" si="28"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="J161">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <f t="shared" si="30"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="M161">
+        <f t="shared" si="31"/>
+        <v>659262.465350062</v>
+      </c>
+    </row>
+    <row r="162" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B162" s="7">
+        <v>46047</v>
+      </c>
+      <c r="C162">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="E162">
+        <v>0.28673497839118917</v>
+      </c>
+      <c r="F162">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G162" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H162">
+        <v>0</v>
+      </c>
+      <c r="I162">
+        <f t="shared" si="28"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="J162">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <f t="shared" si="30"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="M162">
+        <f t="shared" si="31"/>
+        <v>659262.465350062</v>
+      </c>
+    </row>
+    <row r="163" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B163" s="7">
+        <v>46078</v>
+      </c>
+      <c r="C163">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="E163">
+        <v>1.4336865095961708</v>
+      </c>
+      <c r="F163">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G163" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H163">
+        <v>0</v>
+      </c>
+      <c r="I163">
+        <f t="shared" si="28"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="J163">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <f t="shared" si="30"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="M163">
+        <f t="shared" si="31"/>
+        <v>659262.465350062</v>
+      </c>
+    </row>
+    <row r="164" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B164" s="7">
+        <v>46106</v>
+      </c>
+      <c r="C164">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="E164">
+        <v>1.1469515312049816</v>
+      </c>
+      <c r="F164">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G164" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+      <c r="I164">
+        <f t="shared" si="28"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="J164">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <f t="shared" si="30"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="M164">
+        <f t="shared" si="31"/>
+        <v>659262.465350062</v>
+      </c>
+    </row>
+    <row r="165" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="G165">
+        <f>SUM(G153:G164)</f>
+        <v>45922.710905349784</v>
+      </c>
+      <c r="H165">
+        <f>SUM(H153:H164)</f>
+        <v>18921.006852586408</v>
+      </c>
+      <c r="I165" s="9">
+        <f>SUM(I153:I164)</f>
+        <v>2348425</v>
+      </c>
+      <c r="J165" s="9">
+        <f>SUM(J153:J164)</f>
+        <v>659262.465350062</v>
+      </c>
+      <c r="K165" s="9">
+        <f>SUM(K153:K164)</f>
+        <v>3007687.4653500617</v>
+      </c>
+    </row>
+    <row r="166" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="J166">
+        <f>J165/H165</f>
+        <v>34.842884973636806</v>
+      </c>
+    </row>
+    <row r="168" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="G168" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="169" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="E169" t="s">
+        <v>61</v>
+      </c>
+      <c r="G169" t="s">
+        <v>39</v>
+      </c>
+      <c r="H169" t="s">
+        <v>40</v>
+      </c>
+      <c r="I169" t="s">
+        <v>41</v>
+      </c>
+      <c r="J169" t="s">
+        <v>43</v>
+      </c>
+      <c r="K169" t="s">
+        <v>42</v>
+      </c>
+      <c r="L169" t="s">
+        <v>45</v>
+      </c>
+      <c r="O169" t="s">
+        <v>49</v>
+      </c>
+      <c r="P169" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>42</v>
+      </c>
+      <c r="R169" t="s">
+        <v>50</v>
+      </c>
+      <c r="S169" t="s">
+        <v>54</v>
+      </c>
+      <c r="T169" t="s">
+        <v>52</v>
+      </c>
+      <c r="U169" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="170" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="E170">
+        <v>1242</v>
+      </c>
+      <c r="F170" s="7">
+        <v>45772</v>
+      </c>
+      <c r="G170">
+        <v>5195.1035206425595</v>
+      </c>
+      <c r="H170">
+        <v>7369.9982180361203</v>
+      </c>
+      <c r="I170">
+        <f>H170-G170+E170</f>
+        <v>3416.8946973935608</v>
+      </c>
+      <c r="J170">
+        <v>0.05</v>
+      </c>
+      <c r="K170">
+        <f t="shared" ref="K170:K181" si="32">I170*J170*L170</f>
+        <v>4271.1183717419517</v>
+      </c>
+      <c r="L170">
+        <v>25</v>
+      </c>
+      <c r="O170">
+        <v>446884</v>
+      </c>
+      <c r="P170">
+        <f>SUM(Q170:R170)</f>
+        <v>542281.50637903402</v>
+      </c>
+      <c r="Q170">
+        <v>2641.4609053497929</v>
+      </c>
+      <c r="R170">
+        <v>539640.04547368421</v>
+      </c>
+      <c r="S170" s="7">
+        <v>45772</v>
+      </c>
+      <c r="T170">
+        <f>O170</f>
+        <v>446884</v>
+      </c>
+      <c r="U170">
+        <f>P170</f>
+        <v>542281.50637903402</v>
+      </c>
+    </row>
+    <row r="171" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="F171" s="7">
+        <v>45802</v>
+      </c>
+      <c r="G171">
+        <v>5907.1382972953343</v>
+      </c>
+      <c r="H171">
+        <v>3813.8171728011271</v>
+      </c>
+      <c r="I171">
+        <f>I170+H171-G171</f>
+        <v>1323.5735728993532</v>
+      </c>
+      <c r="J171">
+        <v>0.05</v>
+      </c>
+      <c r="K171">
+        <f t="shared" si="32"/>
+        <v>1654.4669661241915</v>
+      </c>
+      <c r="L171">
+        <v>25</v>
+      </c>
+      <c r="O171">
+        <v>240264.99999999997</v>
+      </c>
+      <c r="P171">
+        <f t="shared" ref="P171:P181" si="33">SUM(Q171:R171)</f>
+        <v>251415.3343621399</v>
+      </c>
+      <c r="Q171">
+        <v>11150.334362139914</v>
+      </c>
+      <c r="R171">
+        <v>240264.99999999997</v>
+      </c>
+      <c r="S171" s="7">
+        <v>45802</v>
+      </c>
+      <c r="T171">
+        <f>O171+T170</f>
+        <v>687149</v>
+      </c>
+      <c r="U171">
+        <f>P171+U170</f>
+        <v>793696.84074117395</v>
+      </c>
+    </row>
+    <row r="172" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="F172" s="7">
+        <v>45833</v>
+      </c>
+      <c r="G172">
+        <v>5625.7573205650187</v>
+      </c>
+      <c r="H172">
+        <v>7432.0540666490888</v>
+      </c>
+      <c r="I172">
+        <f t="shared" ref="I172:I181" si="34">I171+H172-G172</f>
+        <v>3129.8703189834232</v>
+      </c>
+      <c r="J172">
+        <v>0.05</v>
+      </c>
+      <c r="K172">
+        <f t="shared" si="32"/>
+        <v>3912.3378987292795</v>
+      </c>
+      <c r="L172">
+        <v>25</v>
+      </c>
+      <c r="O172">
+        <v>474790.57894736843</v>
+      </c>
+      <c r="P172">
+        <f t="shared" si="33"/>
+        <v>578630.59750184091</v>
+      </c>
+      <c r="Q172">
+        <v>13631.044238683122</v>
+      </c>
+      <c r="R172">
+        <v>564999.55326315784</v>
+      </c>
+      <c r="S172" s="7">
+        <v>45833</v>
+      </c>
+      <c r="T172">
+        <f t="shared" ref="T172:U181" si="35">O172+T171</f>
+        <v>1161939.5789473685</v>
+      </c>
+      <c r="U172">
+        <f t="shared" si="35"/>
+        <v>1372327.4382430147</v>
+      </c>
+    </row>
+    <row r="173" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="F173" s="7">
+        <v>45863</v>
+      </c>
+      <c r="G173">
+        <v>6433.9826158977739</v>
+      </c>
+      <c r="H173">
+        <f t="shared" ref="H173:H181" si="36">SUM(G156:H156)</f>
+        <v>11194.444444444423</v>
+      </c>
+      <c r="I173">
+        <f t="shared" si="34"/>
+        <v>7890.3321475300727</v>
+      </c>
+      <c r="J173">
+        <v>0.05</v>
+      </c>
+      <c r="K173">
+        <f t="shared" si="32"/>
+        <v>9862.9151844125918</v>
+      </c>
+      <c r="L173">
+        <v>25</v>
+      </c>
+      <c r="O173">
+        <v>351059.15789473685</v>
+      </c>
+      <c r="P173">
+        <f t="shared" si="33"/>
+        <v>477018.32306021225</v>
+      </c>
+      <c r="Q173">
+        <v>18080.954218106992</v>
+      </c>
+      <c r="R173">
+        <v>458937.36884210526</v>
+      </c>
+      <c r="S173" s="7">
+        <v>45863</v>
+      </c>
+      <c r="T173">
+        <f t="shared" si="35"/>
+        <v>1512998.7368421054</v>
+      </c>
+      <c r="U173">
+        <f t="shared" si="35"/>
+        <v>1849345.7613032269</v>
+      </c>
+    </row>
+    <row r="174" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="F174" s="7">
+        <v>45894</v>
+      </c>
+      <c r="G174">
+        <v>6493.9081133646077</v>
+      </c>
+      <c r="H174">
+        <f t="shared" si="36"/>
+        <v>11886.831275720164</v>
+      </c>
+      <c r="I174">
+        <f t="shared" si="34"/>
+        <v>13283.25530988563</v>
+      </c>
+      <c r="J174">
+        <v>0.05</v>
+      </c>
+      <c r="K174">
+        <f t="shared" si="32"/>
+        <v>16604.069137357037</v>
+      </c>
+      <c r="L174">
+        <v>25</v>
+      </c>
+      <c r="O174">
+        <v>351059.15789473685</v>
+      </c>
+      <c r="P174">
+        <f t="shared" si="33"/>
+        <v>470674.47530300973</v>
+      </c>
+      <c r="Q174">
+        <v>22103.26646090531</v>
+      </c>
+      <c r="R174">
+        <v>448571.20884210442</v>
+      </c>
+      <c r="S174" s="7">
+        <v>45894</v>
+      </c>
+      <c r="T174">
+        <f t="shared" si="35"/>
+        <v>1864057.8947368423</v>
+      </c>
+      <c r="U174">
+        <f t="shared" si="35"/>
+        <v>2320020.2366062365</v>
+      </c>
+    </row>
+    <row r="175" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="F175" s="7">
+        <v>45925</v>
+      </c>
+      <c r="G175">
+        <v>6071.2326312903115</v>
+      </c>
+      <c r="H175">
+        <f t="shared" si="36"/>
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="I175">
+        <f t="shared" si="34"/>
+        <v>12098.853954315482</v>
+      </c>
+      <c r="J175">
+        <v>0.05</v>
+      </c>
+      <c r="K175">
+        <f t="shared" si="32"/>
+        <v>15123.567442894353</v>
+      </c>
+      <c r="L175">
+        <v>25</v>
+      </c>
+      <c r="O175">
+        <v>260452.77631578947</v>
+      </c>
+      <c r="P175">
+        <f t="shared" si="33"/>
+        <v>304452.67678642564</v>
+      </c>
+      <c r="Q175">
+        <v>24514.529012345633</v>
+      </c>
+      <c r="R175">
+        <v>279938.14777407999</v>
+      </c>
+      <c r="S175" s="7">
+        <v>45925</v>
+      </c>
+      <c r="T175">
+        <f t="shared" si="35"/>
+        <v>2124510.6710526319</v>
+      </c>
+      <c r="U175">
+        <f t="shared" si="35"/>
+        <v>2624472.9133926621</v>
+      </c>
+    </row>
+    <row r="176" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="F176" s="7">
+        <v>45955</v>
+      </c>
+      <c r="G176">
+        <v>6403.8158313631438</v>
+      </c>
+      <c r="H176">
+        <f t="shared" si="36"/>
+        <v>2764.9176954732511</v>
+      </c>
+      <c r="I176">
+        <f t="shared" si="34"/>
+        <v>8459.9558184255911</v>
+      </c>
+      <c r="J176">
+        <v>0.05</v>
+      </c>
+      <c r="K176">
+        <f t="shared" si="32"/>
+        <v>10574.94477303199</v>
+      </c>
+      <c r="L176">
+        <v>25</v>
+      </c>
+      <c r="O176">
+        <v>278956.46511627908</v>
+      </c>
+      <c r="P176">
+        <f t="shared" si="33"/>
+        <v>169548.25946502053</v>
+      </c>
+      <c r="Q176">
+        <v>21460.259465020532</v>
+      </c>
+      <c r="R176">
+        <v>148088</v>
+      </c>
+      <c r="S176" s="7">
+        <v>45955</v>
+      </c>
+      <c r="T176">
+        <f t="shared" si="35"/>
+        <v>2403467.1361689111</v>
+      </c>
+      <c r="U176">
+        <f t="shared" si="35"/>
+        <v>2794021.1728576827</v>
+      </c>
+    </row>
+    <row r="177" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F177" s="7">
+        <v>45986</v>
+      </c>
+      <c r="G177">
+        <v>6026.4848889003415</v>
+      </c>
+      <c r="H177">
+        <f t="shared" si="36"/>
+        <v>3352.3650617283793</v>
+      </c>
+      <c r="I177">
+        <f t="shared" si="34"/>
+        <v>5785.835991253628</v>
+      </c>
+      <c r="J177">
+        <v>0.05</v>
+      </c>
+      <c r="K177">
+        <f t="shared" si="32"/>
+        <v>7232.2949890670361</v>
+      </c>
+      <c r="L177">
+        <v>25</v>
+      </c>
+      <c r="O177">
+        <v>333764.02249175153</v>
+      </c>
+      <c r="P177">
+        <f t="shared" si="33"/>
+        <v>165211.03595679012</v>
+      </c>
+      <c r="Q177">
+        <v>17123.035956790081</v>
+      </c>
+      <c r="R177">
+        <v>148088.00000000003</v>
+      </c>
+      <c r="S177" s="7">
+        <v>45986</v>
+      </c>
+      <c r="T177">
+        <f t="shared" si="35"/>
+        <v>2737231.1586606628</v>
+      </c>
+      <c r="U177">
+        <f t="shared" si="35"/>
+        <v>2959232.2088144729</v>
+      </c>
+    </row>
+    <row r="178" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F178" s="7">
+        <v>46016</v>
+      </c>
+      <c r="G178">
+        <v>4479.7985738060161</v>
+      </c>
+      <c r="H178">
+        <f t="shared" si="36"/>
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I178">
+        <f t="shared" si="34"/>
+        <v>4073.3985285587223</v>
+      </c>
+      <c r="J178">
+        <v>0.05</v>
+      </c>
+      <c r="K178">
+        <f t="shared" si="32"/>
+        <v>5091.7481606984029</v>
+      </c>
+      <c r="L178">
+        <v>25</v>
+      </c>
+      <c r="O178">
+        <v>471353.99516706169</v>
+      </c>
+      <c r="P178">
+        <f t="shared" si="33"/>
+        <v>159547.61646090532</v>
+      </c>
+      <c r="Q178">
+        <v>11459.616460905305</v>
+      </c>
+      <c r="R178">
+        <v>148088.00000000003</v>
+      </c>
+      <c r="S178" s="7">
+        <v>46016</v>
+      </c>
+      <c r="T178">
+        <f t="shared" si="35"/>
+        <v>3208585.1538277245</v>
+      </c>
+      <c r="U178">
+        <f t="shared" si="35"/>
+        <v>3118779.8252753783</v>
+      </c>
+    </row>
+    <row r="179" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F179" s="7">
+        <v>46047</v>
+      </c>
+      <c r="G179">
+        <v>4284.164832400751</v>
+      </c>
+      <c r="H179">
+        <f t="shared" si="36"/>
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I179">
+        <f t="shared" si="34"/>
+        <v>2556.5948072690826</v>
+      </c>
+      <c r="J179">
+        <v>0.05</v>
+      </c>
+      <c r="K179">
+        <f t="shared" si="32"/>
+        <v>3195.7435090863532</v>
+      </c>
+      <c r="L179">
+        <v>25</v>
+      </c>
+      <c r="O179">
+        <v>155808.05255820439</v>
+      </c>
+      <c r="P179">
+        <f t="shared" si="33"/>
+        <v>158465.60128600823</v>
+      </c>
+      <c r="Q179">
+        <v>10377.601286008185</v>
+      </c>
+      <c r="R179">
+        <v>148088.00000000003</v>
+      </c>
+      <c r="S179" s="7">
+        <v>46047</v>
+      </c>
+      <c r="T179">
+        <f t="shared" si="35"/>
+        <v>3364393.2063859291</v>
+      </c>
+      <c r="U179">
+        <f t="shared" si="35"/>
+        <v>3277245.4265613863</v>
+      </c>
+    </row>
+    <row r="180" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F180" s="7">
+        <v>46078</v>
+      </c>
+      <c r="G180">
+        <v>3874.8158713185621</v>
+      </c>
+      <c r="H180">
+        <f t="shared" si="36"/>
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I180">
+        <f t="shared" si="34"/>
+        <v>1449.1400470616318</v>
+      </c>
+      <c r="J180">
+        <v>0.05</v>
+      </c>
+      <c r="K180">
+        <f t="shared" si="32"/>
+        <v>1811.4250588270397</v>
+      </c>
+      <c r="L180">
+        <v>25</v>
+      </c>
+      <c r="O180">
+        <v>279878.19870811841</v>
+      </c>
+      <c r="P180">
+        <f t="shared" si="33"/>
+        <v>154771.38189300409</v>
+      </c>
+      <c r="Q180">
+        <v>6683.3818930040688</v>
+      </c>
+      <c r="R180">
+        <v>148088.00000000003</v>
+      </c>
+      <c r="S180" s="7">
+        <v>46078</v>
+      </c>
+      <c r="T180">
+        <f t="shared" si="35"/>
+        <v>3644271.4050940475</v>
+      </c>
+      <c r="U180">
+        <f t="shared" si="35"/>
+        <v>3432016.8084543906</v>
+      </c>
+    </row>
+    <row r="181" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F181" s="7">
+        <v>46106</v>
+      </c>
+      <c r="G181">
+        <v>3826.840185484803</v>
+      </c>
+      <c r="H181">
+        <f t="shared" si="36"/>
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="I181">
+        <f t="shared" si="34"/>
+        <v>389.6609726879401</v>
+      </c>
+      <c r="J181">
+        <v>0.05</v>
+      </c>
+      <c r="K181">
+        <f t="shared" si="32"/>
+        <v>487.07621585992518</v>
+      </c>
+      <c r="L181">
+        <v>25</v>
+      </c>
+      <c r="O181">
+        <v>235169.14805520704</v>
+      </c>
+      <c r="P181">
+        <f t="shared" si="33"/>
+        <v>151720.16661522634</v>
+      </c>
+      <c r="Q181">
+        <v>3632.1666152262928</v>
+      </c>
+      <c r="R181">
+        <v>148088.00000000003</v>
+      </c>
+      <c r="S181" s="7">
+        <v>46106</v>
+      </c>
+      <c r="T181">
+        <f t="shared" si="35"/>
+        <v>3879440.5531492545</v>
+      </c>
+      <c r="U181">
+        <f t="shared" si="35"/>
+        <v>3583736.9750696169</v>
+      </c>
+    </row>
+    <row r="182" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="J182" t="s">
+        <v>42</v>
+      </c>
+      <c r="K182" s="9">
+        <f>SUM(K170:K181)</f>
+        <v>79821.707707830166</v>
+      </c>
+    </row>
+    <row r="184" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="J184" t="s">
+        <v>44</v>
+      </c>
+      <c r="K184">
+        <f>SUM(K165+K182)</f>
+        <v>3087509.1730578919</v>
+      </c>
+    </row>
+    <row r="186" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="J186" t="s">
+        <v>46</v>
+      </c>
+      <c r="K186">
+        <f>(K149-K184)/K149</f>
+        <v>4.6846230524229045E-2</v>
+      </c>
+    </row>
+    <row r="190" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="G190" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="191" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="G191" t="s">
+        <v>39</v>
+      </c>
+      <c r="H191" t="s">
+        <v>40</v>
+      </c>
+      <c r="I191" t="s">
+        <v>41</v>
+      </c>
+      <c r="J191" t="s">
+        <v>43</v>
+      </c>
+      <c r="K191" t="s">
+        <v>42</v>
+      </c>
+      <c r="L191" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="192" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="E192">
+        <v>1242</v>
+      </c>
+      <c r="F192" s="7">
+        <v>45772</v>
+      </c>
+      <c r="G192">
+        <v>5195.1035206425595</v>
+      </c>
+      <c r="H192">
+        <v>7369.9982180361203</v>
+      </c>
+      <c r="I192">
+        <f>H192-G192+E192</f>
+        <v>3416.8946973935608</v>
+      </c>
+      <c r="J192">
+        <v>0.05</v>
+      </c>
+      <c r="K192">
+        <f>I192*J192*L192</f>
+        <v>4271.1183717419517</v>
+      </c>
+      <c r="L192">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="193" spans="6:16" x14ac:dyDescent="0.2">
+      <c r="F193" s="7">
+        <v>45802</v>
+      </c>
+      <c r="G193">
+        <v>5907.1382972953343</v>
+      </c>
+      <c r="H193">
+        <v>3813.8171728011271</v>
+      </c>
+      <c r="I193">
+        <f>I192+H193-G193</f>
+        <v>1323.5735728993532</v>
+      </c>
+      <c r="J193">
+        <v>0.05</v>
+      </c>
+      <c r="K193">
+        <f t="shared" ref="K193:K203" si="37">I193*J193*L193</f>
+        <v>1654.4669661241915</v>
+      </c>
+      <c r="L193">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="194" spans="6:16" x14ac:dyDescent="0.2">
+      <c r="F194" s="7">
+        <v>45833</v>
+      </c>
+      <c r="G194">
+        <v>5625.7573205650187</v>
+      </c>
+      <c r="H194">
+        <v>7432.0540666490888</v>
+      </c>
+      <c r="I194">
+        <f t="shared" ref="I194:I203" si="38">I193+H194-G194</f>
+        <v>3129.8703189834232</v>
+      </c>
+      <c r="J194">
+        <v>0.05</v>
+      </c>
+      <c r="K194">
+        <f t="shared" si="37"/>
+        <v>3912.3378987292795</v>
+      </c>
+      <c r="L194">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="195" spans="6:16" x14ac:dyDescent="0.2">
+      <c r="F195" s="7">
+        <v>45863</v>
+      </c>
+      <c r="G195">
+        <v>6433.9826158977739</v>
+      </c>
+      <c r="H195">
+        <v>6258.571845599231</v>
+      </c>
+      <c r="I195">
+        <f t="shared" si="38"/>
+        <v>2954.4595486848812</v>
+      </c>
+      <c r="J195">
+        <v>0.05</v>
+      </c>
+      <c r="K195">
+        <f t="shared" si="37"/>
+        <v>3693.0744358561014</v>
+      </c>
+      <c r="L195">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="196" spans="6:16" x14ac:dyDescent="0.2">
+      <c r="F196" s="7">
+        <v>45894</v>
+      </c>
+      <c r="G196">
+        <v>6493.9081133646077</v>
+      </c>
+      <c r="H196">
+        <v>6258.571845599231</v>
+      </c>
+      <c r="I196">
+        <f t="shared" si="38"/>
+        <v>2719.1232809195053</v>
+      </c>
+      <c r="J196">
+        <v>0.05</v>
+      </c>
+      <c r="K196">
+        <f t="shared" si="37"/>
+        <v>3398.9041011493819</v>
+      </c>
+      <c r="L196">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="197" spans="6:16" x14ac:dyDescent="0.2">
+      <c r="F197" s="7">
+        <v>45925</v>
+      </c>
+      <c r="G197">
+        <v>6071.2326312903115</v>
+      </c>
+      <c r="H197">
+        <v>4778.7981416454531</v>
+      </c>
+      <c r="I197">
+        <f t="shared" si="38"/>
+        <v>1426.688791274647</v>
+      </c>
+      <c r="J197">
+        <v>0.05</v>
+      </c>
+      <c r="K197">
+        <f t="shared" si="37"/>
+        <v>1783.3609890933087</v>
+      </c>
+      <c r="L197">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="198" spans="6:16" x14ac:dyDescent="0.2">
+      <c r="F198" s="7">
+        <v>45955</v>
+      </c>
+      <c r="G198">
+        <v>6403.8158313631438</v>
+      </c>
+      <c r="H198">
+        <v>6810.537494794291</v>
+      </c>
+      <c r="I198">
+        <f t="shared" si="38"/>
+        <v>1833.4104547057932</v>
+      </c>
+      <c r="J198">
+        <v>0.05</v>
+      </c>
+      <c r="K198">
+        <f t="shared" si="37"/>
+        <v>2291.7630683822417</v>
+      </c>
+      <c r="L198">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="199" spans="6:16" x14ac:dyDescent="0.2">
+      <c r="F199" s="7">
+        <v>45986</v>
+      </c>
+      <c r="G199">
+        <v>6026.4848889003415</v>
+      </c>
+      <c r="H199">
+        <v>5169.9588819954042</v>
+      </c>
+      <c r="I199">
+        <f t="shared" si="38"/>
+        <v>976.88444780085592</v>
+      </c>
+      <c r="J199">
+        <v>0.05</v>
+      </c>
+      <c r="K199">
+        <f t="shared" si="37"/>
+        <v>1221.1055597510701</v>
+      </c>
+      <c r="L199">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="200" spans="6:16" x14ac:dyDescent="0.2">
+      <c r="F200" s="7">
+        <v>46016</v>
+      </c>
+      <c r="G200">
+        <v>4479.7985738060161</v>
+      </c>
+      <c r="H200">
+        <v>4725.1965053637505</v>
+      </c>
+      <c r="I200">
+        <f t="shared" si="38"/>
+        <v>1222.2823793585903</v>
+      </c>
+      <c r="J200">
+        <v>0.05</v>
+      </c>
+      <c r="K200">
+        <f t="shared" si="37"/>
+        <v>1527.8529741982379</v>
+      </c>
+      <c r="L200">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="201" spans="6:16" x14ac:dyDescent="0.2">
+      <c r="F201" s="7">
+        <v>46047</v>
+      </c>
+      <c r="G201">
+        <v>4284.164832400751</v>
+      </c>
+      <c r="H201">
+        <v>3151.6199379169921</v>
+      </c>
+      <c r="I201">
+        <f t="shared" si="38"/>
+        <v>89.737484874831352</v>
+      </c>
+      <c r="J201">
+        <v>0.05</v>
+      </c>
+      <c r="K201">
+        <f t="shared" si="37"/>
+        <v>112.17185609353919</v>
+      </c>
+      <c r="L201">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="202" spans="6:16" x14ac:dyDescent="0.2">
+      <c r="F202" s="7">
+        <v>46078</v>
+      </c>
+      <c r="G202">
+        <v>3874.8158713185621</v>
+      </c>
+      <c r="H202">
+        <v>3956.2754337342722</v>
+      </c>
+      <c r="I202">
+        <f t="shared" si="38"/>
+        <v>171.19704729054138</v>
+      </c>
+      <c r="J202">
+        <v>0.05</v>
+      </c>
+      <c r="K202">
+        <f t="shared" si="37"/>
+        <v>213.99630911317672</v>
+      </c>
+      <c r="L202">
+        <v>25</v>
+      </c>
+      <c r="M202" s="8"/>
+      <c r="N202" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="O202" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P202" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="203" spans="6:16" x14ac:dyDescent="0.2">
+      <c r="F203" s="7">
+        <v>46106</v>
+      </c>
+      <c r="G203">
+        <v>3826.840185484803</v>
+      </c>
+      <c r="H203">
+        <v>3933.9414186168956</v>
+      </c>
+      <c r="I203">
+        <f t="shared" si="38"/>
+        <v>278.29828042263443</v>
+      </c>
+      <c r="J203">
+        <v>0.05</v>
+      </c>
+      <c r="K203">
+        <f t="shared" si="37"/>
+        <v>347.87285052829304</v>
+      </c>
+      <c r="L203">
+        <v>25</v>
+      </c>
+      <c r="M203" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="N203" s="8">
+        <v>890831.11158837902</v>
+      </c>
+      <c r="O203" s="8">
+        <v>659262.465350062</v>
+      </c>
+      <c r="P203" s="8">
+        <f>100*(N203-O203)/N203</f>
+        <v>25.994674324454504</v>
+      </c>
+    </row>
+    <row r="204" spans="6:16" x14ac:dyDescent="0.2">
+      <c r="J204" t="s">
+        <v>42</v>
+      </c>
+      <c r="K204" s="9">
+        <f>SUM(K192:K203)</f>
+        <v>24428.025380760777</v>
+      </c>
+      <c r="M204" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="N204" s="8">
+        <v>2348425</v>
+      </c>
+      <c r="O204" s="8">
+        <v>2348425</v>
+      </c>
+      <c r="P204" s="8">
+        <f t="shared" ref="P204:P206" si="39">100*(N204-O204)/N204</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="6:16" x14ac:dyDescent="0.2">
+      <c r="M205" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="N205" s="8">
+        <v>24428.025380760777</v>
+      </c>
+      <c r="O205" s="11">
+        <f>K182</f>
+        <v>79821.707707830166</v>
+      </c>
+      <c r="P205" s="8">
+        <f t="shared" si="39"/>
+        <v>-226.76283270401706</v>
+      </c>
+    </row>
+    <row r="206" spans="6:16" x14ac:dyDescent="0.2">
+      <c r="J206" t="s">
+        <v>62</v>
+      </c>
+      <c r="K206">
+        <f>K204+K149</f>
+        <v>3263684.1369691398</v>
+      </c>
+      <c r="M206" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="N206" s="8">
+        <f>SUM(N203:N205)</f>
+        <v>3263684.1369691398</v>
+      </c>
+      <c r="O206" s="8">
+        <f>SUM(O203:O205)</f>
+        <v>3087509.1730578924</v>
+      </c>
+      <c r="P206" s="8">
+        <f t="shared" si="39"/>
+        <v>5.3980396545008329</v>
+      </c>
+    </row>
+    <row r="208" spans="6:16" x14ac:dyDescent="0.2">
+      <c r="N208" t="s">
+        <v>33</v>
+      </c>
+      <c r="O208" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="209" spans="13:17" x14ac:dyDescent="0.2">
+      <c r="M209" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="N209">
+        <f>SUM(N203:N204)</f>
+        <v>3239256.1115883789</v>
+      </c>
+      <c r="O209">
+        <f>SUM(O203:O204)</f>
+        <v>3007687.4653500621</v>
+      </c>
+      <c r="P209">
+        <f>100*(N209-O209)/N209</f>
+        <v>7.1488217745390443</v>
+      </c>
+      <c r="Q209">
+        <f>N209-O209</f>
+        <v>231568.64623831678</v>
+      </c>
+    </row>
+    <row r="210" spans="13:17" x14ac:dyDescent="0.2">
+      <c r="M210" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="N210">
+        <f>100*N205/N209</f>
+        <v>0.75412454400780371</v>
+      </c>
+      <c r="O210">
+        <f>ABS(P205)*N210</f>
+        <v>171.00741781083474</v>
+      </c>
+    </row>
+    <row r="214" spans="13:17" x14ac:dyDescent="0.2">
+      <c r="N214" t="s">
+        <v>33</v>
+      </c>
+      <c r="O214" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="215" spans="13:17" x14ac:dyDescent="0.2">
+      <c r="M215" t="s">
+        <v>50</v>
+      </c>
+      <c r="N215">
+        <v>3276</v>
+      </c>
+      <c r="O215">
+        <f>N215*(100-P209)/100</f>
+        <v>3041.8045986661004</v>
+      </c>
+      <c r="P215">
+        <f>N215-O215</f>
+        <v>234.19540133389955</v>
+      </c>
+    </row>
+    <row r="216" spans="13:17" x14ac:dyDescent="0.2">
+      <c r="M216" t="s">
+        <v>57</v>
+      </c>
+      <c r="N216">
+        <f>N215*N210/100</f>
+        <v>24.705120061695649</v>
+      </c>
+      <c r="O216">
+        <f>N216*(100+ABS(P205))/100</f>
+        <v>80.727150136525111</v>
+      </c>
+      <c r="P216">
+        <f>N216-O216</f>
+        <v>-56.022030074829459</v>
+      </c>
+    </row>
+    <row r="217" spans="13:17" x14ac:dyDescent="0.2">
+      <c r="M217" t="s">
+        <v>75</v>
+      </c>
+      <c r="N217">
+        <v>0</v>
+      </c>
+      <c r="O217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="13:17" x14ac:dyDescent="0.2">
+      <c r="N218">
+        <f>SUM(N215:N216)</f>
+        <v>3300.7051200616957</v>
+      </c>
+      <c r="O218">
+        <f>SUM(O215:O216)</f>
+        <v>3122.5317488026258</v>
+      </c>
+      <c r="P218">
+        <f>SUM(P215:P217)</f>
+        <v>178.17337125907011</v>
+      </c>
+    </row>
+    <row r="220" spans="13:17" x14ac:dyDescent="0.2">
+      <c r="N220">
+        <f>N218-O218</f>
+        <v>178.17337125906988</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I130:I131"/>
+  </mergeCells>
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1D5ED8B-B115-8A46-924C-BC1A722319F5}">
   <dimension ref="A1:V29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -29084,643 +34673,4 @@
     <ignoredError sqref="F2 F3:F13" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{350C6D2B-71FC-0A4A-8981-25C5B83CB6E9}">
-  <dimension ref="A1:T13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:20" ht="48" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="L1" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M1" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="N1" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A2" s="12">
-        <v>45748</v>
-      </c>
-      <c r="B2">
-        <v>1.5288157894736842</v>
-      </c>
-      <c r="C2">
-        <v>1.4112105263157895</v>
-      </c>
-      <c r="D2">
-        <v>4886.8312757201647</v>
-      </c>
-      <c r="E2">
-        <v>9513.1687242798362</v>
-      </c>
-      <c r="F2">
-        <f t="shared" ref="F2:F13" si="0">SUM(D2:E2)</f>
-        <v>14400</v>
-      </c>
-      <c r="G2" s="8">
-        <v>4886.8312757201647</v>
-      </c>
-      <c r="H2" s="8">
-        <v>9513.1687242798362</v>
-      </c>
-      <c r="I2">
-        <f>SUM(G2:H2)</f>
-        <v>14400</v>
-      </c>
-      <c r="J2">
-        <v>10314.285714285714</v>
-      </c>
-      <c r="K2">
-        <v>254.28571428571433</v>
-      </c>
-      <c r="L2">
-        <v>254.28571428571433</v>
-      </c>
-      <c r="M2">
-        <f>C2*E2</f>
-        <v>13425.083842321856</v>
-      </c>
-      <c r="N2">
-        <f>C2*H2</f>
-        <v>13425.083842321856</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A3" s="12">
-        <v>45778</v>
-      </c>
-      <c r="B3">
-        <v>1.5806907894736841</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>4886.8312757201647</v>
-      </c>
-      <c r="E3">
-        <v>2570.3115814226921</v>
-      </c>
-      <c r="F3">
-        <f t="shared" si="0"/>
-        <v>7457.1428571428569</v>
-      </c>
-      <c r="G3" s="8">
-        <v>4886.8312757201647</v>
-      </c>
-      <c r="H3" s="8">
-        <v>2570.3115814226921</v>
-      </c>
-      <c r="I3">
-        <f t="shared" ref="I3:I13" si="1">SUM(G3:H3)</f>
-        <v>7457.1428571428569</v>
-      </c>
-      <c r="J3">
-        <v>12000</v>
-      </c>
-      <c r="K3">
-        <v>27.142857142857157</v>
-      </c>
-      <c r="L3">
-        <v>27.142857142857157</v>
-      </c>
-      <c r="M3">
-        <f t="shared" ref="M3:M13" si="2">C3*E3</f>
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <f t="shared" ref="N3:N13" si="3">C3*H3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A4" s="12">
-        <v>45809</v>
-      </c>
-      <c r="B4">
-        <v>1.6237697368421053</v>
-      </c>
-      <c r="C4">
-        <v>1.4613947368421052</v>
-      </c>
-      <c r="D4">
-        <v>4886.8312757201647</v>
-      </c>
-      <c r="E4">
-        <v>9627.4544385655499</v>
-      </c>
-      <c r="F4">
-        <f t="shared" si="0"/>
-        <v>14514.285714285714</v>
-      </c>
-      <c r="G4" s="8">
-        <v>4886.8312757201647</v>
-      </c>
-      <c r="H4" s="8">
-        <v>9627.4544385655499</v>
-      </c>
-      <c r="I4">
-        <f t="shared" si="1"/>
-        <v>14514.285714285714</v>
-      </c>
-      <c r="J4">
-        <v>9828.5714285714294</v>
-      </c>
-      <c r="K4">
-        <v>261.42857142857139</v>
-      </c>
-      <c r="L4">
-        <v>261.42857142857139</v>
-      </c>
-      <c r="M4">
-        <f t="shared" si="2"/>
-        <v>14069.511245706859</v>
-      </c>
-      <c r="N4">
-        <f t="shared" si="3"/>
-        <v>14069.511245706859</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A5" s="12">
-        <v>45839</v>
-      </c>
-      <c r="B5">
-        <v>1.6237697368421053</v>
-      </c>
-      <c r="C5">
-        <v>0.97426315789473683</v>
-      </c>
-      <c r="D5">
-        <v>4886.8312757201647</v>
-      </c>
-      <c r="E5">
-        <v>7341.7401528512646</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="0"/>
-        <v>12228.571428571429</v>
-      </c>
-      <c r="G5" s="8">
-        <v>4886.8312757201647</v>
-      </c>
-      <c r="H5">
-        <v>7341.7401528512646</v>
-      </c>
-      <c r="I5">
-        <f t="shared" si="1"/>
-        <v>12228.571428571429</v>
-      </c>
-      <c r="J5">
-        <v>12457.142857142857</v>
-      </c>
-      <c r="K5">
-        <v>249.99999999999991</v>
-      </c>
-      <c r="L5">
-        <v>249.99999999999991</v>
-      </c>
-      <c r="M5">
-        <f t="shared" si="2"/>
-        <v>7152.7869457594607</v>
-      </c>
-      <c r="N5">
-        <f t="shared" si="3"/>
-        <v>7152.7869457594607</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A6" s="12">
-        <v>45870</v>
-      </c>
-      <c r="B6">
-        <v>1.6237697368421053</v>
-      </c>
-      <c r="C6">
-        <v>0.97426315789473683</v>
-      </c>
-      <c r="D6">
-        <v>4886.8312757201647</v>
-      </c>
-      <c r="E6">
-        <v>7341.7401528512646</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="0"/>
-        <v>12228.571428571429</v>
-      </c>
-      <c r="G6" s="8">
-        <v>4886.8312757201647</v>
-      </c>
-      <c r="H6">
-        <v>15000</v>
-      </c>
-      <c r="I6">
-        <f t="shared" si="1"/>
-        <v>19886.831275720164</v>
-      </c>
-      <c r="J6">
-        <v>12657.142857142857</v>
-      </c>
-      <c r="K6">
-        <v>228.57142857142856</v>
-      </c>
-      <c r="L6">
-        <v>611.48442092886535</v>
-      </c>
-      <c r="M6">
-        <f t="shared" si="2"/>
-        <v>7152.7869457594607</v>
-      </c>
-      <c r="N6">
-        <f t="shared" si="3"/>
-        <v>14613.947368421052</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A7" s="12">
-        <v>45901</v>
-      </c>
-      <c r="B7">
-        <v>1.6237697368421053</v>
-      </c>
-      <c r="C7">
-        <v>0.32475657894736842</v>
-      </c>
-      <c r="D7">
-        <v>4886.8312757201647</v>
-      </c>
-      <c r="E7">
-        <v>4456.0258671369784</v>
-      </c>
-      <c r="F7">
-        <f t="shared" si="0"/>
-        <v>9342.8571428571431</v>
-      </c>
-      <c r="G7" s="8">
-        <v>4886.8312757201647</v>
-      </c>
-      <c r="H7">
-        <v>15000</v>
-      </c>
-      <c r="I7">
-        <f t="shared" si="1"/>
-        <v>19886.831275720164</v>
-      </c>
-      <c r="J7">
-        <v>12000</v>
-      </c>
-      <c r="K7">
-        <v>95.714285714285694</v>
-      </c>
-      <c r="L7">
-        <v>1005.8259847148737</v>
-      </c>
-      <c r="M7">
-        <f t="shared" si="2"/>
-        <v>1447.123716312386</v>
-      </c>
-      <c r="N7">
-        <f t="shared" si="3"/>
-        <v>4871.3486842105267</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="12">
-        <v>45931</v>
-      </c>
-      <c r="B8">
-        <v>1.7219534883720931</v>
-      </c>
-      <c r="C8">
-        <v>1.7219534883720931</v>
-      </c>
-      <c r="D8">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="E8">
-        <v>10546.924603174602</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="0"/>
-        <v>13314.285714285714</v>
-      </c>
-      <c r="G8" s="8">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="H8">
-        <v>15000</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="1"/>
-        <v>17767.361111111109</v>
-      </c>
-      <c r="J8">
-        <v>11714.285714285714</v>
-      </c>
-      <c r="K8">
-        <v>175.71428571428569</v>
-      </c>
-      <c r="L8">
-        <v>1308.4797545561435</v>
-      </c>
-      <c r="M8">
-        <f t="shared" si="2"/>
-        <v>18161.313612033959</v>
-      </c>
-      <c r="N8">
-        <f t="shared" si="3"/>
-        <v>25829.302325581397</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="12">
-        <v>45962</v>
-      </c>
-      <c r="B9">
-        <v>1.720433105627585</v>
-      </c>
-      <c r="C9">
-        <v>1.720433105627585</v>
-      </c>
-      <c r="D9">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="E9">
-        <v>7346.9246031746025</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="0"/>
-        <v>10114.285714285714</v>
-      </c>
-      <c r="G9" s="8">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="H9">
-        <v>3088.8718871251899</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="1"/>
-        <v>5856.2329982363008</v>
-      </c>
-      <c r="J9">
-        <v>9342.8571428571431</v>
-      </c>
-      <c r="K9">
-        <v>214.28571428571422</v>
-      </c>
-      <c r="L9">
-        <v>1134.1485473251014</v>
-      </c>
-      <c r="M9">
-        <f t="shared" si="2"/>
-        <v>12639.892311851394</v>
-      </c>
-      <c r="N9">
-        <f t="shared" si="3"/>
-        <v>5314.1974536525295</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A10" s="12">
-        <v>45992</v>
-      </c>
-      <c r="B10">
-        <v>1.720433105627585</v>
-      </c>
-      <c r="C10">
-        <v>2.2939030624099632</v>
-      </c>
-      <c r="D10">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="E10">
-        <v>6461.210317460318</v>
-      </c>
-      <c r="F10">
-        <f t="shared" si="0"/>
-        <v>9228.5714285714294</v>
-      </c>
-      <c r="G10" s="8">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <f t="shared" si="1"/>
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="J10">
-        <v>9085.7142857142862</v>
-      </c>
-      <c r="K10">
-        <v>221.42857142857139</v>
-      </c>
-      <c r="L10">
-        <v>818.2308885949426</v>
-      </c>
-      <c r="M10">
-        <f t="shared" si="2"/>
-        <v>14821.390134097073</v>
-      </c>
-      <c r="N10">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A11" s="12">
-        <v>46023</v>
-      </c>
-      <c r="B11">
-        <v>1.720433105627585</v>
-      </c>
-      <c r="C11">
-        <v>0.28673497839118917</v>
-      </c>
-      <c r="D11">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="E11">
-        <v>3404.0674603174602</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
-        <v>6171.4285714285716</v>
-      </c>
-      <c r="G11" s="8">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="1"/>
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="J11">
-        <v>9028.5714285714294</v>
-      </c>
-      <c r="K11">
-        <v>78.571428571428541</v>
-      </c>
-      <c r="L11">
-        <v>505.17037272192675</v>
-      </c>
-      <c r="M11">
-        <f t="shared" si="2"/>
-        <v>976.06520967627716</v>
-      </c>
-      <c r="N11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A12" s="12">
-        <v>46054</v>
-      </c>
-      <c r="B12">
-        <v>1.720433105627585</v>
-      </c>
-      <c r="C12">
-        <v>1.4336865095961708</v>
-      </c>
-      <c r="D12">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="E12">
-        <v>4975.4960317460318</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="0"/>
-        <v>7742.8571428571431</v>
-      </c>
-      <c r="G12" s="8">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="1"/>
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="J12">
-        <v>7685.7142857142853</v>
-      </c>
-      <c r="K12">
-        <v>81.428571428571431</v>
-      </c>
-      <c r="L12">
-        <v>259.25271399176808</v>
-      </c>
-      <c r="M12">
-        <f t="shared" si="2"/>
-        <v>7133.3015392635671</v>
-      </c>
-      <c r="N12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A13" s="12">
-        <v>46082</v>
-      </c>
-      <c r="B13">
-        <v>1.720433105627585</v>
-      </c>
-      <c r="C13">
-        <v>1.1469515312049816</v>
-      </c>
-      <c r="D13">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="E13">
-        <v>4918.353174603174</v>
-      </c>
-      <c r="F13">
-        <f t="shared" si="0"/>
-        <v>7685.7142857142853</v>
-      </c>
-      <c r="G13" s="8">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <f t="shared" si="1"/>
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="J13">
-        <v>7571.4285714285716</v>
-      </c>
-      <c r="K13">
-        <v>87.14285714285711</v>
-      </c>
-      <c r="L13">
-        <v>19.049340975895031</v>
-      </c>
-      <c r="M13">
-        <f t="shared" si="2"/>
-        <v>5641.1127046179927</v>
-      </c>
-      <c r="N13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/pidsg25Evaluation.xlsx
+++ b/pidsg25Evaluation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/debdeeppaul/Documents/Procurement/PIDSG25/pricesaa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B528CF3A-B94D-994B-B87A-97D3F6471DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CACDEBE9-A094-6A49-8994-E1D746407932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15680" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -450,7 +450,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -480,15 +480,14 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -15899,10 +15898,10 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="19"/>
+      <c r="C3" s="21"/>
       <c r="D3" s="1">
         <v>45383</v>
       </c>
@@ -16364,10 +16363,10 @@
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="19"/>
+      <c r="C14" s="21"/>
       <c r="D14" s="1">
         <v>45748</v>
       </c>
@@ -19510,7 +19509,7 @@
       </c>
     </row>
     <row r="2" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="22" t="s">
         <v>58</v>
       </c>
       <c r="I2">
@@ -19521,7 +19520,7 @@
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="H3" s="20"/>
+      <c r="H3" s="22"/>
       <c r="I3">
         <v>2116045</v>
       </c>
@@ -21749,7 +21748,7 @@
       </c>
     </row>
     <row r="2" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="22" t="s">
         <v>58</v>
       </c>
       <c r="I2">
@@ -21760,7 +21759,7 @@
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="H3" s="20"/>
+      <c r="H3" s="22"/>
       <c r="I3">
         <v>2116045</v>
       </c>
@@ -26591,7 +26590,7 @@
       </c>
     </row>
     <row r="130" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="I130" s="20" t="s">
+      <c r="I130" s="22" t="s">
         <v>58</v>
       </c>
       <c r="J130">
@@ -26602,7 +26601,7 @@
       </c>
     </row>
     <row r="131" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="I131" s="20"/>
+      <c r="I131" s="22"/>
       <c r="J131">
         <v>2116045</v>
       </c>
@@ -29668,7 +29667,7 @@
       <c r="H22" s="16">
         <v>4886.8312757201647</v>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="19">
         <v>1.5315918917635199E-7</v>
       </c>
       <c r="J22">
@@ -29684,7 +29683,7 @@
         <v>7471.0648150309544</v>
       </c>
       <c r="M22" s="16">
-        <f>SUM(H22:I22)</f>
+        <f t="shared" ref="M22:M33" si="5">SUM(H22:I22)</f>
         <v>4886.8312758733236</v>
       </c>
     </row>
@@ -29699,7 +29698,7 @@
         <v>35</v>
       </c>
       <c r="E23">
-        <f t="shared" ref="E23:E33" si="5">C23*1000/D23</f>
+        <f t="shared" ref="E23:E33" si="6">C23*1000/D23</f>
         <v>7457.1428571428569</v>
       </c>
       <c r="F23">
@@ -29715,19 +29714,19 @@
         <v>540.62315869746203</v>
       </c>
       <c r="J23">
-        <f t="shared" ref="J23:J33" si="6">F23*H23</f>
+        <f t="shared" ref="J23:J33" si="7">F23*H23</f>
         <v>7724.5691872427979</v>
       </c>
       <c r="K23">
-        <f>G23*I23</f>
+        <f t="shared" ref="K23:K33" si="8">G23*I23</f>
         <v>0</v>
       </c>
       <c r="L23">
-        <f t="shared" ref="L23:L34" si="7">SUM(J23:K23)</f>
+        <f t="shared" ref="L23:L34" si="9">SUM(J23:K23)</f>
         <v>7724.5691872427979</v>
       </c>
       <c r="M23" s="16">
-        <f>SUM(H23:I23)</f>
+        <f t="shared" si="5"/>
         <v>5427.4544344176265</v>
       </c>
     </row>
@@ -29742,7 +29741,7 @@
         <v>35</v>
       </c>
       <c r="E24">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14514.285714285714</v>
       </c>
       <c r="F24">
@@ -29758,19 +29757,19 @@
         <v>4941.7401532788099</v>
       </c>
       <c r="J24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7935.0887345679021</v>
       </c>
       <c r="K24">
-        <f>G24*I24</f>
+        <f t="shared" si="8"/>
         <v>7221.8330508429508</v>
       </c>
       <c r="L24">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>15156.921785410854</v>
       </c>
       <c r="M24" s="16">
-        <f>SUM(H24:I24)</f>
+        <f t="shared" si="5"/>
         <v>9828.5714289989737</v>
       </c>
     </row>
@@ -29785,7 +29784,7 @@
         <v>35</v>
       </c>
       <c r="E25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12228.571428571429</v>
       </c>
       <c r="F25">
@@ -29801,19 +29800,19 @@
         <v>7570.3115841096997</v>
       </c>
       <c r="J25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7935.0887345679021</v>
       </c>
       <c r="K25">
-        <f>G25*I25</f>
+        <f t="shared" si="8"/>
         <v>7375.4756701818233</v>
       </c>
       <c r="L25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>15310.564404749726</v>
       </c>
       <c r="M25" s="16">
-        <f>SUM(H25:I25)</f>
+        <f t="shared" si="5"/>
         <v>12457.142859829864</v>
       </c>
     </row>
@@ -29828,7 +29827,7 @@
         <v>35</v>
       </c>
       <c r="E26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12228.571428571429</v>
       </c>
       <c r="F26">
@@ -29844,19 +29843,19 @@
         <v>7770.31158376848</v>
       </c>
       <c r="J26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7935.0887345679021</v>
       </c>
       <c r="K26">
-        <f>G26*I26</f>
+        <f t="shared" si="8"/>
         <v>7570.3283014283334</v>
       </c>
       <c r="L26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>15505.417035996235</v>
       </c>
       <c r="M26" s="16">
-        <f>SUM(H26:I26)</f>
+        <f t="shared" si="5"/>
         <v>12657.142859488646</v>
       </c>
     </row>
@@ -29871,7 +29870,7 @@
         <v>35</v>
       </c>
       <c r="E27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9342.8571428571431</v>
       </c>
       <c r="F27">
@@ -29887,19 +29886,19 @@
         <v>7113.1687245564199</v>
       </c>
       <c r="J27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7935.0887345679021</v>
       </c>
       <c r="K27">
-        <f>G27*I27</f>
+        <f t="shared" si="8"/>
         <v>2310.0483404623587</v>
       </c>
       <c r="L27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10245.137075030261</v>
       </c>
       <c r="M27" s="16">
-        <f>SUM(H27:I27)</f>
+        <f t="shared" si="5"/>
         <v>12000.000000276585</v>
       </c>
     </row>
@@ -29914,7 +29913,7 @@
         <v>35</v>
       </c>
       <c r="E28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>13314.285714285714</v>
       </c>
       <c r="F28">
@@ -29930,19 +29929,19 @@
         <v>8946.9245984865192</v>
       </c>
       <c r="J28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4765.2671188630493</v>
       </c>
       <c r="K28">
-        <f>G28*I28</f>
+        <f t="shared" si="8"/>
         <v>15406.18802256595</v>
       </c>
       <c r="L28">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>20171.455141429</v>
       </c>
       <c r="M28" s="16">
-        <f>SUM(H28:I28)</f>
+        <f t="shared" si="5"/>
         <v>11714.285709597631</v>
       </c>
     </row>
@@ -29957,7 +29956,7 @@
         <v>35</v>
       </c>
       <c r="E29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10114.285714285714</v>
       </c>
       <c r="F29">
@@ -29977,15 +29976,15 @@
         <v>4761.0596707818931</v>
       </c>
       <c r="K29">
-        <f>G29*I29</f>
+        <f t="shared" si="8"/>
         <v>11312.701059692285</v>
       </c>
       <c r="L29">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>16073.760730474178</v>
       </c>
       <c r="M29" s="16">
-        <f>SUM(H29:I29)</f>
+        <f t="shared" si="5"/>
         <v>9342.8571432951721</v>
       </c>
     </row>
@@ -30000,7 +29999,7 @@
         <v>35</v>
       </c>
       <c r="E30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9228.5714285714294</v>
       </c>
       <c r="F30">
@@ -30016,19 +30015,19 @@
         <v>6318.3531745293103</v>
       </c>
       <c r="J30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4761.0596707818931</v>
       </c>
       <c r="K30">
-        <f>G30*I30</f>
+        <f t="shared" si="8"/>
         <v>14493.689696440499</v>
       </c>
       <c r="L30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>19254.749367222394</v>
       </c>
       <c r="M30" s="16">
-        <f>SUM(H30:I30)</f>
+        <f t="shared" si="5"/>
         <v>9085.7142856404207</v>
       </c>
     </row>
@@ -30043,7 +30042,7 @@
         <v>35</v>
       </c>
       <c r="E31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6171.4285714285716</v>
       </c>
       <c r="F31">
@@ -30059,22 +30058,22 @@
         <v>6261.21031907623</v>
       </c>
       <c r="J31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4761.0596707818931</v>
       </c>
       <c r="K31">
-        <f>G31*I31</f>
+        <f t="shared" si="8"/>
         <v>1795.3080055430135</v>
       </c>
       <c r="L31">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>6556.3676763249068</v>
       </c>
       <c r="M31" s="16">
-        <f>SUM(H31:I31)</f>
+        <f t="shared" si="5"/>
         <v>9028.5714301873413</v>
       </c>
-      <c r="N31" s="21"/>
+      <c r="N31" s="19"/>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B32" s="14">
@@ -30087,7 +30086,7 @@
         <v>35</v>
       </c>
       <c r="E32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7742.8571428571431</v>
       </c>
       <c r="F32">
@@ -30103,22 +30102,22 @@
         <v>4918.3531743943704</v>
       </c>
       <c r="J32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4761.0596707818931</v>
       </c>
       <c r="K32">
-        <f>G32*I32</f>
+        <f t="shared" si="8"/>
         <v>7051.3765955587114</v>
       </c>
       <c r="L32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>11812.436266340605</v>
       </c>
       <c r="M32" s="16">
-        <f>SUM(H32:I32)</f>
+        <f t="shared" si="5"/>
         <v>7685.7142855054817</v>
       </c>
-      <c r="N32" s="21"/>
+      <c r="N32" s="19"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B33" s="14">
@@ -30131,7 +30130,7 @@
         <v>35</v>
       </c>
       <c r="E33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7685.7142857142853</v>
       </c>
       <c r="F33">
@@ -30147,22 +30146,22 @@
         <v>4804.06745988488</v>
       </c>
       <c r="J33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4761.0596707818931</v>
       </c>
       <c r="K33">
-        <f>G33*I33</f>
+        <f t="shared" si="8"/>
         <v>5510.0325291269901</v>
       </c>
       <c r="L33">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10271.092199908882</v>
       </c>
       <c r="M33" s="16">
-        <f>SUM(H33:I33)</f>
+        <f t="shared" si="5"/>
         <v>7571.4285709959913</v>
       </c>
-      <c r="N33" s="21"/>
+      <c r="N33" s="19"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="I34" t="s">
@@ -30177,7 +30176,7 @@
         <v>80046.981272059056</v>
       </c>
       <c r="L34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>155553.53568516078</v>
       </c>
     </row>
@@ -30259,7 +30258,7 @@
         <f>H39-G39+E39</f>
         <v>5085.7142857142862</v>
       </c>
-      <c r="J39" s="22">
+      <c r="J39" s="20">
         <f>M22</f>
         <v>4886.8312758733236</v>
       </c>
@@ -30285,6 +30284,10 @@
         <f>J70</f>
         <v>75506.554413101723</v>
       </c>
+      <c r="R39">
+        <f>100*(P39-Q39)/P39</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="40" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B40" s="17">
@@ -30297,19 +30300,19 @@
         <v>45778</v>
       </c>
       <c r="G40">
-        <f t="shared" ref="G40:G49" si="8">B40*1000/C40</f>
+        <f t="shared" ref="G40:G49" si="10">B40*1000/C40</f>
         <v>12000</v>
       </c>
       <c r="H40" s="16">
-        <f t="shared" ref="H40:H50" si="9">SUM(H5:I5)</f>
+        <f t="shared" ref="H40:H50" si="11">SUM(H5:I5)</f>
         <v>7457.1428571428569</v>
       </c>
       <c r="I40" s="16">
         <f>I39+H40-G40</f>
         <v>542.85714285714312</v>
       </c>
-      <c r="J40" s="22">
-        <f t="shared" ref="J40:J50" si="10">M23</f>
+      <c r="J40" s="20">
+        <f t="shared" ref="J40:J50" si="12">M23</f>
         <v>5427.4544344176265</v>
       </c>
       <c r="K40">
@@ -30317,11 +30320,11 @@
         <v>-11000.000003994763</v>
       </c>
       <c r="L40">
-        <f t="shared" ref="L40:L50" si="11">I40*0.05</f>
+        <f t="shared" ref="L40:L50" si="13">I40*0.05</f>
         <v>27.142857142857157</v>
       </c>
       <c r="M40">
-        <f t="shared" ref="M40:M50" si="12">K40*0.05</f>
+        <f t="shared" ref="M40:M50" si="14">K40*0.05</f>
         <v>-550.00000019973811</v>
       </c>
       <c r="O40" t="s">
@@ -30332,7 +30335,11 @@
       </c>
       <c r="Q40">
         <f>K70</f>
-        <v>86295.051536851184</v>
+        <v>95225.738794344288</v>
+      </c>
+      <c r="R40">
+        <f t="shared" ref="R40:R43" si="15">100*(P40-Q40)/P40</f>
+        <v>7.2058106419099373</v>
       </c>
     </row>
     <row r="41" spans="2:18" ht="16" x14ac:dyDescent="0.2">
@@ -30346,19 +30353,19 @@
         <v>45809</v>
       </c>
       <c r="G41">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>9828.5714285714294</v>
       </c>
       <c r="H41" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>14514.285714285714</v>
       </c>
       <c r="I41" s="16">
-        <f t="shared" ref="I41:I50" si="13">I40+H41-G41</f>
+        <f t="shared" ref="I41:I50" si="16">I40+H41-G41</f>
         <v>5228.5714285714275</v>
       </c>
-      <c r="J41" s="22">
-        <f t="shared" si="10"/>
+      <c r="J41" s="20">
+        <f t="shared" si="12"/>
         <v>9828.5714289989737</v>
       </c>
       <c r="K41">
@@ -30366,11 +30373,11 @@
         <v>-11000.000003567218</v>
       </c>
       <c r="L41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>261.42857142857139</v>
       </c>
       <c r="M41">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-550.00000017836089</v>
       </c>
       <c r="O41" t="s">
@@ -30381,7 +30388,11 @@
       </c>
       <c r="Q41">
         <f>P70</f>
-        <v>-1.4030861666469719E-5</v>
+        <v>792.8571422707995</v>
+      </c>
+      <c r="R41">
+        <f t="shared" si="15"/>
+        <v>59.869848185859738</v>
       </c>
     </row>
     <row r="42" spans="2:18" ht="16" x14ac:dyDescent="0.2">
@@ -30395,31 +30406,31 @@
         <v>45839</v>
       </c>
       <c r="G42">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>12457.142857142857</v>
       </c>
       <c r="H42" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12228.571428571429</v>
       </c>
       <c r="I42" s="16">
+        <f t="shared" si="16"/>
+        <v>4999.9999999999982</v>
+      </c>
+      <c r="J42" s="20">
+        <f t="shared" si="12"/>
+        <v>12457.142859829864</v>
+      </c>
+      <c r="K42">
+        <f t="shared" ref="K42:K50" si="17">K41+J42-G42</f>
+        <v>-11000.000000880211</v>
+      </c>
+      <c r="L42">
         <f t="shared" si="13"/>
-        <v>4999.9999999999982</v>
-      </c>
-      <c r="J42" s="22">
-        <f t="shared" si="10"/>
-        <v>12457.142859829864</v>
-      </c>
-      <c r="K42">
-        <f t="shared" ref="K42:K50" si="14">K41+J42-G42</f>
-        <v>-11000.000000880211</v>
-      </c>
-      <c r="L42">
-        <f t="shared" si="11"/>
         <v>249.99999999999991</v>
       </c>
       <c r="M42">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-550.00000004401056</v>
       </c>
       <c r="O42" t="s">
@@ -30443,31 +30454,31 @@
         <v>45870</v>
       </c>
       <c r="G43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>12657.142857142857</v>
       </c>
       <c r="H43" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12228.571428571429</v>
       </c>
       <c r="I43" s="16">
+        <f t="shared" si="16"/>
+        <v>4571.4285714285706</v>
+      </c>
+      <c r="J43" s="20">
+        <f t="shared" si="12"/>
+        <v>12657.142859488646</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="17"/>
+        <v>-10999.999998534422</v>
+      </c>
+      <c r="L43">
         <f t="shared" si="13"/>
-        <v>4571.4285714285706</v>
-      </c>
-      <c r="J43" s="22">
-        <f t="shared" si="10"/>
-        <v>12657.142859488646</v>
-      </c>
-      <c r="K43">
+        <v>228.57142857142856</v>
+      </c>
+      <c r="M43">
         <f t="shared" si="14"/>
-        <v>-10999.999998534422</v>
-      </c>
-      <c r="L43">
-        <f t="shared" si="11"/>
-        <v>228.57142857142856</v>
-      </c>
-      <c r="M43">
-        <f t="shared" si="12"/>
         <v>-549.9999999267211</v>
       </c>
       <c r="O43" t="s">
@@ -30478,7 +30489,11 @@
       </c>
       <c r="Q43">
         <f>SUM(Q39:Q42)</f>
-        <v>161801.60593592204</v>
+        <v>171525.1503497168</v>
+      </c>
+      <c r="R43">
+        <f t="shared" si="15"/>
+        <v>4.7625546765125923</v>
       </c>
     </row>
     <row r="44" spans="2:18" ht="16" x14ac:dyDescent="0.2">
@@ -30492,31 +30507,31 @@
         <v>45901</v>
       </c>
       <c r="G44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>12000</v>
       </c>
       <c r="H44" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>9342.8571428571431</v>
       </c>
       <c r="I44" s="16">
+        <f t="shared" si="16"/>
+        <v>1914.2857142857138</v>
+      </c>
+      <c r="J44" s="20">
+        <f t="shared" si="12"/>
+        <v>12000.000000276585</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="17"/>
+        <v>-10999.999998257837</v>
+      </c>
+      <c r="L44">
         <f t="shared" si="13"/>
-        <v>1914.2857142857138</v>
-      </c>
-      <c r="J44" s="22">
-        <f t="shared" si="10"/>
-        <v>12000.000000276585</v>
-      </c>
-      <c r="K44">
+        <v>95.714285714285694</v>
+      </c>
+      <c r="M44">
         <f t="shared" si="14"/>
-        <v>-10999.999998257837</v>
-      </c>
-      <c r="L44">
-        <f t="shared" si="11"/>
-        <v>95.714285714285694</v>
-      </c>
-      <c r="M44">
-        <f t="shared" si="12"/>
         <v>-549.99999991289189</v>
       </c>
     </row>
@@ -30531,31 +30546,31 @@
         <v>45931</v>
       </c>
       <c r="G45">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>11714.285714285714</v>
       </c>
       <c r="H45" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>13314.285714285714</v>
       </c>
       <c r="I45" s="16">
+        <f t="shared" si="16"/>
+        <v>3514.2857142857138</v>
+      </c>
+      <c r="J45" s="20">
+        <f t="shared" si="12"/>
+        <v>11714.285709597631</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="17"/>
+        <v>-11000.000002945921</v>
+      </c>
+      <c r="L45">
         <f t="shared" si="13"/>
-        <v>3514.2857142857138</v>
-      </c>
-      <c r="J45" s="22">
-        <f t="shared" si="10"/>
-        <v>11714.285709597631</v>
-      </c>
-      <c r="K45">
+        <v>175.71428571428569</v>
+      </c>
+      <c r="M45">
         <f t="shared" si="14"/>
-        <v>-11000.000002945921</v>
-      </c>
-      <c r="L45">
-        <f t="shared" si="11"/>
-        <v>175.71428571428569</v>
-      </c>
-      <c r="M45">
-        <f t="shared" si="12"/>
         <v>-550.00000014729608</v>
       </c>
     </row>
@@ -30570,31 +30585,31 @@
         <v>45962</v>
       </c>
       <c r="G46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>9342.8571428571431</v>
       </c>
       <c r="H46" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10114.285714285714</v>
       </c>
       <c r="I46" s="16">
+        <f t="shared" si="16"/>
+        <v>4285.7142857142844</v>
+      </c>
+      <c r="J46" s="20">
+        <f t="shared" si="12"/>
+        <v>9342.8571432951721</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="17"/>
+        <v>-11000.000002507892</v>
+      </c>
+      <c r="L46">
         <f t="shared" si="13"/>
-        <v>4285.7142857142844</v>
-      </c>
-      <c r="J46" s="22">
-        <f t="shared" si="10"/>
-        <v>9342.8571432951721</v>
-      </c>
-      <c r="K46">
+        <v>214.28571428571422</v>
+      </c>
+      <c r="M46">
         <f t="shared" si="14"/>
-        <v>-11000.000002507892</v>
-      </c>
-      <c r="L46">
-        <f t="shared" si="11"/>
-        <v>214.28571428571422</v>
-      </c>
-      <c r="M46">
-        <f t="shared" si="12"/>
         <v>-550.00000012539465</v>
       </c>
     </row>
@@ -30609,31 +30624,31 @@
         <v>45992</v>
       </c>
       <c r="G47">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>9085.7142857142862</v>
       </c>
       <c r="H47" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>9228.5714285714294</v>
       </c>
       <c r="I47" s="16">
+        <f t="shared" si="16"/>
+        <v>4428.5714285714275</v>
+      </c>
+      <c r="J47" s="20">
+        <f t="shared" si="12"/>
+        <v>9085.7142856404207</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="17"/>
+        <v>-11000.000002581757</v>
+      </c>
+      <c r="L47">
         <f t="shared" si="13"/>
-        <v>4428.5714285714275</v>
-      </c>
-      <c r="J47" s="22">
-        <f t="shared" si="10"/>
-        <v>9085.7142856404207</v>
-      </c>
-      <c r="K47">
+        <v>221.42857142857139</v>
+      </c>
+      <c r="M47">
         <f t="shared" si="14"/>
-        <v>-11000.000002581757</v>
-      </c>
-      <c r="L47">
-        <f t="shared" si="11"/>
-        <v>221.42857142857139</v>
-      </c>
-      <c r="M47">
-        <f t="shared" si="12"/>
         <v>-550.00000012908788</v>
       </c>
     </row>
@@ -30648,31 +30663,31 @@
         <v>46023</v>
       </c>
       <c r="G48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>9028.5714285714294</v>
       </c>
       <c r="H48" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>6171.4285714285716</v>
       </c>
       <c r="I48" s="16">
+        <f t="shared" si="16"/>
+        <v>1571.4285714285706</v>
+      </c>
+      <c r="J48" s="20">
+        <f t="shared" si="12"/>
+        <v>9028.5714301873413</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="17"/>
+        <v>-11000.000000965845</v>
+      </c>
+      <c r="L48">
         <f t="shared" si="13"/>
-        <v>1571.4285714285706</v>
-      </c>
-      <c r="J48" s="22">
-        <f t="shared" si="10"/>
-        <v>9028.5714301873413</v>
-      </c>
-      <c r="K48">
+        <v>78.571428571428541</v>
+      </c>
+      <c r="M48">
         <f t="shared" si="14"/>
-        <v>-11000.000000965845</v>
-      </c>
-      <c r="L48">
-        <f t="shared" si="11"/>
-        <v>78.571428571428541</v>
-      </c>
-      <c r="M48">
-        <f t="shared" si="12"/>
         <v>-550.00000004829224</v>
       </c>
     </row>
@@ -30687,31 +30702,31 @@
         <v>46054</v>
       </c>
       <c r="G49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>7685.7142857142853</v>
       </c>
       <c r="H49" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>7742.8571428571431</v>
       </c>
       <c r="I49" s="16">
+        <f t="shared" si="16"/>
+        <v>1628.5714285714284</v>
+      </c>
+      <c r="J49" s="20">
+        <f t="shared" si="12"/>
+        <v>7685.7142855054817</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="17"/>
+        <v>-11000.000001174649</v>
+      </c>
+      <c r="L49">
         <f t="shared" si="13"/>
-        <v>1628.5714285714284</v>
-      </c>
-      <c r="J49" s="22">
-        <f t="shared" si="10"/>
-        <v>7685.7142855054817</v>
-      </c>
-      <c r="K49">
+        <v>81.428571428571431</v>
+      </c>
+      <c r="M49">
         <f t="shared" si="14"/>
-        <v>-11000.000001174649</v>
-      </c>
-      <c r="L49">
-        <f t="shared" si="11"/>
-        <v>81.428571428571431</v>
-      </c>
-      <c r="M49">
-        <f t="shared" si="12"/>
         <v>-550.00000005873244</v>
       </c>
     </row>
@@ -30730,27 +30745,27 @@
         <v>7571.4285714285716</v>
       </c>
       <c r="H50" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>7685.7142857142853</v>
       </c>
       <c r="I50" s="16">
+        <f t="shared" si="16"/>
+        <v>1742.8571428571422</v>
+      </c>
+      <c r="J50" s="20">
+        <f t="shared" si="12"/>
+        <v>7571.4285709959913</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="17"/>
+        <v>-11000.00000160723</v>
+      </c>
+      <c r="L50">
         <f t="shared" si="13"/>
-        <v>1742.8571428571422</v>
-      </c>
-      <c r="J50" s="22">
-        <f t="shared" si="10"/>
-        <v>7571.4285709959913</v>
-      </c>
-      <c r="K50">
+        <v>87.14285714285711</v>
+      </c>
+      <c r="M50">
         <f t="shared" si="14"/>
-        <v>-11000.00000160723</v>
-      </c>
-      <c r="L50">
-        <f t="shared" si="11"/>
-        <v>87.14285714285711</v>
-      </c>
-      <c r="M50">
-        <f t="shared" si="12"/>
         <v>-550.00000008036147</v>
       </c>
     </row>
@@ -30819,7 +30834,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>1000</v>
       </c>
@@ -30845,8 +30860,8 @@
       <c r="H58" s="16">
         <v>4886.8312757201647</v>
       </c>
-      <c r="I58" s="23">
-        <v>4427.4544299999998</v>
+      <c r="I58">
+        <v>9513.1687239999901</v>
       </c>
       <c r="J58">
         <f>F58*H58</f>
@@ -30854,32 +30869,32 @@
       </c>
       <c r="K58">
         <f>G58*I58</f>
-        <v>6248.0702963994736</v>
+        <v>13425.083841926933</v>
       </c>
       <c r="L58">
         <f>SUM(J58:K58)</f>
-        <v>13719.135111214287</v>
+        <v>20896.148656741749</v>
       </c>
       <c r="M58" s="16">
         <f>SUM(H58:I58)</f>
-        <v>9314.2857057201654</v>
+        <v>14399.999999720156</v>
       </c>
       <c r="O58" s="16">
         <f>A58+M58-G39</f>
-        <v>-8.5655483417212963E-6</v>
+        <v>5085.714285434442</v>
       </c>
       <c r="P58">
         <f>O58*0.05</f>
-        <v>-4.2827741708606482E-7</v>
-      </c>
-      <c r="R58" s="21">
+        <v>254.2857142717221</v>
+      </c>
+      <c r="R58" s="19">
         <v>2.4889492989708898E-7</v>
       </c>
-      <c r="S58" s="21">
+      <c r="S58" s="19">
         <v>2.4889492989708898E-7</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B59" s="14">
         <v>45778</v>
       </c>
@@ -30890,7 +30905,7 @@
         <v>35</v>
       </c>
       <c r="E59">
-        <f t="shared" ref="E59:E69" si="15">C59*1000/D59</f>
+        <f t="shared" ref="E59:E69" si="18">C59*1000/D59</f>
         <v>7457.1428571428569</v>
       </c>
       <c r="F59">
@@ -30902,32 +30917,32 @@
       <c r="H59" s="16">
         <v>4886.8312757201647</v>
       </c>
-      <c r="I59" s="23">
-        <v>7113.1687199999997</v>
+      <c r="I59">
+        <v>2570.3115809999999</v>
       </c>
       <c r="J59">
-        <f t="shared" ref="J59:K69" si="16">F59*H59</f>
+        <f t="shared" ref="J59:K69" si="19">F59*H59</f>
         <v>7724.5691872427979</v>
       </c>
       <c r="K59">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="L59">
-        <f t="shared" ref="L59:L70" si="17">SUM(J59:K59)</f>
+        <f t="shared" ref="L59:L70" si="20">SUM(J59:K59)</f>
         <v>7724.5691872427979</v>
       </c>
       <c r="M59" s="16">
-        <f t="shared" ref="M59:M61" si="18">SUM(H59:I59)</f>
-        <v>11999.999995720165</v>
+        <f t="shared" ref="M59:M61" si="21">SUM(H59:I59)</f>
+        <v>7457.1428567201647</v>
       </c>
       <c r="O59" s="16">
         <f>O58+M59-G40</f>
-        <v>-1.2845383025705814E-5</v>
+        <v>542.85714215460757</v>
       </c>
       <c r="P59">
-        <f t="shared" ref="P59:P69" si="19">O59*0.05</f>
-        <v>-6.4226915128529074E-7</v>
+        <f t="shared" ref="P59:P69" si="22">O59*0.05</f>
+        <v>27.142857107730379</v>
       </c>
       <c r="R59">
         <v>1040.6231586454401</v>
@@ -30936,7 +30951,7 @@
         <v>1040.6231586454401</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B60" s="14">
         <v>45809</v>
       </c>
@@ -30947,7 +30962,7 @@
         <v>35</v>
       </c>
       <c r="E60">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>14514.285714285714</v>
       </c>
       <c r="F60">
@@ -30959,32 +30974,32 @@
       <c r="H60" s="16">
         <v>4886.8312757201647</v>
       </c>
-      <c r="I60" s="23">
-        <v>4941.7401499999996</v>
+      <c r="I60">
+        <v>9627.4544389999992</v>
       </c>
       <c r="J60">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>7935.0887345679021</v>
       </c>
       <c r="K60">
-        <f t="shared" si="16"/>
-        <v>7221.8330460513153</v>
+        <f t="shared" si="19"/>
+        <v>14069.511246341761</v>
       </c>
       <c r="L60">
-        <f t="shared" si="17"/>
-        <v>15156.921780619217</v>
+        <f t="shared" si="20"/>
+        <v>22004.599980909661</v>
       </c>
       <c r="M60" s="16">
-        <f t="shared" si="18"/>
-        <v>9828.5714257201653</v>
+        <f t="shared" si="21"/>
+        <v>14514.285714720165</v>
       </c>
       <c r="O60" s="16">
-        <f t="shared" ref="O60:O69" si="20">O59+M60-G41</f>
-        <v>-1.5696647096774541E-5</v>
+        <f t="shared" ref="O60:O69" si="23">O59+M60-G41</f>
+        <v>5228.5714283033431</v>
       </c>
       <c r="P60">
-        <f t="shared" si="19"/>
-        <v>-7.8483235483872708E-7</v>
+        <f t="shared" si="22"/>
+        <v>261.42857141516714</v>
       </c>
       <c r="R60">
         <v>4941.7401525896903</v>
@@ -30993,7 +31008,7 @@
         <v>4941.7401525896903</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B61" s="14">
         <v>45839</v>
       </c>
@@ -31004,7 +31019,7 @@
         <v>35</v>
       </c>
       <c r="E61">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>12228.571428571429</v>
       </c>
       <c r="F61">
@@ -31016,32 +31031,32 @@
       <c r="H61" s="16">
         <v>4886.8312757201647</v>
       </c>
-      <c r="I61" s="23">
-        <v>7570.3115799999996</v>
+      <c r="I61">
+        <v>7341.7401529999997</v>
       </c>
       <c r="J61">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>7935.0887345679021</v>
       </c>
       <c r="K61">
-        <f t="shared" si="16"/>
-        <v>7375.4756661778947</v>
+        <f t="shared" si="19"/>
+        <v>7152.7869459043677</v>
       </c>
       <c r="L61">
-        <f t="shared" si="17"/>
-        <v>15310.564400745796</v>
+        <f t="shared" si="20"/>
+        <v>15087.875680472269</v>
       </c>
       <c r="M61" s="16">
-        <f t="shared" si="18"/>
-        <v>12457.142855720165</v>
+        <f t="shared" si="21"/>
+        <v>12228.571428720164</v>
       </c>
       <c r="O61" s="16">
-        <f t="shared" si="20"/>
-        <v>-1.7119338735938072E-5</v>
+        <f t="shared" si="23"/>
+        <v>4999.9999998806506</v>
       </c>
       <c r="P61">
-        <f t="shared" si="19"/>
-        <v>-8.5596693679690369E-7</v>
+        <f t="shared" si="22"/>
+        <v>249.99999999403255</v>
       </c>
       <c r="R61">
         <v>7570.3115839435704</v>
@@ -31050,7 +31065,7 @@
         <v>7570.3115839435704</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B62" s="14">
         <v>45870</v>
       </c>
@@ -31061,7 +31076,7 @@
         <v>35</v>
       </c>
       <c r="E62">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>12228.571428571429</v>
       </c>
       <c r="F62">
@@ -31073,32 +31088,32 @@
       <c r="H62" s="16">
         <v>4886.8312757201647</v>
       </c>
-      <c r="I62" s="23">
-        <v>7770.3115799999996</v>
+      <c r="I62">
+        <v>2770.3115821323399</v>
       </c>
       <c r="J62">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>7935.0887345679021</v>
       </c>
       <c r="K62">
-        <f t="shared" si="16"/>
-        <v>7570.3282977568415</v>
+        <f t="shared" si="19"/>
+        <v>2699.0125103606183</v>
       </c>
       <c r="L62">
-        <f t="shared" si="17"/>
-        <v>15505.417032324744</v>
+        <f t="shared" si="20"/>
+        <v>10634.101244928521</v>
       </c>
       <c r="M62" s="16">
-        <f t="shared" ref="M62:M69" si="21">SUM(H62:I62)</f>
-        <v>12657.142855720165</v>
+        <f t="shared" ref="M62:M69" si="24">SUM(H62:I62)</f>
+        <v>7657.1428578525047</v>
       </c>
       <c r="O62" s="16">
-        <f t="shared" si="20"/>
-        <v>-1.8542030375101604E-5</v>
+        <f t="shared" si="23"/>
+        <v>5.9029844123870134E-7</v>
       </c>
       <c r="P62">
-        <f t="shared" si="19"/>
-        <v>-9.271015187550802E-7</v>
+        <f t="shared" si="22"/>
+        <v>2.9514922061935067E-8</v>
       </c>
       <c r="R62">
         <v>7770.3115839225802</v>
@@ -31107,7 +31122,7 @@
         <v>7770.3115839225802</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B63" s="14">
         <v>45901</v>
       </c>
@@ -31118,7 +31133,7 @@
         <v>35</v>
       </c>
       <c r="E63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>9342.8571428571431</v>
       </c>
       <c r="F63">
@@ -31130,32 +31145,32 @@
       <c r="H63" s="16">
         <v>4886.8312757201647</v>
       </c>
-      <c r="I63" s="23">
-        <v>7113.1687199999997</v>
+      <c r="I63">
+        <v>7113.1687252683996</v>
       </c>
       <c r="J63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>7935.0887345679021</v>
       </c>
       <c r="K63">
-        <f t="shared" si="16"/>
-        <v>2310.0483389826313</v>
+        <f t="shared" si="19"/>
+        <v>2310.0483406935791</v>
       </c>
       <c r="L63">
-        <f t="shared" si="17"/>
-        <v>10245.137073550533</v>
+        <f t="shared" si="20"/>
+        <v>10245.137075261482</v>
       </c>
       <c r="M63" s="16">
-        <f t="shared" si="21"/>
-        <v>11999.999995720165</v>
+        <f t="shared" si="24"/>
+        <v>12000.000000988564</v>
       </c>
       <c r="O63" s="16">
-        <f t="shared" si="20"/>
-        <v>-2.2821865059086122E-5</v>
+        <f t="shared" si="23"/>
+        <v>1.5788627933943644E-6</v>
       </c>
       <c r="P63">
-        <f t="shared" si="19"/>
-        <v>-1.1410932529543061E-6</v>
+        <f t="shared" si="22"/>
+        <v>7.8943139669718229E-8</v>
       </c>
       <c r="R63">
         <v>7113.1687240479496</v>
@@ -31164,7 +31179,7 @@
         <v>7113.1687240479496</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B64" s="14">
         <v>45931</v>
       </c>
@@ -31175,7 +31190,7 @@
         <v>35</v>
       </c>
       <c r="E64">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>13314.285714285714</v>
       </c>
       <c r="F64">
@@ -31187,32 +31202,32 @@
       <c r="H64" s="16">
         <v>2767.3611111111113</v>
       </c>
-      <c r="I64" s="23">
-        <v>8946.9246000000003</v>
+      <c r="I64">
+        <v>8946.9245985163598</v>
       </c>
       <c r="J64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>4765.2671188630493</v>
       </c>
       <c r="K64">
-        <f t="shared" si="16"/>
-        <v>15406.188025172094</v>
+        <f t="shared" si="19"/>
+        <v>15406.188022617334</v>
       </c>
       <c r="L64">
-        <f t="shared" si="17"/>
-        <v>20171.455144035142</v>
+        <f t="shared" si="20"/>
+        <v>20171.455141480383</v>
       </c>
       <c r="M64" s="16">
-        <f t="shared" si="21"/>
-        <v>11714.285711111112</v>
+        <f t="shared" si="24"/>
+        <v>11714.285709627471</v>
       </c>
       <c r="O64" s="16">
-        <f t="shared" si="20"/>
-        <v>-2.5996467229560949E-5</v>
+        <f t="shared" si="23"/>
+        <v>-3.0793798941886052E-6</v>
       </c>
       <c r="P64">
-        <f t="shared" si="19"/>
-        <v>-1.2998233614780476E-6</v>
+        <f t="shared" si="22"/>
+        <v>-1.5396899470943027E-7</v>
       </c>
       <c r="R64">
         <v>8946.9245989600804</v>
@@ -31221,7 +31236,7 @@
         <v>8946.9245989600804</v>
       </c>
     </row>
-    <row r="65" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B65" s="14">
         <v>45962</v>
       </c>
@@ -31232,7 +31247,7 @@
         <v>35</v>
       </c>
       <c r="E65">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>10114.285714285714</v>
       </c>
       <c r="F65">
@@ -31244,32 +31259,32 @@
       <c r="H65" s="16">
         <v>2767.3611111111113</v>
       </c>
-      <c r="I65" s="23">
-        <v>6575.4960300000002</v>
+      <c r="I65">
+        <v>6575.4960321757098</v>
       </c>
       <c r="J65">
         <f>F65*H65</f>
         <v>4761.0596707818931</v>
       </c>
       <c r="K65">
-        <f t="shared" si="16"/>
-        <v>11312.701055934756</v>
+        <f t="shared" si="19"/>
+        <v>11312.701059677918</v>
       </c>
       <c r="L65">
-        <f t="shared" si="17"/>
-        <v>16073.76072671665</v>
+        <f t="shared" si="20"/>
+        <v>16073.760730459811</v>
       </c>
       <c r="M65" s="16">
-        <f t="shared" si="21"/>
-        <v>9342.8571411111116</v>
+        <f t="shared" si="24"/>
+        <v>9342.8571432868212</v>
       </c>
       <c r="O65" s="16">
-        <f t="shared" si="20"/>
-        <v>-2.7742498787119985E-5</v>
+        <f t="shared" si="23"/>
+        <v>-2.6497018552618101E-6</v>
       </c>
       <c r="P65">
-        <f t="shared" si="19"/>
-        <v>-1.3871249393559992E-6</v>
+        <f t="shared" si="22"/>
+        <v>-1.324850927630905E-7</v>
       </c>
       <c r="R65">
         <v>6575.4960320465498</v>
@@ -31278,7 +31293,7 @@
         <v>6575.4960320465498</v>
       </c>
     </row>
-    <row r="66" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B66" s="14">
         <v>45992</v>
       </c>
@@ -31289,7 +31304,7 @@
         <v>35</v>
       </c>
       <c r="E66">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>9228.5714285714294</v>
       </c>
       <c r="F66">
@@ -31301,32 +31316,32 @@
       <c r="H66" s="16">
         <v>2767.3611111111113</v>
       </c>
-      <c r="I66" s="23">
-        <v>6318.3531700000003</v>
+      <c r="I66">
+        <v>6318.3531745687897</v>
       </c>
       <c r="J66">
-        <f t="shared" ref="J66:J69" si="22">F66*H66</f>
+        <f t="shared" ref="J66:J69" si="25">F66*H66</f>
         <v>4761.0596707818931</v>
       </c>
       <c r="K66">
-        <f t="shared" si="16"/>
-        <v>14493.6896860507</v>
+        <f t="shared" si="19"/>
+        <v>14493.689696531059</v>
       </c>
       <c r="L66">
-        <f t="shared" si="17"/>
-        <v>19254.749356832595</v>
+        <f t="shared" si="20"/>
+        <v>19254.74936731295</v>
       </c>
       <c r="M66" s="16">
-        <f t="shared" si="21"/>
-        <v>9085.7142811111116</v>
+        <f t="shared" si="24"/>
+        <v>9085.7142856799001</v>
       </c>
       <c r="O66" s="16">
-        <f t="shared" si="20"/>
-        <v>-3.2345673389500007E-5</v>
+        <f t="shared" si="23"/>
+        <v>-2.684088030946441E-6</v>
       </c>
       <c r="P66">
-        <f t="shared" si="19"/>
-        <v>-1.6172836694750005E-6</v>
+        <f t="shared" si="22"/>
+        <v>-1.3420440154732207E-7</v>
       </c>
       <c r="R66">
         <v>6318.3531747647503</v>
@@ -31335,7 +31350,7 @@
         <v>6318.3531747647503</v>
       </c>
     </row>
-    <row r="67" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B67" s="14">
         <v>46023</v>
       </c>
@@ -31346,7 +31361,7 @@
         <v>35</v>
       </c>
       <c r="E67">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>6171.4285714285716</v>
       </c>
       <c r="F67">
@@ -31358,32 +31373,32 @@
       <c r="H67" s="16">
         <v>2767.3611111111113</v>
       </c>
-      <c r="I67" s="23">
-        <v>6261.2103200000001</v>
+      <c r="I67">
+        <v>6261.2103190224898</v>
       </c>
       <c r="J67">
+        <f t="shared" si="25"/>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K67">
+        <f t="shared" si="19"/>
+        <v>1795.3080055276043</v>
+      </c>
+      <c r="L67">
+        <f t="shared" si="20"/>
+        <v>6556.3676763094973</v>
+      </c>
+      <c r="M67" s="16">
+        <f t="shared" si="24"/>
+        <v>9028.5714301336011</v>
+      </c>
+      <c r="O67" s="16">
+        <f t="shared" si="23"/>
+        <v>-1.1219162843190134E-6</v>
+      </c>
+      <c r="P67">
         <f t="shared" si="22"/>
-        <v>4761.0596707818931</v>
-      </c>
-      <c r="K67">
-        <f t="shared" si="16"/>
-        <v>1795.3080058078906</v>
-      </c>
-      <c r="L67">
-        <f t="shared" si="17"/>
-        <v>6556.3676765897835</v>
-      </c>
-      <c r="M67" s="16">
-        <f t="shared" si="21"/>
-        <v>9028.5714311111115</v>
-      </c>
-      <c r="O67" s="16">
-        <f t="shared" si="20"/>
-        <v>-2.9805991289322264E-5</v>
-      </c>
-      <c r="P67">
-        <f t="shared" si="19"/>
-        <v>-1.4902995644661134E-6</v>
+        <v>-5.6095814215950668E-8</v>
       </c>
       <c r="R67">
         <v>6261.2103181756202</v>
@@ -31392,7 +31407,7 @@
         <v>6261.2103181756202</v>
       </c>
     </row>
-    <row r="68" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B68" s="14">
         <v>46054</v>
       </c>
@@ -31403,7 +31418,7 @@
         <v>35</v>
       </c>
       <c r="E68">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>7742.8571428571431</v>
       </c>
       <c r="F68">
@@ -31415,32 +31430,32 @@
       <c r="H68" s="16">
         <v>2767.3611111111113</v>
       </c>
-      <c r="I68" s="23">
-        <v>4918.3531700000003</v>
+      <c r="I68">
+        <v>4918.3531744415704</v>
       </c>
       <c r="J68">
+        <f t="shared" si="25"/>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="19"/>
+        <v>7051.3765956263815</v>
+      </c>
+      <c r="L68">
+        <f t="shared" si="20"/>
+        <v>11812.436266408275</v>
+      </c>
+      <c r="M68" s="16">
+        <f t="shared" si="24"/>
+        <v>7685.7142855526818</v>
+      </c>
+      <c r="O68" s="16">
+        <f t="shared" si="23"/>
+        <v>-1.2835198504035361E-6</v>
+      </c>
+      <c r="P68">
         <f t="shared" si="22"/>
-        <v>4761.0596707818931</v>
-      </c>
-      <c r="K68">
-        <f t="shared" si="16"/>
-        <v>7051.3765892585625</v>
-      </c>
-      <c r="L68">
-        <f t="shared" si="17"/>
-        <v>11812.436260040457</v>
-      </c>
-      <c r="M68" s="16">
-        <f t="shared" si="21"/>
-        <v>7685.7142811111116</v>
-      </c>
-      <c r="O68" s="16">
-        <f t="shared" si="20"/>
-        <v>-3.4409164982207585E-5</v>
-      </c>
-      <c r="P68">
-        <f t="shared" si="19"/>
-        <v>-1.7204582491103793E-6</v>
+        <v>-6.4175992520176806E-8</v>
       </c>
       <c r="R68">
         <v>4918.3531750745196</v>
@@ -31449,7 +31464,7 @@
         <v>4918.3531750745196</v>
       </c>
     </row>
-    <row r="69" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B69" s="14">
         <v>46082</v>
       </c>
@@ -31460,7 +31475,7 @@
         <v>35</v>
       </c>
       <c r="E69">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>7685.7142857142853</v>
       </c>
       <c r="F69">
@@ -31472,32 +31487,32 @@
       <c r="H69" s="16">
         <v>2767.3611111111113</v>
       </c>
-      <c r="I69" s="23">
-        <v>4804.0674600000002</v>
+      <c r="I69">
+        <v>4804.0674598933701</v>
       </c>
       <c r="J69">
+        <f t="shared" si="25"/>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="19"/>
+        <v>5510.0325291367271</v>
+      </c>
+      <c r="L69">
+        <f t="shared" si="20"/>
+        <v>10271.092199918621</v>
+      </c>
+      <c r="M69" s="16">
+        <f t="shared" si="24"/>
+        <v>7571.4285710044815</v>
+      </c>
+      <c r="O69" s="16">
+        <f t="shared" si="23"/>
+        <v>-1.7076099538826384E-6</v>
+      </c>
+      <c r="P69">
         <f t="shared" si="22"/>
-        <v>4761.0596707818931</v>
-      </c>
-      <c r="K69">
-        <f t="shared" si="16"/>
-        <v>5510.0325292590269</v>
-      </c>
-      <c r="L69">
-        <f t="shared" si="17"/>
-        <v>10271.092200040919</v>
-      </c>
-      <c r="M69" s="16">
-        <f t="shared" si="21"/>
-        <v>7571.4285711111115</v>
-      </c>
-      <c r="O69" s="16">
-        <f t="shared" si="20"/>
-        <v>-3.4726625017356128E-5</v>
-      </c>
-      <c r="P69">
-        <f t="shared" si="19"/>
-        <v>-1.7363312508678065E-6</v>
+        <v>-8.5380497694131924E-8</v>
       </c>
       <c r="R69">
         <v>4804.0674600945304</v>
@@ -31516,15 +31531,15 @@
       </c>
       <c r="K70">
         <f>SUM(K58:K69)</f>
-        <v>86295.051536851184</v>
+        <v>95225.738794344288</v>
       </c>
       <c r="L70">
-        <f t="shared" si="17"/>
-        <v>161801.60594995291</v>
+        <f t="shared" si="20"/>
+        <v>170732.293207446</v>
       </c>
       <c r="P70" s="18">
         <f>SUM(P58:P69)</f>
-        <v>-1.4030861666469719E-5</v>
+        <v>792.8571422707995</v>
       </c>
     </row>
     <row r="129" spans="2:14" x14ac:dyDescent="0.2">
@@ -31539,7 +31554,7 @@
       </c>
     </row>
     <row r="130" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="I130" s="20" t="s">
+      <c r="I130" s="22" t="s">
         <v>58</v>
       </c>
       <c r="J130">
@@ -31550,7 +31565,7 @@
       </c>
     </row>
     <row r="131" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="I131" s="20"/>
+      <c r="I131" s="22"/>
       <c r="J131">
         <v>2116045</v>
       </c>
@@ -31650,7 +31665,7 @@
         <v>2483.1669423159556</v>
       </c>
       <c r="I137">
-        <f t="shared" ref="I137:I148" si="23">C137*F137*G137</f>
+        <f t="shared" ref="I137:I148" si="26">C137*F137*G137</f>
         <v>232379.9999999998</v>
       </c>
       <c r="J137">
@@ -31693,15 +31708,15 @@
         <v>0</v>
       </c>
       <c r="I138">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>240264.99999999997</v>
       </c>
       <c r="J138">
-        <f t="shared" ref="J138:J148" si="24">E138*F138*H138</f>
+        <f t="shared" ref="J138:J148" si="27">E138*F138*H138</f>
         <v>0</v>
       </c>
       <c r="K138">
-        <f t="shared" ref="K138:K148" si="25">I138+J138</f>
+        <f t="shared" ref="K138:K148" si="28">I138+J138</f>
         <v>240264.99999999997</v>
       </c>
       <c r="L138" s="7">
@@ -31712,7 +31727,7 @@
         <v>108996.8553735357</v>
       </c>
       <c r="N138">
-        <f t="shared" ref="N138:N148" si="26">M154</f>
+        <f t="shared" ref="N138:N148" si="29">M154</f>
         <v>108996.8553735357</v>
       </c>
     </row>
@@ -31736,26 +31751,26 @@
         <v>2545.222790928924</v>
       </c>
       <c r="I139">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>246813</v>
       </c>
       <c r="J139">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>115693.66673321562</v>
       </c>
       <c r="K139">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>362506.66673321562</v>
       </c>
       <c r="L139" s="7">
         <v>45833</v>
       </c>
       <c r="M139">
-        <f t="shared" ref="M139:M148" si="27">M138+J139</f>
+        <f t="shared" ref="M139:M148" si="30">M138+J139</f>
         <v>224690.52210675133</v>
       </c>
       <c r="N139">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>224690.52210675133</v>
       </c>
     </row>
@@ -31779,26 +31794,26 @@
         <v>1371.7405698790662</v>
       </c>
       <c r="I140">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>246813</v>
       </c>
       <c r="J140">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>41568.514657243817</v>
       </c>
       <c r="K140">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>288381.5146572438</v>
       </c>
       <c r="L140" s="7">
         <v>45863</v>
       </c>
       <c r="M140">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>266259.03676399513</v>
       </c>
       <c r="N140">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>415833.15958043491</v>
       </c>
     </row>
@@ -31822,26 +31837,26 @@
         <v>1371.7405698790662</v>
       </c>
       <c r="I141">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>246813</v>
       </c>
       <c r="J141">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>41568.514657243817</v>
       </c>
       <c r="K141">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>288381.5146572438</v>
       </c>
       <c r="L141" s="7">
         <v>45894</v>
       </c>
       <c r="M141">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>307827.55142123892</v>
       </c>
       <c r="N141">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>627957.52842254017</v>
       </c>
     </row>
@@ -31865,26 +31880,26 @@
         <v>0</v>
       </c>
       <c r="I142">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>246813</v>
       </c>
       <c r="J142">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="K142">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>246813</v>
       </c>
       <c r="L142" s="7">
         <v>45925</v>
       </c>
       <c r="M142">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>307827.55142123892</v>
       </c>
       <c r="N142">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>627957.52842254017</v>
       </c>
     </row>
@@ -31908,26 +31923,26 @@
         <v>4045.6197993210399</v>
       </c>
       <c r="I143">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>148088</v>
       </c>
       <c r="J143">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>216681.9452972213</v>
       </c>
       <c r="K143">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>364769.9452972213</v>
       </c>
       <c r="L143" s="7">
         <v>45955</v>
       </c>
       <c r="M143">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>524509.49671846023</v>
       </c>
       <c r="N143">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>627957.52842254017</v>
       </c>
     </row>
@@ -31951,26 +31966,26 @@
         <v>2402.5977708842929</v>
       </c>
       <c r="I144">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J144">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>128568.65599005947</v>
       </c>
       <c r="K144">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>276656.65599005949</v>
       </c>
       <c r="L144" s="7">
         <v>45986</v>
       </c>
       <c r="M144">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>653078.15270851972</v>
       </c>
       <c r="N144">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -31994,26 +32009,26 @@
         <v>1957.8353942526392</v>
       </c>
       <c r="I145">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J145">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>139690.69560277648</v>
       </c>
       <c r="K145">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>287778.69560277648</v>
       </c>
       <c r="L145" s="7">
         <v>46016</v>
       </c>
       <c r="M145">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>792768.8483112962</v>
       </c>
       <c r="N145">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32037,26 +32052,26 @@
         <v>384.25882680588074</v>
       </c>
       <c r="I146">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J146">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>3427.052604850729</v>
       </c>
       <c r="K146">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>151515.05260485076</v>
       </c>
       <c r="L146" s="7">
         <v>46047</v>
       </c>
       <c r="M146">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>796195.90091614693</v>
       </c>
       <c r="N146">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32080,26 +32095,26 @@
         <v>1188.9143226231608</v>
       </c>
       <c r="I147">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J147">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>53017.714351968039</v>
       </c>
       <c r="K147">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>201105.71435196808</v>
       </c>
       <c r="L147" s="7">
         <v>46078</v>
       </c>
       <c r="M147">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>849213.61526811495</v>
       </c>
       <c r="N147">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32123,26 +32138,26 @@
         <v>1166.5803075057843</v>
       </c>
       <c r="I148">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J148">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>41617.496320264065</v>
       </c>
       <c r="K148">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>189705.49632026409</v>
       </c>
       <c r="L148" s="7">
         <v>46106</v>
       </c>
       <c r="M148">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>890831.11158837902</v>
       </c>
       <c r="N148">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32235,7 +32250,7 @@
         <v>2483.1669423159556</v>
       </c>
       <c r="I153">
-        <f t="shared" ref="I153:I164" si="28">C153*F153*G153</f>
+        <f t="shared" ref="I153:I164" si="31">C153*F153*G153</f>
         <v>232380</v>
       </c>
       <c r="J153">
@@ -32271,15 +32286,15 @@
         <v>0</v>
       </c>
       <c r="I154">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>240264.99999999997</v>
       </c>
       <c r="J154">
-        <f t="shared" ref="J154:J164" si="29">E154*F154*H154</f>
+        <f t="shared" ref="J154:J164" si="32">E154*F154*H154</f>
         <v>0</v>
       </c>
       <c r="K154">
-        <f t="shared" ref="K154:K164" si="30">I154+J154</f>
+        <f t="shared" ref="K154:K164" si="33">I154+J154</f>
         <v>240264.99999999997</v>
       </c>
       <c r="M154">
@@ -32316,19 +32331,19 @@
         <v>2545.222790928924</v>
       </c>
       <c r="I155">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>246813</v>
       </c>
       <c r="J155">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>115693.66673321562</v>
       </c>
       <c r="K155">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>362506.66673321562</v>
       </c>
       <c r="M155">
-        <f t="shared" ref="M155:M164" si="31">M154+J155</f>
+        <f t="shared" ref="M155:M164" si="34">M154+J155</f>
         <v>224690.52210675133</v>
       </c>
       <c r="P155">
@@ -32363,19 +32378,19 @@
         <v>6307.6131687242596</v>
       </c>
       <c r="I156">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>246813</v>
       </c>
       <c r="J156">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>191142.6374736836</v>
       </c>
       <c r="K156">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>437955.63747368357</v>
       </c>
       <c r="M156">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>415833.15958043491</v>
       </c>
     </row>
@@ -32399,19 +32414,19 @@
         <v>7000</v>
       </c>
       <c r="I157">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>246813</v>
       </c>
       <c r="J157">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>212124.36884210526</v>
       </c>
       <c r="K157">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>458937.36884210526</v>
       </c>
       <c r="M157">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>627957.52842254017</v>
       </c>
     </row>
@@ -32435,19 +32450,19 @@
         <v>0</v>
       </c>
       <c r="I158">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>246813</v>
       </c>
       <c r="J158">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K158">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>246813</v>
       </c>
       <c r="M158">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>627957.52842254017</v>
       </c>
     </row>
@@ -32471,19 +32486,19 @@
         <v>0</v>
       </c>
       <c r="I159">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>148088</v>
       </c>
       <c r="J159">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K159">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>148088</v>
       </c>
       <c r="M159">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>627957.52842254017</v>
       </c>
     </row>
@@ -32507,19 +32522,19 @@
         <v>585.00395061726795</v>
       </c>
       <c r="I160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J160">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>31304.936927521801</v>
       </c>
       <c r="K160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>179392.93692752183</v>
       </c>
       <c r="M160">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32543,19 +32558,19 @@
         <v>0</v>
       </c>
       <c r="I161">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K161">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>148088.00000000003</v>
       </c>
       <c r="M161">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32579,19 +32594,19 @@
         <v>0</v>
       </c>
       <c r="I162">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J162">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K162">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>148088.00000000003</v>
       </c>
       <c r="M162">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32615,19 +32630,19 @@
         <v>0</v>
       </c>
       <c r="I163">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J163">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K163">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>148088.00000000003</v>
       </c>
       <c r="M163">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32651,19 +32666,19 @@
         <v>0</v>
       </c>
       <c r="I164">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J164">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K164">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>148088.00000000003</v>
       </c>
       <c r="M164">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32765,7 +32780,7 @@
         <v>0.05</v>
       </c>
       <c r="K170">
-        <f t="shared" ref="K170:K181" si="32">I170*J170*L170</f>
+        <f t="shared" ref="K170:K181" si="35">I170*J170*L170</f>
         <v>4271.1183717419517</v>
       </c>
       <c r="L170">
@@ -32814,7 +32829,7 @@
         <v>0.05</v>
       </c>
       <c r="K171">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1654.4669661241915</v>
       </c>
       <c r="L171">
@@ -32824,7 +32839,7 @@
         <v>240264.99999999997</v>
       </c>
       <c r="P171">
-        <f t="shared" ref="P171:P181" si="33">SUM(Q171:R171)</f>
+        <f t="shared" ref="P171:P181" si="36">SUM(Q171:R171)</f>
         <v>251415.3343621399</v>
       </c>
       <c r="Q171">
@@ -32856,14 +32871,14 @@
         <v>7432.0540666490888</v>
       </c>
       <c r="I172">
-        <f t="shared" ref="I172:I181" si="34">I171+H172-G172</f>
+        <f t="shared" ref="I172:I181" si="37">I171+H172-G172</f>
         <v>3129.8703189834232</v>
       </c>
       <c r="J172">
         <v>0.05</v>
       </c>
       <c r="K172">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>3912.3378987292795</v>
       </c>
       <c r="L172">
@@ -32873,7 +32888,7 @@
         <v>474790.57894736843</v>
       </c>
       <c r="P172">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>578630.59750184091</v>
       </c>
       <c r="Q172">
@@ -32886,11 +32901,11 @@
         <v>45833</v>
       </c>
       <c r="T172">
-        <f t="shared" ref="T172:U181" si="35">O172+T171</f>
+        <f t="shared" ref="T172:U181" si="38">O172+T171</f>
         <v>1161939.5789473685</v>
       </c>
       <c r="U172">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>1372327.4382430147</v>
       </c>
     </row>
@@ -32902,18 +32917,18 @@
         <v>6433.9826158977739</v>
       </c>
       <c r="H173">
-        <f t="shared" ref="H173:H181" si="36">SUM(G156:H156)</f>
+        <f t="shared" ref="H173:H181" si="39">SUM(G156:H156)</f>
         <v>11194.444444444423</v>
       </c>
       <c r="I173">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>7890.3321475300727</v>
       </c>
       <c r="J173">
         <v>0.05</v>
       </c>
       <c r="K173">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>9862.9151844125918</v>
       </c>
       <c r="L173">
@@ -32923,7 +32938,7 @@
         <v>351059.15789473685</v>
       </c>
       <c r="P173">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>477018.32306021225</v>
       </c>
       <c r="Q173">
@@ -32936,11 +32951,11 @@
         <v>45863</v>
       </c>
       <c r="T173">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>1512998.7368421054</v>
       </c>
       <c r="U173">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>1849345.7613032269</v>
       </c>
     </row>
@@ -32952,18 +32967,18 @@
         <v>6493.9081133646077</v>
       </c>
       <c r="H174">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>11886.831275720164</v>
       </c>
       <c r="I174">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>13283.25530988563</v>
       </c>
       <c r="J174">
         <v>0.05</v>
       </c>
       <c r="K174">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>16604.069137357037</v>
       </c>
       <c r="L174">
@@ -32973,7 +32988,7 @@
         <v>351059.15789473685</v>
       </c>
       <c r="P174">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>470674.47530300973</v>
       </c>
       <c r="Q174">
@@ -32986,11 +33001,11 @@
         <v>45894</v>
       </c>
       <c r="T174">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>1864057.8947368423</v>
       </c>
       <c r="U174">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>2320020.2366062365</v>
       </c>
     </row>
@@ -33002,18 +33017,18 @@
         <v>6071.2326312903115</v>
       </c>
       <c r="H175">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>4886.8312757201647</v>
       </c>
       <c r="I175">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>12098.853954315482</v>
       </c>
       <c r="J175">
         <v>0.05</v>
       </c>
       <c r="K175">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>15123.567442894353</v>
       </c>
       <c r="L175">
@@ -33023,7 +33038,7 @@
         <v>260452.77631578947</v>
       </c>
       <c r="P175">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>304452.67678642564</v>
       </c>
       <c r="Q175">
@@ -33036,11 +33051,11 @@
         <v>45925</v>
       </c>
       <c r="T175">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>2124510.6710526319</v>
       </c>
       <c r="U175">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>2624472.9133926621</v>
       </c>
     </row>
@@ -33052,18 +33067,18 @@
         <v>6403.8158313631438</v>
       </c>
       <c r="H176">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>2764.9176954732511</v>
       </c>
       <c r="I176">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>8459.9558184255911</v>
       </c>
       <c r="J176">
         <v>0.05</v>
       </c>
       <c r="K176">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>10574.94477303199</v>
       </c>
       <c r="L176">
@@ -33073,7 +33088,7 @@
         <v>278956.46511627908</v>
       </c>
       <c r="P176">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>169548.25946502053</v>
       </c>
       <c r="Q176">
@@ -33086,11 +33101,11 @@
         <v>45955</v>
       </c>
       <c r="T176">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>2403467.1361689111</v>
       </c>
       <c r="U176">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>2794021.1728576827</v>
       </c>
     </row>
@@ -33102,18 +33117,18 @@
         <v>6026.4848889003415</v>
       </c>
       <c r="H177">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>3352.3650617283793</v>
       </c>
       <c r="I177">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>5785.835991253628</v>
       </c>
       <c r="J177">
         <v>0.05</v>
       </c>
       <c r="K177">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>7232.2949890670361</v>
       </c>
       <c r="L177">
@@ -33123,7 +33138,7 @@
         <v>333764.02249175153</v>
       </c>
       <c r="P177">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>165211.03595679012</v>
       </c>
       <c r="Q177">
@@ -33136,11 +33151,11 @@
         <v>45986</v>
       </c>
       <c r="T177">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>2737231.1586606628</v>
       </c>
       <c r="U177">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>2959232.2088144729</v>
       </c>
     </row>
@@ -33152,18 +33167,18 @@
         <v>4479.7985738060161</v>
       </c>
       <c r="H178">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>2767.3611111111113</v>
       </c>
       <c r="I178">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>4073.3985285587223</v>
       </c>
       <c r="J178">
         <v>0.05</v>
       </c>
       <c r="K178">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>5091.7481606984029</v>
       </c>
       <c r="L178">
@@ -33173,7 +33188,7 @@
         <v>471353.99516706169</v>
       </c>
       <c r="P178">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>159547.61646090532</v>
       </c>
       <c r="Q178">
@@ -33186,11 +33201,11 @@
         <v>46016</v>
       </c>
       <c r="T178">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>3208585.1538277245</v>
       </c>
       <c r="U178">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>3118779.8252753783</v>
       </c>
     </row>
@@ -33202,18 +33217,18 @@
         <v>4284.164832400751</v>
       </c>
       <c r="H179">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>2767.3611111111113</v>
       </c>
       <c r="I179">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>2556.5948072690826</v>
       </c>
       <c r="J179">
         <v>0.05</v>
       </c>
       <c r="K179">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>3195.7435090863532</v>
       </c>
       <c r="L179">
@@ -33223,7 +33238,7 @@
         <v>155808.05255820439</v>
       </c>
       <c r="P179">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>158465.60128600823</v>
       </c>
       <c r="Q179">
@@ -33236,11 +33251,11 @@
         <v>46047</v>
       </c>
       <c r="T179">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>3364393.2063859291</v>
       </c>
       <c r="U179">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>3277245.4265613863</v>
       </c>
     </row>
@@ -33252,18 +33267,18 @@
         <v>3874.8158713185621</v>
       </c>
       <c r="H180">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>2767.3611111111113</v>
       </c>
       <c r="I180">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>1449.1400470616318</v>
       </c>
       <c r="J180">
         <v>0.05</v>
       </c>
       <c r="K180">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1811.4250588270397</v>
       </c>
       <c r="L180">
@@ -33273,7 +33288,7 @@
         <v>279878.19870811841</v>
       </c>
       <c r="P180">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>154771.38189300409</v>
       </c>
       <c r="Q180">
@@ -33286,11 +33301,11 @@
         <v>46078</v>
       </c>
       <c r="T180">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>3644271.4050940475</v>
       </c>
       <c r="U180">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>3432016.8084543906</v>
       </c>
     </row>
@@ -33302,18 +33317,18 @@
         <v>3826.840185484803</v>
       </c>
       <c r="H181">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>2767.3611111111113</v>
       </c>
       <c r="I181">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>389.6609726879401</v>
       </c>
       <c r="J181">
         <v>0.05</v>
       </c>
       <c r="K181">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>487.07621585992518</v>
       </c>
       <c r="L181">
@@ -33323,7 +33338,7 @@
         <v>235169.14805520704</v>
       </c>
       <c r="P181">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>151720.16661522634</v>
       </c>
       <c r="Q181">
@@ -33336,11 +33351,11 @@
         <v>46106</v>
       </c>
       <c r="T181">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>3879440.5531492545</v>
       </c>
       <c r="U181">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>3583736.9750696169</v>
       </c>
     </row>
@@ -33442,7 +33457,7 @@
         <v>0.05</v>
       </c>
       <c r="K193">
-        <f t="shared" ref="K193:K203" si="37">I193*J193*L193</f>
+        <f t="shared" ref="K193:K203" si="40">I193*J193*L193</f>
         <v>1654.4669661241915</v>
       </c>
       <c r="L193">
@@ -33460,14 +33475,14 @@
         <v>7432.0540666490888</v>
       </c>
       <c r="I194">
-        <f t="shared" ref="I194:I203" si="38">I193+H194-G194</f>
+        <f t="shared" ref="I194:I203" si="41">I193+H194-G194</f>
         <v>3129.8703189834232</v>
       </c>
       <c r="J194">
         <v>0.05</v>
       </c>
       <c r="K194">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>3912.3378987292795</v>
       </c>
       <c r="L194">
@@ -33485,14 +33500,14 @@
         <v>6258.571845599231</v>
       </c>
       <c r="I195">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>2954.4595486848812</v>
       </c>
       <c r="J195">
         <v>0.05</v>
       </c>
       <c r="K195">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>3693.0744358561014</v>
       </c>
       <c r="L195">
@@ -33510,14 +33525,14 @@
         <v>6258.571845599231</v>
       </c>
       <c r="I196">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>2719.1232809195053</v>
       </c>
       <c r="J196">
         <v>0.05</v>
       </c>
       <c r="K196">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>3398.9041011493819</v>
       </c>
       <c r="L196">
@@ -33535,14 +33550,14 @@
         <v>4778.7981416454531</v>
       </c>
       <c r="I197">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>1426.688791274647</v>
       </c>
       <c r="J197">
         <v>0.05</v>
       </c>
       <c r="K197">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>1783.3609890933087</v>
       </c>
       <c r="L197">
@@ -33560,14 +33575,14 @@
         <v>6810.537494794291</v>
       </c>
       <c r="I198">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>1833.4104547057932</v>
       </c>
       <c r="J198">
         <v>0.05</v>
       </c>
       <c r="K198">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>2291.7630683822417</v>
       </c>
       <c r="L198">
@@ -33585,14 +33600,14 @@
         <v>5169.9588819954042</v>
       </c>
       <c r="I199">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>976.88444780085592</v>
       </c>
       <c r="J199">
         <v>0.05</v>
       </c>
       <c r="K199">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>1221.1055597510701</v>
       </c>
       <c r="L199">
@@ -33610,14 +33625,14 @@
         <v>4725.1965053637505</v>
       </c>
       <c r="I200">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>1222.2823793585903</v>
       </c>
       <c r="J200">
         <v>0.05</v>
       </c>
       <c r="K200">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>1527.8529741982379</v>
       </c>
       <c r="L200">
@@ -33635,14 +33650,14 @@
         <v>3151.6199379169921</v>
       </c>
       <c r="I201">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>89.737484874831352</v>
       </c>
       <c r="J201">
         <v>0.05</v>
       </c>
       <c r="K201">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>112.17185609353919</v>
       </c>
       <c r="L201">
@@ -33660,14 +33675,14 @@
         <v>3956.2754337342722</v>
       </c>
       <c r="I202">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>171.19704729054138</v>
       </c>
       <c r="J202">
         <v>0.05</v>
       </c>
       <c r="K202">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>213.99630911317672</v>
       </c>
       <c r="L202">
@@ -33695,14 +33710,14 @@
         <v>3933.9414186168956</v>
       </c>
       <c r="I203">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>278.29828042263443</v>
       </c>
       <c r="J203">
         <v>0.05</v>
       </c>
       <c r="K203">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>347.87285052829304</v>
       </c>
       <c r="L203">
@@ -33740,7 +33755,7 @@
         <v>2348425</v>
       </c>
       <c r="P204" s="8">
-        <f t="shared" ref="P204:P206" si="39">100*(N204-O204)/N204</f>
+        <f t="shared" ref="P204:P206" si="42">100*(N204-O204)/N204</f>
         <v>0</v>
       </c>
     </row>
@@ -33756,7 +33771,7 @@
         <v>79821.707707830166</v>
       </c>
       <c r="P205" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-226.76283270401706</v>
       </c>
     </row>
@@ -33780,7 +33795,7 @@
         <v>3087509.1730578924</v>
       </c>
       <c r="P206" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>5.3980396545008329</v>
       </c>
     </row>

--- a/pidsg25Evaluation.xlsx
+++ b/pidsg25Evaluation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/debdeeppaul/Documents/Procurement/PIDSG25/pricesaa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CACDEBE9-A094-6A49-8994-E1D746407932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A63B66-53D6-D043-A3B5-DBDB77D7CC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15680" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="100">
   <si>
     <t>FY24</t>
   </si>
@@ -343,6 +343,9 @@
   <si>
     <t>AI storage cost</t>
   </si>
+  <si>
+    <t>Total procurement</t>
+  </si>
 </sst>
 </file>
 
@@ -450,7 +453,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -487,6 +490,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -30442,6 +30451,9 @@
       <c r="Q42">
         <v>0</v>
       </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B43" s="17">
@@ -30651,6 +30663,21 @@
         <f t="shared" si="14"/>
         <v>-550.00000012908788</v>
       </c>
+      <c r="O47" t="s">
+        <v>99</v>
+      </c>
+      <c r="P47">
+        <f>SUM(P39:P40)</f>
+        <v>178126.92262050201</v>
+      </c>
+      <c r="Q47">
+        <f>SUM(Q39:Q40)</f>
+        <v>170732.293207446</v>
+      </c>
+      <c r="R47">
+        <f t="shared" ref="R47" si="18">100*(P47-Q47)/P47</f>
+        <v>4.1513260905597136</v>
+      </c>
     </row>
     <row r="48" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B48" s="17">
@@ -30729,6 +30756,11 @@
         <f t="shared" si="14"/>
         <v>-550.00000005873244</v>
       </c>
+      <c r="P49" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q49" s="23"/>
+      <c r="R49" s="23"/>
     </row>
     <row r="50" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="B50" s="17">
@@ -30768,6 +30800,11 @@
         <f t="shared" si="14"/>
         <v>-550.00000008036147</v>
       </c>
+      <c r="P50" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q50" s="23"/>
+      <c r="R50" s="23"/>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="K51" t="s">
@@ -30781,6 +30818,49 @@
         <f>SUM(M39:M50)</f>
         <v>-6271.3727227715071</v>
       </c>
+      <c r="P51" s="23">
+        <v>2768</v>
+      </c>
+      <c r="Q51" s="23">
+        <f>P51*(1-R47/100)</f>
+        <v>2653.0912938133069</v>
+      </c>
+      <c r="R51" s="23">
+        <f>P51-Q51</f>
+        <v>114.90870618669305</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="P52" s="23">
+        <v>30.7</v>
+      </c>
+      <c r="Q52" s="23">
+        <f>P52*(1-R41/100)</f>
+        <v>12.319956606941059</v>
+      </c>
+      <c r="R52" s="23">
+        <f>P52-Q52</f>
+        <v>18.380043393058941</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="P53" s="23">
+        <f>SUM(P51:P52)</f>
+        <v>2798.7</v>
+      </c>
+      <c r="Q53" s="23">
+        <f>SUM(Q51:Q52)</f>
+        <v>2665.4112504202481</v>
+      </c>
+      <c r="R53" s="23">
+        <f>SUM(R51:R52)</f>
+        <v>133.28874957975199</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="P54" s="23"/>
+      <c r="Q54" s="23"/>
+      <c r="R54" s="23"/>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B56" s="9" t="s">
@@ -30905,7 +30985,7 @@
         <v>35</v>
       </c>
       <c r="E59">
-        <f t="shared" ref="E59:E69" si="18">C59*1000/D59</f>
+        <f t="shared" ref="E59:E69" si="19">C59*1000/D59</f>
         <v>7457.1428571428569</v>
       </c>
       <c r="F59">
@@ -30921,19 +31001,19 @@
         <v>2570.3115809999999</v>
       </c>
       <c r="J59">
-        <f t="shared" ref="J59:K69" si="19">F59*H59</f>
+        <f t="shared" ref="J59:K69" si="20">F59*H59</f>
         <v>7724.5691872427979</v>
       </c>
       <c r="K59">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="L59">
-        <f t="shared" ref="L59:L70" si="20">SUM(J59:K59)</f>
+        <f t="shared" ref="L59:L70" si="21">SUM(J59:K59)</f>
         <v>7724.5691872427979</v>
       </c>
       <c r="M59" s="16">
-        <f t="shared" ref="M59:M61" si="21">SUM(H59:I59)</f>
+        <f t="shared" ref="M59:M61" si="22">SUM(H59:I59)</f>
         <v>7457.1428567201647</v>
       </c>
       <c r="O59" s="16">
@@ -30941,7 +31021,7 @@
         <v>542.85714215460757</v>
       </c>
       <c r="P59">
-        <f t="shared" ref="P59:P69" si="22">O59*0.05</f>
+        <f t="shared" ref="P59:P69" si="23">O59*0.05</f>
         <v>27.142857107730379</v>
       </c>
       <c r="R59">
@@ -30962,7 +31042,7 @@
         <v>35</v>
       </c>
       <c r="E60">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>14514.285714285714</v>
       </c>
       <c r="F60">
@@ -30978,27 +31058,27 @@
         <v>9627.4544389999992</v>
       </c>
       <c r="J60">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7935.0887345679021</v>
       </c>
       <c r="K60">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>14069.511246341761</v>
       </c>
       <c r="L60">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>22004.599980909661</v>
       </c>
       <c r="M60" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>14514.285714720165</v>
       </c>
       <c r="O60" s="16">
-        <f t="shared" ref="O60:O69" si="23">O59+M60-G41</f>
+        <f t="shared" ref="O60:O69" si="24">O59+M60-G41</f>
         <v>5228.5714283033431</v>
       </c>
       <c r="P60">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>261.42857141516714</v>
       </c>
       <c r="R60">
@@ -31019,7 +31099,7 @@
         <v>35</v>
       </c>
       <c r="E61">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>12228.571428571429</v>
       </c>
       <c r="F61">
@@ -31035,27 +31115,27 @@
         <v>7341.7401529999997</v>
       </c>
       <c r="J61">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7935.0887345679021</v>
       </c>
       <c r="K61">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7152.7869459043677</v>
       </c>
       <c r="L61">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>15087.875680472269</v>
       </c>
       <c r="M61" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>12228.571428720164</v>
       </c>
       <c r="O61" s="16">
+        <f t="shared" si="24"/>
+        <v>4999.9999998806506</v>
+      </c>
+      <c r="P61">
         <f t="shared" si="23"/>
-        <v>4999.9999998806506</v>
-      </c>
-      <c r="P61">
-        <f t="shared" si="22"/>
         <v>249.99999999403255</v>
       </c>
       <c r="R61">
@@ -31076,7 +31156,7 @@
         <v>35</v>
       </c>
       <c r="E62">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>12228.571428571429</v>
       </c>
       <c r="F62">
@@ -31092,27 +31172,27 @@
         <v>2770.3115821323399</v>
       </c>
       <c r="J62">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7935.0887345679021</v>
       </c>
       <c r="K62">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2699.0125103606183</v>
       </c>
       <c r="L62">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10634.101244928521</v>
       </c>
       <c r="M62" s="16">
-        <f t="shared" ref="M62:M69" si="24">SUM(H62:I62)</f>
+        <f t="shared" ref="M62:M69" si="25">SUM(H62:I62)</f>
         <v>7657.1428578525047</v>
       </c>
       <c r="O62" s="16">
+        <f t="shared" si="24"/>
+        <v>5.9029844123870134E-7</v>
+      </c>
+      <c r="P62">
         <f t="shared" si="23"/>
-        <v>5.9029844123870134E-7</v>
-      </c>
-      <c r="P62">
-        <f t="shared" si="22"/>
         <v>2.9514922061935067E-8</v>
       </c>
       <c r="R62">
@@ -31133,7 +31213,7 @@
         <v>35</v>
       </c>
       <c r="E63">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9342.8571428571431</v>
       </c>
       <c r="F63">
@@ -31149,27 +31229,27 @@
         <v>7113.1687252683996</v>
       </c>
       <c r="J63">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7935.0887345679021</v>
       </c>
       <c r="K63">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2310.0483406935791</v>
       </c>
       <c r="L63">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10245.137075261482</v>
       </c>
       <c r="M63" s="16">
+        <f t="shared" si="25"/>
+        <v>12000.000000988564</v>
+      </c>
+      <c r="O63" s="16">
         <f t="shared" si="24"/>
-        <v>12000.000000988564</v>
-      </c>
-      <c r="O63" s="16">
+        <v>1.5788627933943644E-6</v>
+      </c>
+      <c r="P63">
         <f t="shared" si="23"/>
-        <v>1.5788627933943644E-6</v>
-      </c>
-      <c r="P63">
-        <f t="shared" si="22"/>
         <v>7.8943139669718229E-8</v>
       </c>
       <c r="R63">
@@ -31190,7 +31270,7 @@
         <v>35</v>
       </c>
       <c r="E64">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>13314.285714285714</v>
       </c>
       <c r="F64">
@@ -31206,27 +31286,27 @@
         <v>8946.9245985163598</v>
       </c>
       <c r="J64">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4765.2671188630493</v>
       </c>
       <c r="K64">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>15406.188022617334</v>
       </c>
       <c r="L64">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>20171.455141480383</v>
       </c>
       <c r="M64" s="16">
+        <f t="shared" si="25"/>
+        <v>11714.285709627471</v>
+      </c>
+      <c r="O64" s="16">
         <f t="shared" si="24"/>
-        <v>11714.285709627471</v>
-      </c>
-      <c r="O64" s="16">
+        <v>-3.0793798941886052E-6</v>
+      </c>
+      <c r="P64">
         <f t="shared" si="23"/>
-        <v>-3.0793798941886052E-6</v>
-      </c>
-      <c r="P64">
-        <f t="shared" si="22"/>
         <v>-1.5396899470943027E-7</v>
       </c>
       <c r="R64">
@@ -31247,7 +31327,7 @@
         <v>35</v>
       </c>
       <c r="E65">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10114.285714285714</v>
       </c>
       <c r="F65">
@@ -31267,23 +31347,23 @@
         <v>4761.0596707818931</v>
       </c>
       <c r="K65">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11312.701059677918</v>
       </c>
       <c r="L65">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>16073.760730459811</v>
       </c>
       <c r="M65" s="16">
+        <f t="shared" si="25"/>
+        <v>9342.8571432868212</v>
+      </c>
+      <c r="O65" s="16">
         <f t="shared" si="24"/>
-        <v>9342.8571432868212</v>
-      </c>
-      <c r="O65" s="16">
+        <v>-2.6497018552618101E-6</v>
+      </c>
+      <c r="P65">
         <f t="shared" si="23"/>
-        <v>-2.6497018552618101E-6</v>
-      </c>
-      <c r="P65">
-        <f t="shared" si="22"/>
         <v>-1.324850927630905E-7</v>
       </c>
       <c r="R65">
@@ -31304,7 +31384,7 @@
         <v>35</v>
       </c>
       <c r="E66">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9228.5714285714294</v>
       </c>
       <c r="F66">
@@ -31320,27 +31400,27 @@
         <v>6318.3531745687897</v>
       </c>
       <c r="J66">
-        <f t="shared" ref="J66:J69" si="25">F66*H66</f>
+        <f t="shared" ref="J66:J69" si="26">F66*H66</f>
         <v>4761.0596707818931</v>
       </c>
       <c r="K66">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>14493.689696531059</v>
       </c>
       <c r="L66">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>19254.74936731295</v>
       </c>
       <c r="M66" s="16">
+        <f t="shared" si="25"/>
+        <v>9085.7142856799001</v>
+      </c>
+      <c r="O66" s="16">
         <f t="shared" si="24"/>
-        <v>9085.7142856799001</v>
-      </c>
-      <c r="O66" s="16">
+        <v>-2.684088030946441E-6</v>
+      </c>
+      <c r="P66">
         <f t="shared" si="23"/>
-        <v>-2.684088030946441E-6</v>
-      </c>
-      <c r="P66">
-        <f t="shared" si="22"/>
         <v>-1.3420440154732207E-7</v>
       </c>
       <c r="R66">
@@ -31361,7 +31441,7 @@
         <v>35</v>
       </c>
       <c r="E67">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6171.4285714285716</v>
       </c>
       <c r="F67">
@@ -31377,27 +31457,27 @@
         <v>6261.2103190224898</v>
       </c>
       <c r="J67">
+        <f t="shared" si="26"/>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K67">
+        <f t="shared" si="20"/>
+        <v>1795.3080055276043</v>
+      </c>
+      <c r="L67">
+        <f t="shared" si="21"/>
+        <v>6556.3676763094973</v>
+      </c>
+      <c r="M67" s="16">
         <f t="shared" si="25"/>
-        <v>4761.0596707818931</v>
-      </c>
-      <c r="K67">
-        <f t="shared" si="19"/>
-        <v>1795.3080055276043</v>
-      </c>
-      <c r="L67">
-        <f t="shared" si="20"/>
-        <v>6556.3676763094973</v>
-      </c>
-      <c r="M67" s="16">
+        <v>9028.5714301336011</v>
+      </c>
+      <c r="O67" s="16">
         <f t="shared" si="24"/>
-        <v>9028.5714301336011</v>
-      </c>
-      <c r="O67" s="16">
+        <v>-1.1219162843190134E-6</v>
+      </c>
+      <c r="P67">
         <f t="shared" si="23"/>
-        <v>-1.1219162843190134E-6</v>
-      </c>
-      <c r="P67">
-        <f t="shared" si="22"/>
         <v>-5.6095814215950668E-8</v>
       </c>
       <c r="R67">
@@ -31418,7 +31498,7 @@
         <v>35</v>
       </c>
       <c r="E68">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7742.8571428571431</v>
       </c>
       <c r="F68">
@@ -31434,27 +31514,27 @@
         <v>4918.3531744415704</v>
       </c>
       <c r="J68">
+        <f t="shared" si="26"/>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="20"/>
+        <v>7051.3765956263815</v>
+      </c>
+      <c r="L68">
+        <f t="shared" si="21"/>
+        <v>11812.436266408275</v>
+      </c>
+      <c r="M68" s="16">
         <f t="shared" si="25"/>
-        <v>4761.0596707818931</v>
-      </c>
-      <c r="K68">
-        <f t="shared" si="19"/>
-        <v>7051.3765956263815</v>
-      </c>
-      <c r="L68">
-        <f t="shared" si="20"/>
-        <v>11812.436266408275</v>
-      </c>
-      <c r="M68" s="16">
+        <v>7685.7142855526818</v>
+      </c>
+      <c r="O68" s="16">
         <f t="shared" si="24"/>
-        <v>7685.7142855526818</v>
-      </c>
-      <c r="O68" s="16">
+        <v>-1.2835198504035361E-6</v>
+      </c>
+      <c r="P68">
         <f t="shared" si="23"/>
-        <v>-1.2835198504035361E-6</v>
-      </c>
-      <c r="P68">
-        <f t="shared" si="22"/>
         <v>-6.4175992520176806E-8</v>
       </c>
       <c r="R68">
@@ -31475,7 +31555,7 @@
         <v>35</v>
       </c>
       <c r="E69">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7685.7142857142853</v>
       </c>
       <c r="F69">
@@ -31491,27 +31571,27 @@
         <v>4804.0674598933701</v>
       </c>
       <c r="J69">
+        <f t="shared" si="26"/>
+        <v>4761.0596707818931</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="20"/>
+        <v>5510.0325291367271</v>
+      </c>
+      <c r="L69">
+        <f t="shared" si="21"/>
+        <v>10271.092199918621</v>
+      </c>
+      <c r="M69" s="16">
         <f t="shared" si="25"/>
-        <v>4761.0596707818931</v>
-      </c>
-      <c r="K69">
-        <f t="shared" si="19"/>
-        <v>5510.0325291367271</v>
-      </c>
-      <c r="L69">
-        <f t="shared" si="20"/>
-        <v>10271.092199918621</v>
-      </c>
-      <c r="M69" s="16">
+        <v>7571.4285710044815</v>
+      </c>
+      <c r="O69" s="16">
         <f t="shared" si="24"/>
-        <v>7571.4285710044815</v>
-      </c>
-      <c r="O69" s="16">
+        <v>-1.7076099538826384E-6</v>
+      </c>
+      <c r="P69">
         <f t="shared" si="23"/>
-        <v>-1.7076099538826384E-6</v>
-      </c>
-      <c r="P69">
-        <f t="shared" si="22"/>
         <v>-8.5380497694131924E-8</v>
       </c>
       <c r="R69">
@@ -31534,7 +31614,7 @@
         <v>95225.738794344288</v>
       </c>
       <c r="L70">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>170732.293207446</v>
       </c>
       <c r="P70" s="18">
@@ -31665,7 +31745,7 @@
         <v>2483.1669423159556</v>
       </c>
       <c r="I137">
-        <f t="shared" ref="I137:I148" si="26">C137*F137*G137</f>
+        <f t="shared" ref="I137:I148" si="27">C137*F137*G137</f>
         <v>232379.9999999998</v>
       </c>
       <c r="J137">
@@ -31708,15 +31788,15 @@
         <v>0</v>
       </c>
       <c r="I138">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>240264.99999999997</v>
       </c>
       <c r="J138">
-        <f t="shared" ref="J138:J148" si="27">E138*F138*H138</f>
+        <f t="shared" ref="J138:J148" si="28">E138*F138*H138</f>
         <v>0</v>
       </c>
       <c r="K138">
-        <f t="shared" ref="K138:K148" si="28">I138+J138</f>
+        <f t="shared" ref="K138:K148" si="29">I138+J138</f>
         <v>240264.99999999997</v>
       </c>
       <c r="L138" s="7">
@@ -31727,7 +31807,7 @@
         <v>108996.8553735357</v>
       </c>
       <c r="N138">
-        <f t="shared" ref="N138:N148" si="29">M154</f>
+        <f t="shared" ref="N138:N148" si="30">M154</f>
         <v>108996.8553735357</v>
       </c>
     </row>
@@ -31751,26 +31831,26 @@
         <v>2545.222790928924</v>
       </c>
       <c r="I139">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>246813</v>
       </c>
       <c r="J139">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>115693.66673321562</v>
       </c>
       <c r="K139">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>362506.66673321562</v>
       </c>
       <c r="L139" s="7">
         <v>45833</v>
       </c>
       <c r="M139">
-        <f t="shared" ref="M139:M148" si="30">M138+J139</f>
+        <f t="shared" ref="M139:M148" si="31">M138+J139</f>
         <v>224690.52210675133</v>
       </c>
       <c r="N139">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>224690.52210675133</v>
       </c>
     </row>
@@ -31794,26 +31874,26 @@
         <v>1371.7405698790662</v>
       </c>
       <c r="I140">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>246813</v>
       </c>
       <c r="J140">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>41568.514657243817</v>
       </c>
       <c r="K140">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>288381.5146572438</v>
       </c>
       <c r="L140" s="7">
         <v>45863</v>
       </c>
       <c r="M140">
+        <f t="shared" si="31"/>
+        <v>266259.03676399513</v>
+      </c>
+      <c r="N140">
         <f t="shared" si="30"/>
-        <v>266259.03676399513</v>
-      </c>
-      <c r="N140">
-        <f t="shared" si="29"/>
         <v>415833.15958043491</v>
       </c>
     </row>
@@ -31837,26 +31917,26 @@
         <v>1371.7405698790662</v>
       </c>
       <c r="I141">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>246813</v>
       </c>
       <c r="J141">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>41568.514657243817</v>
       </c>
       <c r="K141">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>288381.5146572438</v>
       </c>
       <c r="L141" s="7">
         <v>45894</v>
       </c>
       <c r="M141">
+        <f t="shared" si="31"/>
+        <v>307827.55142123892</v>
+      </c>
+      <c r="N141">
         <f t="shared" si="30"/>
-        <v>307827.55142123892</v>
-      </c>
-      <c r="N141">
-        <f t="shared" si="29"/>
         <v>627957.52842254017</v>
       </c>
     </row>
@@ -31880,26 +31960,26 @@
         <v>0</v>
       </c>
       <c r="I142">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>246813</v>
       </c>
       <c r="J142">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K142">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>246813</v>
       </c>
       <c r="L142" s="7">
         <v>45925</v>
       </c>
       <c r="M142">
+        <f t="shared" si="31"/>
+        <v>307827.55142123892</v>
+      </c>
+      <c r="N142">
         <f t="shared" si="30"/>
-        <v>307827.55142123892</v>
-      </c>
-      <c r="N142">
-        <f t="shared" si="29"/>
         <v>627957.52842254017</v>
       </c>
     </row>
@@ -31923,26 +32003,26 @@
         <v>4045.6197993210399</v>
       </c>
       <c r="I143">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>148088</v>
       </c>
       <c r="J143">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>216681.9452972213</v>
       </c>
       <c r="K143">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>364769.9452972213</v>
       </c>
       <c r="L143" s="7">
         <v>45955</v>
       </c>
       <c r="M143">
+        <f t="shared" si="31"/>
+        <v>524509.49671846023</v>
+      </c>
+      <c r="N143">
         <f t="shared" si="30"/>
-        <v>524509.49671846023</v>
-      </c>
-      <c r="N143">
-        <f t="shared" si="29"/>
         <v>627957.52842254017</v>
       </c>
     </row>
@@ -31966,26 +32046,26 @@
         <v>2402.5977708842929</v>
       </c>
       <c r="I144">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J144">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>128568.65599005947</v>
       </c>
       <c r="K144">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>276656.65599005949</v>
       </c>
       <c r="L144" s="7">
         <v>45986</v>
       </c>
       <c r="M144">
+        <f t="shared" si="31"/>
+        <v>653078.15270851972</v>
+      </c>
+      <c r="N144">
         <f t="shared" si="30"/>
-        <v>653078.15270851972</v>
-      </c>
-      <c r="N144">
-        <f t="shared" si="29"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32009,26 +32089,26 @@
         <v>1957.8353942526392</v>
       </c>
       <c r="I145">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J145">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>139690.69560277648</v>
       </c>
       <c r="K145">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>287778.69560277648</v>
       </c>
       <c r="L145" s="7">
         <v>46016</v>
       </c>
       <c r="M145">
+        <f t="shared" si="31"/>
+        <v>792768.8483112962</v>
+      </c>
+      <c r="N145">
         <f t="shared" si="30"/>
-        <v>792768.8483112962</v>
-      </c>
-      <c r="N145">
-        <f t="shared" si="29"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32052,26 +32132,26 @@
         <v>384.25882680588074</v>
       </c>
       <c r="I146">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J146">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>3427.052604850729</v>
       </c>
       <c r="K146">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>151515.05260485076</v>
       </c>
       <c r="L146" s="7">
         <v>46047</v>
       </c>
       <c r="M146">
+        <f t="shared" si="31"/>
+        <v>796195.90091614693</v>
+      </c>
+      <c r="N146">
         <f t="shared" si="30"/>
-        <v>796195.90091614693</v>
-      </c>
-      <c r="N146">
-        <f t="shared" si="29"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32095,26 +32175,26 @@
         <v>1188.9143226231608</v>
       </c>
       <c r="I147">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J147">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>53017.714351968039</v>
       </c>
       <c r="K147">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>201105.71435196808</v>
       </c>
       <c r="L147" s="7">
         <v>46078</v>
       </c>
       <c r="M147">
+        <f t="shared" si="31"/>
+        <v>849213.61526811495</v>
+      </c>
+      <c r="N147">
         <f t="shared" si="30"/>
-        <v>849213.61526811495</v>
-      </c>
-      <c r="N147">
-        <f t="shared" si="29"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32138,26 +32218,26 @@
         <v>1166.5803075057843</v>
       </c>
       <c r="I148">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J148">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>41617.496320264065</v>
       </c>
       <c r="K148">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>189705.49632026409</v>
       </c>
       <c r="L148" s="7">
         <v>46106</v>
       </c>
       <c r="M148">
+        <f t="shared" si="31"/>
+        <v>890831.11158837902</v>
+      </c>
+      <c r="N148">
         <f t="shared" si="30"/>
-        <v>890831.11158837902</v>
-      </c>
-      <c r="N148">
-        <f t="shared" si="29"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32250,7 +32330,7 @@
         <v>2483.1669423159556</v>
       </c>
       <c r="I153">
-        <f t="shared" ref="I153:I164" si="31">C153*F153*G153</f>
+        <f t="shared" ref="I153:I164" si="32">C153*F153*G153</f>
         <v>232380</v>
       </c>
       <c r="J153">
@@ -32286,15 +32366,15 @@
         <v>0</v>
       </c>
       <c r="I154">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>240264.99999999997</v>
       </c>
       <c r="J154">
-        <f t="shared" ref="J154:J164" si="32">E154*F154*H154</f>
+        <f t="shared" ref="J154:J164" si="33">E154*F154*H154</f>
         <v>0</v>
       </c>
       <c r="K154">
-        <f t="shared" ref="K154:K164" si="33">I154+J154</f>
+        <f t="shared" ref="K154:K164" si="34">I154+J154</f>
         <v>240264.99999999997</v>
       </c>
       <c r="M154">
@@ -32331,19 +32411,19 @@
         <v>2545.222790928924</v>
       </c>
       <c r="I155">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>246813</v>
       </c>
       <c r="J155">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>115693.66673321562</v>
       </c>
       <c r="K155">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>362506.66673321562</v>
       </c>
       <c r="M155">
-        <f t="shared" ref="M155:M164" si="34">M154+J155</f>
+        <f t="shared" ref="M155:M164" si="35">M154+J155</f>
         <v>224690.52210675133</v>
       </c>
       <c r="P155">
@@ -32378,19 +32458,19 @@
         <v>6307.6131687242596</v>
       </c>
       <c r="I156">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>246813</v>
       </c>
       <c r="J156">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>191142.6374736836</v>
       </c>
       <c r="K156">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>437955.63747368357</v>
       </c>
       <c r="M156">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>415833.15958043491</v>
       </c>
     </row>
@@ -32414,19 +32494,19 @@
         <v>7000</v>
       </c>
       <c r="I157">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>246813</v>
       </c>
       <c r="J157">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>212124.36884210526</v>
       </c>
       <c r="K157">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>458937.36884210526</v>
       </c>
       <c r="M157">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>627957.52842254017</v>
       </c>
     </row>
@@ -32450,19 +32530,19 @@
         <v>0</v>
       </c>
       <c r="I158">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>246813</v>
       </c>
       <c r="J158">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K158">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>246813</v>
       </c>
       <c r="M158">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>627957.52842254017</v>
       </c>
     </row>
@@ -32486,19 +32566,19 @@
         <v>0</v>
       </c>
       <c r="I159">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>148088</v>
       </c>
       <c r="J159">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K159">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>148088</v>
       </c>
       <c r="M159">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>627957.52842254017</v>
       </c>
     </row>
@@ -32522,19 +32602,19 @@
         <v>585.00395061726795</v>
       </c>
       <c r="I160">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J160">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>31304.936927521801</v>
       </c>
       <c r="K160">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>179392.93692752183</v>
       </c>
       <c r="M160">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32558,19 +32638,19 @@
         <v>0</v>
       </c>
       <c r="I161">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J161">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K161">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>148088.00000000003</v>
       </c>
       <c r="M161">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32594,19 +32674,19 @@
         <v>0</v>
       </c>
       <c r="I162">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J162">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K162">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>148088.00000000003</v>
       </c>
       <c r="M162">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32630,19 +32710,19 @@
         <v>0</v>
       </c>
       <c r="I163">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J163">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K163">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>148088.00000000003</v>
       </c>
       <c r="M163">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32666,19 +32746,19 @@
         <v>0</v>
       </c>
       <c r="I164">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>148088.00000000003</v>
       </c>
       <c r="J164">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K164">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>148088.00000000003</v>
       </c>
       <c r="M164">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>659262.465350062</v>
       </c>
     </row>
@@ -32780,7 +32860,7 @@
         <v>0.05</v>
       </c>
       <c r="K170">
-        <f t="shared" ref="K170:K181" si="35">I170*J170*L170</f>
+        <f t="shared" ref="K170:K181" si="36">I170*J170*L170</f>
         <v>4271.1183717419517</v>
       </c>
       <c r="L170">
@@ -32829,7 +32909,7 @@
         <v>0.05</v>
       </c>
       <c r="K171">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1654.4669661241915</v>
       </c>
       <c r="L171">
@@ -32839,7 +32919,7 @@
         <v>240264.99999999997</v>
       </c>
       <c r="P171">
-        <f t="shared" ref="P171:P181" si="36">SUM(Q171:R171)</f>
+        <f t="shared" ref="P171:P181" si="37">SUM(Q171:R171)</f>
         <v>251415.3343621399</v>
       </c>
       <c r="Q171">
@@ -32871,14 +32951,14 @@
         <v>7432.0540666490888</v>
       </c>
       <c r="I172">
-        <f t="shared" ref="I172:I181" si="37">I171+H172-G172</f>
+        <f t="shared" ref="I172:I181" si="38">I171+H172-G172</f>
         <v>3129.8703189834232</v>
       </c>
       <c r="J172">
         <v>0.05</v>
       </c>
       <c r="K172">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>3912.3378987292795</v>
       </c>
       <c r="L172">
@@ -32888,7 +32968,7 @@
         <v>474790.57894736843</v>
       </c>
       <c r="P172">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>578630.59750184091</v>
       </c>
       <c r="Q172">
@@ -32901,11 +32981,11 @@
         <v>45833</v>
       </c>
       <c r="T172">
-        <f t="shared" ref="T172:U181" si="38">O172+T171</f>
+        <f t="shared" ref="T172:U181" si="39">O172+T171</f>
         <v>1161939.5789473685</v>
       </c>
       <c r="U172">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1372327.4382430147</v>
       </c>
     </row>
@@ -32917,18 +32997,18 @@
         <v>6433.9826158977739</v>
       </c>
       <c r="H173">
-        <f t="shared" ref="H173:H181" si="39">SUM(G156:H156)</f>
+        <f t="shared" ref="H173:H181" si="40">SUM(G156:H156)</f>
         <v>11194.444444444423</v>
       </c>
       <c r="I173">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>7890.3321475300727</v>
       </c>
       <c r="J173">
         <v>0.05</v>
       </c>
       <c r="K173">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>9862.9151844125918</v>
       </c>
       <c r="L173">
@@ -32938,7 +33018,7 @@
         <v>351059.15789473685</v>
       </c>
       <c r="P173">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>477018.32306021225</v>
       </c>
       <c r="Q173">
@@ -32951,11 +33031,11 @@
         <v>45863</v>
       </c>
       <c r="T173">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1512998.7368421054</v>
       </c>
       <c r="U173">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1849345.7613032269</v>
       </c>
     </row>
@@ -32967,18 +33047,18 @@
         <v>6493.9081133646077</v>
       </c>
       <c r="H174">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>11886.831275720164</v>
       </c>
       <c r="I174">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>13283.25530988563</v>
       </c>
       <c r="J174">
         <v>0.05</v>
       </c>
       <c r="K174">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>16604.069137357037</v>
       </c>
       <c r="L174">
@@ -32988,7 +33068,7 @@
         <v>351059.15789473685</v>
       </c>
       <c r="P174">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>470674.47530300973</v>
       </c>
       <c r="Q174">
@@ -33001,11 +33081,11 @@
         <v>45894</v>
       </c>
       <c r="T174">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1864057.8947368423</v>
       </c>
       <c r="U174">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2320020.2366062365</v>
       </c>
     </row>
@@ -33017,18 +33097,18 @@
         <v>6071.2326312903115</v>
       </c>
       <c r="H175">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>4886.8312757201647</v>
       </c>
       <c r="I175">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>12098.853954315482</v>
       </c>
       <c r="J175">
         <v>0.05</v>
       </c>
       <c r="K175">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>15123.567442894353</v>
       </c>
       <c r="L175">
@@ -33038,7 +33118,7 @@
         <v>260452.77631578947</v>
       </c>
       <c r="P175">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>304452.67678642564</v>
       </c>
       <c r="Q175">
@@ -33051,11 +33131,11 @@
         <v>45925</v>
       </c>
       <c r="T175">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2124510.6710526319</v>
       </c>
       <c r="U175">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2624472.9133926621</v>
       </c>
     </row>
@@ -33067,18 +33147,18 @@
         <v>6403.8158313631438</v>
       </c>
       <c r="H176">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2764.9176954732511</v>
       </c>
       <c r="I176">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>8459.9558184255911</v>
       </c>
       <c r="J176">
         <v>0.05</v>
       </c>
       <c r="K176">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>10574.94477303199</v>
       </c>
       <c r="L176">
@@ -33088,7 +33168,7 @@
         <v>278956.46511627908</v>
       </c>
       <c r="P176">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>169548.25946502053</v>
       </c>
       <c r="Q176">
@@ -33101,11 +33181,11 @@
         <v>45955</v>
       </c>
       <c r="T176">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2403467.1361689111</v>
       </c>
       <c r="U176">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2794021.1728576827</v>
       </c>
     </row>
@@ -33117,18 +33197,18 @@
         <v>6026.4848889003415</v>
       </c>
       <c r="H177">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>3352.3650617283793</v>
       </c>
       <c r="I177">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>5785.835991253628</v>
       </c>
       <c r="J177">
         <v>0.05</v>
       </c>
       <c r="K177">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>7232.2949890670361</v>
       </c>
       <c r="L177">
@@ -33138,7 +33218,7 @@
         <v>333764.02249175153</v>
       </c>
       <c r="P177">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>165211.03595679012</v>
       </c>
       <c r="Q177">
@@ -33151,11 +33231,11 @@
         <v>45986</v>
       </c>
       <c r="T177">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2737231.1586606628</v>
       </c>
       <c r="U177">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2959232.2088144729</v>
       </c>
     </row>
@@ -33167,18 +33247,18 @@
         <v>4479.7985738060161</v>
       </c>
       <c r="H178">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2767.3611111111113</v>
       </c>
       <c r="I178">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>4073.3985285587223</v>
       </c>
       <c r="J178">
         <v>0.05</v>
       </c>
       <c r="K178">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>5091.7481606984029</v>
       </c>
       <c r="L178">
@@ -33188,7 +33268,7 @@
         <v>471353.99516706169</v>
       </c>
       <c r="P178">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>159547.61646090532</v>
       </c>
       <c r="Q178">
@@ -33201,11 +33281,11 @@
         <v>46016</v>
       </c>
       <c r="T178">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3208585.1538277245</v>
       </c>
       <c r="U178">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3118779.8252753783</v>
       </c>
     </row>
@@ -33217,18 +33297,18 @@
         <v>4284.164832400751</v>
       </c>
       <c r="H179">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2767.3611111111113</v>
       </c>
       <c r="I179">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>2556.5948072690826</v>
       </c>
       <c r="J179">
         <v>0.05</v>
       </c>
       <c r="K179">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>3195.7435090863532</v>
       </c>
       <c r="L179">
@@ -33238,7 +33318,7 @@
         <v>155808.05255820439</v>
       </c>
       <c r="P179">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>158465.60128600823</v>
       </c>
       <c r="Q179">
@@ -33251,11 +33331,11 @@
         <v>46047</v>
       </c>
       <c r="T179">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3364393.2063859291</v>
       </c>
       <c r="U179">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3277245.4265613863</v>
       </c>
     </row>
@@ -33267,18 +33347,18 @@
         <v>3874.8158713185621</v>
       </c>
       <c r="H180">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2767.3611111111113</v>
       </c>
       <c r="I180">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1449.1400470616318</v>
       </c>
       <c r="J180">
         <v>0.05</v>
       </c>
       <c r="K180">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1811.4250588270397</v>
       </c>
       <c r="L180">
@@ -33288,7 +33368,7 @@
         <v>279878.19870811841</v>
       </c>
       <c r="P180">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>154771.38189300409</v>
       </c>
       <c r="Q180">
@@ -33301,11 +33381,11 @@
         <v>46078</v>
       </c>
       <c r="T180">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3644271.4050940475</v>
       </c>
       <c r="U180">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3432016.8084543906</v>
       </c>
     </row>
@@ -33317,18 +33397,18 @@
         <v>3826.840185484803</v>
       </c>
       <c r="H181">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2767.3611111111113</v>
       </c>
       <c r="I181">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>389.6609726879401</v>
       </c>
       <c r="J181">
         <v>0.05</v>
       </c>
       <c r="K181">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>487.07621585992518</v>
       </c>
       <c r="L181">
@@ -33338,7 +33418,7 @@
         <v>235169.14805520704</v>
       </c>
       <c r="P181">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>151720.16661522634</v>
       </c>
       <c r="Q181">
@@ -33351,11 +33431,11 @@
         <v>46106</v>
       </c>
       <c r="T181">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3879440.5531492545</v>
       </c>
       <c r="U181">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3583736.9750696169</v>
       </c>
     </row>
@@ -33457,7 +33537,7 @@
         <v>0.05</v>
       </c>
       <c r="K193">
-        <f t="shared" ref="K193:K203" si="40">I193*J193*L193</f>
+        <f t="shared" ref="K193:K203" si="41">I193*J193*L193</f>
         <v>1654.4669661241915</v>
       </c>
       <c r="L193">
@@ -33475,14 +33555,14 @@
         <v>7432.0540666490888</v>
       </c>
       <c r="I194">
-        <f t="shared" ref="I194:I203" si="41">I193+H194-G194</f>
+        <f t="shared" ref="I194:I203" si="42">I193+H194-G194</f>
         <v>3129.8703189834232</v>
       </c>
       <c r="J194">
         <v>0.05</v>
       </c>
       <c r="K194">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>3912.3378987292795</v>
       </c>
       <c r="L194">
@@ -33500,14 +33580,14 @@
         <v>6258.571845599231</v>
       </c>
       <c r="I195">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>2954.4595486848812</v>
       </c>
       <c r="J195">
         <v>0.05</v>
       </c>
       <c r="K195">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>3693.0744358561014</v>
       </c>
       <c r="L195">
@@ -33525,14 +33605,14 @@
         <v>6258.571845599231</v>
       </c>
       <c r="I196">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>2719.1232809195053</v>
       </c>
       <c r="J196">
         <v>0.05</v>
       </c>
       <c r="K196">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>3398.9041011493819</v>
       </c>
       <c r="L196">
@@ -33550,14 +33630,14 @@
         <v>4778.7981416454531</v>
       </c>
       <c r="I197">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>1426.688791274647</v>
       </c>
       <c r="J197">
         <v>0.05</v>
       </c>
       <c r="K197">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1783.3609890933087</v>
       </c>
       <c r="L197">
@@ -33575,14 +33655,14 @@
         <v>6810.537494794291</v>
       </c>
       <c r="I198">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>1833.4104547057932</v>
       </c>
       <c r="J198">
         <v>0.05</v>
       </c>
       <c r="K198">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>2291.7630683822417</v>
       </c>
       <c r="L198">
@@ -33600,14 +33680,14 @@
         <v>5169.9588819954042</v>
       </c>
       <c r="I199">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>976.88444780085592</v>
       </c>
       <c r="J199">
         <v>0.05</v>
       </c>
       <c r="K199">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1221.1055597510701</v>
       </c>
       <c r="L199">
@@ -33625,14 +33705,14 @@
         <v>4725.1965053637505</v>
       </c>
       <c r="I200">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>1222.2823793585903</v>
       </c>
       <c r="J200">
         <v>0.05</v>
       </c>
       <c r="K200">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1527.8529741982379</v>
       </c>
       <c r="L200">
@@ -33650,14 +33730,14 @@
         <v>3151.6199379169921</v>
       </c>
       <c r="I201">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>89.737484874831352</v>
       </c>
       <c r="J201">
         <v>0.05</v>
       </c>
       <c r="K201">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>112.17185609353919</v>
       </c>
       <c r="L201">
@@ -33675,14 +33755,14 @@
         <v>3956.2754337342722</v>
       </c>
       <c r="I202">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>171.19704729054138</v>
       </c>
       <c r="J202">
         <v>0.05</v>
       </c>
       <c r="K202">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>213.99630911317672</v>
       </c>
       <c r="L202">
@@ -33710,14 +33790,14 @@
         <v>3933.9414186168956</v>
       </c>
       <c r="I203">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>278.29828042263443</v>
       </c>
       <c r="J203">
         <v>0.05</v>
       </c>
       <c r="K203">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>347.87285052829304</v>
       </c>
       <c r="L203">
@@ -33755,7 +33835,7 @@
         <v>2348425</v>
       </c>
       <c r="P204" s="8">
-        <f t="shared" ref="P204:P206" si="42">100*(N204-O204)/N204</f>
+        <f t="shared" ref="P204:P206" si="43">100*(N204-O204)/N204</f>
         <v>0</v>
       </c>
     </row>
@@ -33771,7 +33851,7 @@
         <v>79821.707707830166</v>
       </c>
       <c r="P205" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>-226.76283270401706</v>
       </c>
     </row>
@@ -33795,7 +33875,7 @@
         <v>3087509.1730578924</v>
       </c>
       <c r="P206" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>5.3980396545008329</v>
       </c>
     </row>

--- a/pidsg25Evaluation.xlsx
+++ b/pidsg25Evaluation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/debdeeppaul/Documents/Procurement/PIDSG25/pricesaa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A63B66-53D6-D043-A3B5-DBDB77D7CC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D216AC-73DF-0546-A26B-53EE8CBABBD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15680" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15680" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="from_alvin" sheetId="1" r:id="rId1"/>
@@ -485,17 +485,17 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -15907,10 +15907,10 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="21"/>
+      <c r="C3" s="23"/>
       <c r="D3" s="1">
         <v>45383</v>
       </c>
@@ -16372,10 +16372,10 @@
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="21"/>
+      <c r="C14" s="23"/>
       <c r="D14" s="1">
         <v>45748</v>
       </c>
@@ -19518,7 +19518,7 @@
       </c>
     </row>
     <row r="2" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="24" t="s">
         <v>58</v>
       </c>
       <c r="I2">
@@ -19529,7 +19529,7 @@
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="H3" s="22"/>
+      <c r="H3" s="24"/>
       <c r="I3">
         <v>2116045</v>
       </c>
@@ -21757,7 +21757,7 @@
       </c>
     </row>
     <row r="2" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="24" t="s">
         <v>58</v>
       </c>
       <c r="I2">
@@ -21768,7 +21768,7 @@
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="H3" s="22"/>
+      <c r="H3" s="24"/>
       <c r="I3">
         <v>2116045</v>
       </c>
@@ -26599,7 +26599,7 @@
       </c>
     </row>
     <row r="130" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="I130" s="22" t="s">
+      <c r="I130" s="24" t="s">
         <v>58</v>
       </c>
       <c r="J130">
@@ -26610,7 +26610,7 @@
       </c>
     </row>
     <row r="131" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="I131" s="22"/>
+      <c r="I131" s="24"/>
       <c r="J131">
         <v>2116045</v>
       </c>
@@ -30756,11 +30756,11 @@
         <f t="shared" si="14"/>
         <v>-550.00000005873244</v>
       </c>
-      <c r="P49" s="24" t="s">
+      <c r="P49" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="Q49" s="23"/>
-      <c r="R49" s="23"/>
+      <c r="Q49" s="21"/>
+      <c r="R49" s="21"/>
     </row>
     <row r="50" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="B50" s="17">
@@ -30800,11 +30800,11 @@
         <f t="shared" si="14"/>
         <v>-550.00000008036147</v>
       </c>
-      <c r="P50" s="24" t="s">
+      <c r="P50" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="Q50" s="23"/>
-      <c r="R50" s="23"/>
+      <c r="Q50" s="21"/>
+      <c r="R50" s="21"/>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="K51" t="s">
@@ -30818,49 +30818,49 @@
         <f>SUM(M39:M50)</f>
         <v>-6271.3727227715071</v>
       </c>
-      <c r="P51" s="23">
+      <c r="P51" s="21">
         <v>2768</v>
       </c>
-      <c r="Q51" s="23">
+      <c r="Q51" s="21">
         <f>P51*(1-R47/100)</f>
         <v>2653.0912938133069</v>
       </c>
-      <c r="R51" s="23">
+      <c r="R51" s="21">
         <f>P51-Q51</f>
         <v>114.90870618669305</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="P52" s="23">
+      <c r="P52" s="21">
         <v>30.7</v>
       </c>
-      <c r="Q52" s="23">
+      <c r="Q52" s="21">
         <f>P52*(1-R41/100)</f>
         <v>12.319956606941059</v>
       </c>
-      <c r="R52" s="23">
+      <c r="R52" s="21">
         <f>P52-Q52</f>
         <v>18.380043393058941</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="P53" s="23">
+      <c r="P53" s="21">
         <f>SUM(P51:P52)</f>
         <v>2798.7</v>
       </c>
-      <c r="Q53" s="23">
+      <c r="Q53" s="21">
         <f>SUM(Q51:Q52)</f>
         <v>2665.4112504202481</v>
       </c>
-      <c r="R53" s="23">
+      <c r="R53" s="21">
         <f>SUM(R51:R52)</f>
         <v>133.28874957975199</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="P54" s="23"/>
-      <c r="Q54" s="23"/>
-      <c r="R54" s="23"/>
+      <c r="P54" s="21"/>
+      <c r="Q54" s="21"/>
+      <c r="R54" s="21"/>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B56" s="9" t="s">
@@ -31634,7 +31634,7 @@
       </c>
     </row>
     <row r="130" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="I130" s="22" t="s">
+      <c r="I130" s="24" t="s">
         <v>58</v>
       </c>
       <c r="J130">
@@ -31645,7 +31645,7 @@
       </c>
     </row>
     <row r="131" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="I131" s="22"/>
+      <c r="I131" s="24"/>
       <c r="J131">
         <v>2116045</v>
       </c>

--- a/pidsg25Evaluation.xlsx
+++ b/pidsg25Evaluation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/debdeeppaul/Documents/Procurement/PIDSG25/pricesaa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D216AC-73DF-0546-A26B-53EE8CBABBD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F13D83A7-5CC4-D34B-A443-8BB7F49C533F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15680" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19506,7 +19506,7 @@
     <col min="7" max="7" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:14" x14ac:dyDescent="0.2">
       <c r="I1" t="s">
         <v>33</v>
       </c>
@@ -19517,7 +19517,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
       <c r="H2" s="24" t="s">
         <v>58</v>
       </c>
@@ -19528,7 +19528,7 @@
         <v>765195</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
       <c r="H3" s="24"/>
       <c r="I3">
         <v>2116045</v>
@@ -19540,7 +19540,7 @@
         <v>160216</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.2">
       <c r="I4">
         <f>SUM(I2:I3)</f>
         <v>3432556.5530000003</v>
@@ -19554,7 +19554,7 @@
         <v>3041456</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.2">
       <c r="I5">
         <v>3432556.5529999998</v>
       </c>
@@ -19565,7 +19565,7 @@
         <v>3041456</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>26</v>
       </c>
@@ -19576,7 +19576,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C8" s="8" t="s">
         <v>30</v>
       </c>
@@ -19608,7 +19608,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B9" s="7">
         <v>45772</v>
       </c>
@@ -19650,8 +19650,12 @@
         <f>L25</f>
         <v>307260.04547368421</v>
       </c>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N9">
+        <f>G9*31.104</f>
+        <v>152000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B10" s="7">
         <v>45802</v>
       </c>
@@ -19694,7 +19698,7 @@
         <v>307260.04547368421</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B11" s="7">
         <v>45833</v>
       </c>
@@ -19737,7 +19741,7 @@
         <v>625446.59873684205</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B12" s="7">
         <v>45863</v>
       </c>
@@ -19780,7 +19784,7 @@
         <v>837570.96757894731</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B13" s="7">
         <v>45894</v>
       </c>
@@ -19823,7 +19827,7 @@
         <v>1039329.1764210517</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B14" s="7">
         <v>45925</v>
       </c>
@@ -19866,7 +19870,7 @@
         <v>1072454.3241951317</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B15" s="7">
         <v>45955</v>
       </c>
@@ -19909,7 +19913,7 @@
         <v>1072454.3241951317</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B16" s="7">
         <v>45986</v>
       </c>
@@ -21349,14 +21353,14 @@
         <v>55</v>
       </c>
       <c r="M60" s="8">
-        <v>1531015.5531492536</v>
+        <v>1531015.5531492501</v>
       </c>
       <c r="N60" s="8">
         <v>1072454.3241951317</v>
       </c>
       <c r="O60" s="8">
         <f>100*(M60-N60)/M60</f>
-        <v>29.95144157816523</v>
+        <v>29.95144157816507</v>
       </c>
     </row>
     <row r="61" spans="5:20" x14ac:dyDescent="0.2">
@@ -21381,9 +21385,7 @@
       <c r="M62" s="8">
         <v>0</v>
       </c>
-      <c r="N62" s="11">
-        <v>162857.65087448523</v>
-      </c>
+      <c r="N62" s="11"/>
       <c r="O62" s="8"/>
     </row>
     <row r="63" spans="5:20" x14ac:dyDescent="0.2">
@@ -21401,15 +21403,15 @@
       </c>
       <c r="M63" s="8">
         <f>SUM(M60:M62)</f>
-        <v>3879440.5531492536</v>
+        <v>3879440.5531492503</v>
       </c>
       <c r="N63" s="8">
         <f>SUM(N60:N62)</f>
-        <v>3583736.9750696169</v>
+        <v>3420879.3241951317</v>
       </c>
       <c r="O63" s="8">
         <f t="shared" si="15"/>
-        <v>7.6223252819170106</v>
+        <v>11.820292711583582</v>
       </c>
     </row>
     <row r="64" spans="5:20" x14ac:dyDescent="0.2">
